--- a/Color/LogicDocs/formulas y funciones .xlsx
+++ b/Color/LogicDocs/formulas y funciones .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coatsplc-my.sharepoint.com/personal/elkinduvan_quebradaguapacha_coats_com/Documents/Escritorio/Colorimetria/Color/LogicDocs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1060" documentId="8_{9F78D261-5971-4E36-A791-098E2ABB119D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{505A8C73-BF1A-4B90-8D3A-1129F6B1D33A}"/>
+  <xr:revisionPtr revIDLastSave="1132" documentId="8_{9F78D261-5971-4E36-A791-098E2ABB119D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A586577-7C02-4391-B8F9-780D0F2601CF}"/>
   <bookViews>
-    <workbookView xWindow="10695" yWindow="0" windowWidth="11010" windowHeight="12885" xr2:uid="{74F1A0B1-3ED8-4C59-B930-9B261CE40F5C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="1" activeTab="3" xr2:uid="{74F1A0B1-3ED8-4C59-B930-9B261CE40F5C}"/>
   </bookViews>
   <sheets>
     <sheet name="CALCULO SAMPLE COMPARISON " sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="140">
   <si>
     <t>CMC(2.1)</t>
   </si>
@@ -377,18 +377,9 @@
     <t>b</t>
   </si>
   <si>
-    <t>variacion</t>
-  </si>
-  <si>
     <t>(((ll-ls)/ls)*100)</t>
   </si>
   <si>
-    <t>l</t>
-  </si>
-  <si>
-    <t>((std- lot)/std)</t>
-  </si>
-  <si>
     <t xml:space="preserve">dl </t>
   </si>
   <si>
@@ -396,6 +387,190 @@
   </si>
   <si>
     <t>dh</t>
+  </si>
+  <si>
+    <t>varacion</t>
+  </si>
+  <si>
+    <t>Valor Abs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L </t>
+  </si>
+  <si>
+    <t>lot-std</t>
+  </si>
+  <si>
+    <t>(std-lot)/std</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">_      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Si esta opaco y si esta oscuro; entonces </t>
+    </r>
+  </si>
+  <si>
+    <t>(-)</t>
+  </si>
+  <si>
+    <t>(=) restar brillante 0%</t>
+  </si>
+  <si>
+    <t>Receta # 1</t>
+  </si>
+  <si>
+    <t>Receta # 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receta # 3 </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">_  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Si esta opaco y si esta oscuro; entonces </t>
+    </r>
+  </si>
+  <si>
+    <t>(=) restar oscuro 0%</t>
+  </si>
+  <si>
+    <t>_+%</t>
+  </si>
+  <si>
+    <t>------</t>
+  </si>
+  <si>
+    <t>-------</t>
+  </si>
+  <si>
+    <t>oscuro (-)</t>
+  </si>
+  <si>
+    <t>✔</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">_  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Si esta brillante y si esta claro; </t>
+    </r>
+  </si>
+  <si>
+    <t>(+)</t>
+  </si>
+  <si>
+    <t>(=) sumar opaco 0%</t>
+  </si>
+  <si>
+    <t>--------</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Si esta opaco y si esta esta claro; entonces </t>
+    </r>
+  </si>
+  <si>
+    <t>(=) sumar brillante 0%</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>claro (+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brillante </t>
+  </si>
+  <si>
+    <t xml:space="preserve">opaco </t>
+  </si>
+  <si>
+    <t>delta %</t>
+  </si>
+  <si>
+    <t>La teoría de Kubelka-Munk (1931) es un modelo matemático fundamental que describe cómo la luz interactúa con materiales difusores y absorbentes, como pinturas, recubrimientos o polvos, relacionando la reflectancia con el coeficiente de absorción (\(K\)) y dispersión (\(S\)). Se basa en dos flujos de luz (uno ascendente y otro descendente) para predecir color, opacidad y concentración de pigmentos.Aspectos Clave de la Ley de Kubelka-MunkFundamento: Desarrollada por Paul Kubelka y Franz Munk, simplifica la transferencia radiativa asumiendo que la luz se difunde en medios espesos.Ecuación Fundamental: Para una muestra de espesor infinito o muy grueso, la reflectancia se relaciona con \(K\) (absorción) y \(S\) (dispersión) mediante:\(\frac{K}{S}=\frac{(1-R_{\infty })^{2}}{2R_{\infty }}\)Donde \(R_{\infty }\) es la reflectancia de una capa gruesa (reflectancia absoluta).Aplicaciones Principales:Ciencia del Color: Predecir el color y la opacidad de pinturas y recubrimientos.Espectroscopia (DRIFTS): Analizar muestras sólidas, donde se usa para convertir la reflectancia difusa en una señal linealmente proporcional a la concentración del analito.Caracterización de Materiales: Determinar la banda prohibida (band gap) de semiconductores en polvo.Modelo de Dos Flujos: Considera un flujo de luz hacia abajo (incidente) y otro hacia arriba (dispersado) para modelar la dispersión y la absorción.Limitaciones: Funciona mejor en medios turbios y con alta difusión. No se aplica con precisión en películas muy delgadas o materiales transparentes.</t>
+  </si>
+  <si>
+    <t>UTILIZACION DE TEORIA EN EL PROGRAMA</t>
+  </si>
+  <si>
+    <t>El Salto de "Espacio Color" a "Fuerza de Color" (K/S)
+El programa no calcula sobre los valores $L^*, a^*, b^*$ directamente. Utiliza la ley de Kubelka-Munk.
+•	El Problema: El color no es lineal. Si duplicas la cantidad de colorante en una tina, el hilo no se ve "el doble de oscuro".
+•	La Solución Dinámica: El programa convierte la reflectancia en una función llamada $K/S$ (Absorción/Dispersión). Esto permite que el $\Delta\%$ que ves en pantalla sea directamente proporcional a la masa de colorante.
+•	Resultado: Si el programa dice $-2.60\%$, es porque calculó cuánta energía de luz se está perdiendo y cuántos gramos de colorante real compensan esa pérdida.
+2. Ponderación Multiluminante (Metamerismo)
+Un cálculo dinámico significa que el programa está analizando el lote bajo tres realidades distintas simultáneamente (D65, TL84, A).
+•	Si el lote se desvía mucho bajo luz de tungsteno (A) pero poco bajo luz de día (D65), el programa no te da un promedio simple.
+•	Dinámica: El algoritmo prioriza el iluminante principal de Coats, pero ajusta la recomendación de receta para que el color sea estable en todas las luces. El Excel, al ser estático, solo ve un escenario a la vez.
+3. El Algoritmo de Diferencia de Color (CMC 2:1 o CIE2000)
+•	Cálculo Dinámico (Programa): Crea un elipsoide de tolerancia. Si el color es un amarillo brillante, el elipsoide se expande (somos menos sensibles). Si el color es un neutro, el elipsoide se encoge.
+•	Por eso el programa puede decir que un lote "CUMPLE" aunque numéricamente parezca desviado, o viceversa.
+Resumen del Proceso Interno
+Cada vez que presionas "Iniciar Escaneo", ocurre esta secuencia en milisegundos:
+1.	Normalización: El OCR entrega los números.
+2.	Transformación: Los números se convierten en curvas de energía ($K/S$).
+3.	Comparación Vectorial: Se mide la distancia entre el estándar y el lote dentro del elipsoide de tolerancia.
+4.	Traducción Química: Esa distancia se traduce a porcentaje de colorante ($\Delta\%$) y finalmente a la recomendación de ingeniería que ves en la pantalla final.</t>
   </si>
 </sst>
 </file>
@@ -409,7 +584,7 @@
     <numFmt numFmtId="167" formatCode="0.00000"/>
     <numFmt numFmtId="168" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -505,6 +680,56 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -538,7 +763,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -627,11 +852,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -762,6 +1012,44 @@
     <xf numFmtId="9" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -774,12 +1062,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -813,27 +1095,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -843,9 +1125,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -858,6 +1153,579 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Straight Arrow Connector 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A036C56-3AA8-4812-A378-E9E2966DC91F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="7620000"/>
+          <a:ext cx="876300" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Arrow Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A3EC302-F39C-47B8-A208-2515A9C52782}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="571500" y="7810500"/>
+          <a:ext cx="923925" cy="219075"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Arrow Connector 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{131057BE-94F2-461A-881A-47D5287DDF76}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2190750" y="8039100"/>
+          <a:ext cx="704850" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="Straight Arrow Connector 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC2A0F86-4407-4382-9834-77D8CEE39FEA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1676400" y="8020050"/>
+          <a:ext cx="361950" cy="333375"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Arrow: Right 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F0159DB-27BF-4085-9F1C-214BB34B493C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2981325" y="7429500"/>
+          <a:ext cx="1457325" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-CO" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>712615</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>121756</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>207648</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>30833</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Arrow: Right 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A97DA82C-D1AC-4E8C-835E-A5555789F8D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="8132590" y="7598881"/>
+          <a:ext cx="1066658" cy="328177"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-CO" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1273175</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>62442</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>68792</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>3175</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Right Bracket 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC385C18-FF22-4255-AD8B-2DB2ACC26C72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7302500" y="7120467"/>
+          <a:ext cx="186267" cy="359833"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightBracket">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-CO" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1261533</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>49741</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>202141</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Right Bracket 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9076EC7-6620-40E0-8522-5F2194AF656F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7290858" y="7526866"/>
+          <a:ext cx="167217" cy="361950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightBracket">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-CO" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>596198</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>68841</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>122982</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>189584</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Arrow: Right 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3179BF79-080F-423F-AFDE-D8EC7299F772}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="8016173" y="7126866"/>
+          <a:ext cx="1098409" cy="330293"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-CO" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>656166</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>21167</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>690950</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>141910</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Arrow: Right 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{455ABC7C-5BBB-4EE4-8FDC-A3FA8D2FB076}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="11095566" y="7288742"/>
+          <a:ext cx="1073009" cy="330293"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-CO" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1268,16 +2136,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BE2DF79-A7C0-4C59-8A5D-80E5B6D3C3CA}">
-  <dimension ref="A1:U29"/>
+  <dimension ref="A1:U44"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.7109375" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" customWidth="1"/>
+    <col min="4" max="5" width="11.140625" customWidth="1"/>
     <col min="6" max="6" width="20.42578125" customWidth="1"/>
-    <col min="9" max="9" width="33" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="11.5703125" customWidth="1"/>
     <col min="11" max="11" width="10.5703125" customWidth="1"/>
     <col min="12" max="12" width="11.140625" customWidth="1"/>
@@ -1291,13 +2157,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
+      <c r="A1" s="68" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -1312,14 +2178,16 @@
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F2" s="1"/>
+        <v>108</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="G2" s="1"/>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="57"/>
+      <c r="I2" s="71"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -1328,33 +2196,36 @@
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="B3" s="33">
         <v>82.83</v>
       </c>
       <c r="C3" s="33">
-        <v>80.680000000000007</v>
-      </c>
-      <c r="D3" s="12">
+        <v>80.599999999999994</v>
+      </c>
+      <c r="D3" s="54">
         <f>+(B3-C3)/B3</f>
-        <v>2.5956778944826651E-2</v>
-      </c>
-      <c r="E3" s="12">
+        <v>2.6922612579983147E-2</v>
+      </c>
+      <c r="E3" s="54">
         <f>+ABS(D3)</f>
-        <v>2.5956778944826651E-2</v>
-      </c>
-      <c r="F3" s="1"/>
+        <v>2.6922612579983147E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <f>E3/100%</f>
+        <v>2.6922612579983147E-2</v>
+      </c>
       <c r="G3" s="1"/>
       <c r="H3" s="13">
         <f>+E3/B3</f>
-        <v>3.1337412706539483E-4</v>
+        <v>3.2503455970038812E-4</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>101</v>
       </c>
@@ -1372,7 +2243,10 @@
         <f>+ABS(D4)</f>
         <v>8.6376404494382053E-2</v>
       </c>
-      <c r="F4" s="1"/>
+      <c r="F4" s="55">
+        <f>E4/100%</f>
+        <v>8.6376404494382053E-2</v>
+      </c>
       <c r="G4" s="1"/>
       <c r="H4" s="13">
         <f>+E4/B4</f>
@@ -1382,7 +2256,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>102</v>
       </c>
@@ -1392,7 +2266,7 @@
       <c r="C5" s="33">
         <v>-3.47</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="56">
         <f>+(B5-C5)/B5</f>
         <v>3.611111111111108E-2</v>
       </c>
@@ -1400,7 +2274,10 @@
         <f>+ABS(D5)</f>
         <v>3.611111111111108E-2</v>
       </c>
-      <c r="F5" s="1"/>
+      <c r="F5" s="55">
+        <f>E5/100%</f>
+        <v>3.611111111111108E-2</v>
+      </c>
       <c r="G5" s="1"/>
       <c r="H5" s="13">
         <f>+E5/B5</f>
@@ -1410,7 +2287,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:21" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>53</v>
@@ -1437,6 +2314,10 @@
         <f>MOD(ATAN2(B4,B5)*180/PI(),360)</f>
         <v>194.18761901931759</v>
       </c>
+      <c r="F9" s="57">
+        <f>E4/(1-E4)</f>
+        <v>9.4542659492697953E-2</v>
+      </c>
     </row>
     <row r="10" spans="1:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
@@ -1465,11 +2346,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14"/>
       <c r="B13" s="15"/>
     </row>
-    <row r="14" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7" t="s">
@@ -1527,8 +2408,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="55" t="s">
+    <row r="15" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="69" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="7" t="s">
@@ -1543,39 +2424,39 @@
       <c r="F15" s="28">
         <v>-3.6</v>
       </c>
-      <c r="G15" s="58">
+      <c r="G15" s="69">
         <f>+(D15-D16)/D15</f>
         <v>2.5956778944826651E-2</v>
       </c>
-      <c r="H15" s="59">
+      <c r="H15" s="69">
         <f>+(E15-E16)/E15</f>
         <v>8.6376404494382053E-2</v>
       </c>
-      <c r="I15" s="58">
+      <c r="I15" s="69">
         <f>+(F15-F16)/F15</f>
         <v>3.611111111111108E-2</v>
       </c>
-      <c r="J15" s="58">
+      <c r="J15" s="69">
         <f>+ABS(G15)</f>
         <v>2.5956778944826651E-2</v>
       </c>
-      <c r="K15" s="58">
+      <c r="K15" s="69">
         <f>+ABS(H15)</f>
         <v>8.6376404494382053E-2</v>
       </c>
-      <c r="L15" s="55">
+      <c r="L15" s="69">
         <f>+ABS(I15)</f>
         <v>3.611111111111108E-2</v>
       </c>
-      <c r="M15" s="56">
+      <c r="M15" s="70">
         <f>+K15/F15</f>
         <v>-2.3993445692883902E-2</v>
       </c>
-      <c r="N15" s="56">
+      <c r="N15" s="70">
         <f>+K15/E15</f>
         <v>-6.0657587425830091E-3</v>
       </c>
-      <c r="O15" s="56">
+      <c r="O15" s="70">
         <f>+L15/F15</f>
         <v>-1.0030864197530855E-2</v>
       </c>
@@ -1604,8 +2485,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="55"/>
+    <row r="16" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="69"/>
       <c r="C16" s="7" t="s">
         <v>26</v>
       </c>
@@ -1618,15 +2499,15 @@
       <c r="F16" s="28">
         <v>-3.47</v>
       </c>
-      <c r="G16" s="58"/>
-      <c r="H16" s="59"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="58"/>
-      <c r="K16" s="58"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="55"/>
-      <c r="N16" s="55"/>
-      <c r="O16" s="55"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="69"/>
+      <c r="K16" s="69"/>
+      <c r="L16" s="69"/>
+      <c r="M16" s="69"/>
+      <c r="N16" s="69"/>
+      <c r="O16" s="69"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
@@ -1634,8 +2515,8 @@
       <c r="T16" s="7"/>
       <c r="U16" s="7"/>
     </row>
-    <row r="17" spans="2:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="55" t="s">
+    <row r="17" spans="2:21" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="69" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="7" t="s">
@@ -1650,39 +2531,39 @@
       <c r="F17" s="28">
         <v>5.0599999999999996</v>
       </c>
-      <c r="G17" s="58">
+      <c r="G17" s="69">
         <f>+(D17-D18)/D17</f>
         <v>2.4813592470358161E-2</v>
       </c>
-      <c r="H17" s="59">
+      <c r="H17" s="69">
         <f>+(E17-E18)/E17</f>
         <v>5.7165231010180145E-2</v>
       </c>
-      <c r="I17" s="59">
+      <c r="I17" s="69">
         <f>+(F17-F18)/F17</f>
         <v>1.8557312252964429</v>
       </c>
-      <c r="J17" s="58">
+      <c r="J17" s="69">
         <f>+ABS(G17)</f>
         <v>2.4813592470358161E-2</v>
       </c>
-      <c r="K17" s="55">
+      <c r="K17" s="69">
         <f>+ABS(H17)</f>
         <v>5.7165231010180145E-2</v>
       </c>
-      <c r="L17" s="55">
+      <c r="L17" s="69">
         <f>+ABS(I17)</f>
         <v>1.8557312252964429</v>
       </c>
-      <c r="M17" s="56">
+      <c r="M17" s="70">
         <f>+J17/D17</f>
         <v>3.0330757206158365E-4</v>
       </c>
-      <c r="N17" s="56">
+      <c r="N17" s="70">
         <f>+K17/E17</f>
         <v>-4.4765255293798076E-3</v>
       </c>
-      <c r="O17" s="56">
+      <c r="O17" s="70">
         <f>+L17/F17</f>
         <v>0.36674530144198481</v>
       </c>
@@ -1711,8 +2592,8 @@
         <v>1.6004671261736865</v>
       </c>
     </row>
-    <row r="18" spans="2:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="55"/>
+    <row r="18" spans="2:21" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="69"/>
       <c r="C18" s="7" t="s">
         <v>26</v>
       </c>
@@ -1725,15 +2606,15 @@
       <c r="F18" s="28">
         <v>-4.33</v>
       </c>
-      <c r="G18" s="58"/>
-      <c r="H18" s="59"/>
-      <c r="I18" s="59"/>
-      <c r="J18" s="58"/>
-      <c r="K18" s="55"/>
-      <c r="L18" s="55"/>
-      <c r="M18" s="55"/>
-      <c r="N18" s="55"/>
-      <c r="O18" s="55"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="69"/>
+      <c r="K18" s="69"/>
+      <c r="L18" s="69"/>
+      <c r="M18" s="69"/>
+      <c r="N18" s="69"/>
+      <c r="O18" s="69"/>
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
       <c r="R18" s="7"/>
@@ -1741,8 +2622,8 @@
       <c r="T18" s="7"/>
       <c r="U18" s="7"/>
     </row>
-    <row r="19" spans="2:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="55" t="s">
+    <row r="19" spans="2:21" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="69" t="s">
         <v>32</v>
       </c>
       <c r="C19" s="7" t="s">
@@ -1757,39 +2638,39 @@
       <c r="F19" s="28">
         <v>7.39</v>
       </c>
-      <c r="G19" s="58">
+      <c r="G19" s="69">
         <f>+(D19-D20)/D19</f>
         <v>4.9419322955275513E-2</v>
       </c>
-      <c r="H19" s="59">
+      <c r="H19" s="69">
         <f>+(E19-E20)/E19</f>
         <v>5.7884231536926095E-2</v>
       </c>
-      <c r="I19" s="58">
+      <c r="I19" s="69">
         <f>+(F19-F20)/F19</f>
         <v>7.9837618403247615E-2</v>
       </c>
-      <c r="J19" s="58">
+      <c r="J19" s="69">
         <f>+ABS(G19)</f>
         <v>4.9419322955275513E-2</v>
       </c>
-      <c r="K19" s="55">
+      <c r="K19" s="69">
         <f>+ABS(H19)</f>
         <v>5.7884231536926095E-2</v>
       </c>
-      <c r="L19" s="55">
+      <c r="L19" s="69">
         <f>+ABS(I19)</f>
         <v>7.9837618403247615E-2</v>
       </c>
-      <c r="M19" s="56">
+      <c r="M19" s="70">
         <f>+J19/D19</f>
         <v>6.1056737033945529E-4</v>
       </c>
-      <c r="N19" s="56">
+      <c r="N19" s="70">
         <f>+K19/E19</f>
         <v>-3.8512462765752562E-3</v>
       </c>
-      <c r="O19" s="56">
+      <c r="O19" s="70">
         <f>+L19/F19</f>
         <v>1.0803466631021328E-2</v>
       </c>
@@ -1818,8 +2699,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="55"/>
+    <row r="20" spans="2:21" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="69"/>
       <c r="C20" s="7" t="s">
         <v>26</v>
       </c>
@@ -1832,15 +2713,15 @@
       <c r="F20" s="28">
         <v>6.8</v>
       </c>
-      <c r="G20" s="58"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="58"/>
-      <c r="K20" s="55"/>
-      <c r="L20" s="55"/>
-      <c r="M20" s="55"/>
-      <c r="N20" s="55"/>
-      <c r="O20" s="55"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
+      <c r="I20" s="69"/>
+      <c r="J20" s="69"/>
+      <c r="K20" s="69"/>
+      <c r="L20" s="69"/>
+      <c r="M20" s="69"/>
+      <c r="N20" s="69"/>
+      <c r="O20" s="69"/>
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
       <c r="R20" s="7"/>
@@ -1848,8 +2729,8 @@
       <c r="T20" s="7"/>
       <c r="U20" s="7"/>
     </row>
-    <row r="21" spans="2:21" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="2:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="2:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="7" t="s">
         <v>31</v>
       </c>
@@ -1860,59 +2741,184 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="2:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="2:21" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+    </row>
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B25" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F38" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="I38" s="67" t="s">
+        <v>113</v>
+      </c>
+      <c r="L38" t="s">
+        <v>114</v>
+      </c>
+      <c r="M38" s="59"/>
+      <c r="N38" s="59"/>
+      <c r="O38" s="60" t="s">
+        <v>79</v>
+      </c>
+      <c r="P38" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q38" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="R38" s="61" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>104</v>
+      </c>
+      <c r="C39" t="s">
+        <v>105</v>
+      </c>
+      <c r="D39" t="s">
         <v>106</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I23" t="s">
-        <v>105</v>
-      </c>
-      <c r="J23" t="s">
-        <v>101</v>
-      </c>
-      <c r="K23" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="2:21" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="N29" t="s">
-        <v>107</v>
-      </c>
-      <c r="O29" t="s">
-        <v>108</v>
-      </c>
-      <c r="P29" t="s">
-        <v>109</v>
+      <c r="F39" s="58" t="s">
+        <v>118</v>
+      </c>
+      <c r="I39" s="67"/>
+      <c r="L39" t="s">
+        <v>119</v>
+      </c>
+      <c r="M39" s="62"/>
+      <c r="N39" s="62"/>
+      <c r="O39" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="P39" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q39" s="64" t="s">
+        <v>121</v>
+      </c>
+      <c r="R39" s="63" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" t="s">
+        <v>124</v>
+      </c>
+      <c r="D40" t="s">
+        <v>124</v>
+      </c>
+      <c r="F40" s="58" t="s">
+        <v>125</v>
+      </c>
+      <c r="I40" s="67" t="s">
+        <v>126</v>
+      </c>
+      <c r="L40" t="s">
+        <v>127</v>
+      </c>
+      <c r="M40" s="62"/>
+      <c r="N40" s="62"/>
+      <c r="O40" s="63" t="s">
+        <v>33</v>
+      </c>
+      <c r="P40" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q40" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="R40" s="65"/>
+    </row>
+    <row r="41" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" t="s">
+        <v>129</v>
+      </c>
+      <c r="C41" t="s">
+        <v>124</v>
+      </c>
+      <c r="D41" t="s">
+        <v>124</v>
+      </c>
+      <c r="F41" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="I41" s="67"/>
+      <c r="L41" t="s">
+        <v>131</v>
+      </c>
+      <c r="M41" s="62"/>
+      <c r="N41" s="62"/>
+      <c r="O41" s="66" t="s">
+        <v>132</v>
+      </c>
+      <c r="P41" s="64" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q41" s="64" t="s">
+        <v>121</v>
+      </c>
+      <c r="R41" s="64" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>133</v>
+      </c>
+      <c r="B42" t="s">
+        <v>124</v>
+      </c>
+      <c r="C42" t="s">
+        <v>129</v>
+      </c>
+      <c r="D42" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>134</v>
+      </c>
+      <c r="D44" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="H15:H16"/>
+  <mergeCells count="34">
     <mergeCell ref="I15:I16"/>
     <mergeCell ref="J15:J16"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="M19:M20"/>
     <mergeCell ref="N19:N20"/>
     <mergeCell ref="O19:O20"/>
     <mergeCell ref="H2:I2"/>
@@ -1926,8 +2932,28 @@
     <mergeCell ref="N15:N16"/>
     <mergeCell ref="O15:O16"/>
     <mergeCell ref="K17:K18"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="H15:H16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1954,13 +2980,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
     </row>
     <row r="3" spans="4:15" x14ac:dyDescent="0.2">
       <c r="E3" s="2"/>
@@ -2008,30 +3034,30 @@
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="4:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E5" s="68" t="s">
+      <c r="E5" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="65">
+      <c r="F5" s="77">
         <v>-0.78</v>
       </c>
-      <c r="G5" s="65">
+      <c r="G5" s="77">
         <v>-0.86</v>
       </c>
-      <c r="H5" s="67">
+      <c r="H5" s="79">
         <v>0.17</v>
       </c>
-      <c r="I5" s="63">
+      <c r="I5" s="75">
         <v>1.17</v>
       </c>
-      <c r="J5" s="72">
+      <c r="J5" s="87">
         <f>+ABS(F5*10)</f>
         <v>7.8000000000000007</v>
       </c>
-      <c r="K5" s="74">
+      <c r="K5" s="86">
         <f>+ABS(G5*10)</f>
         <v>8.6</v>
       </c>
-      <c r="L5" s="74">
+      <c r="L5" s="86">
         <f>+ABS(H5*10)</f>
         <v>1.7000000000000002</v>
       </c>
@@ -2049,43 +3075,43 @@
       </c>
     </row>
     <row r="6" spans="4:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E6" s="68"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="72"/>
-      <c r="K6" s="74"/>
-      <c r="L6" s="74"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="87"/>
+      <c r="K6" s="86"/>
+      <c r="L6" s="86"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
     <row r="7" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E7" s="57" t="s">
+      <c r="E7" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="60">
+      <c r="F7" s="72">
         <v>-0.74</v>
       </c>
-      <c r="G7" s="62">
+      <c r="G7" s="74">
         <v>-0.54</v>
       </c>
-      <c r="H7" s="62">
+      <c r="H7" s="74">
         <v>0.1</v>
       </c>
-      <c r="I7" s="61">
+      <c r="I7" s="73">
         <v>0.92</v>
       </c>
-      <c r="J7" s="73">
+      <c r="J7" s="88">
         <f>+ABS(F7*10)</f>
         <v>7.4</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="89">
         <f>+ABS(G7*10)</f>
         <v>5.4</v>
       </c>
-      <c r="L7" s="71">
+      <c r="L7" s="89">
         <f>+ABS(H7*10)</f>
         <v>1</v>
       </c>
@@ -2103,43 +3129,43 @@
       </c>
     </row>
     <row r="8" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E8" s="57"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="73"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="71"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73"/>
+      <c r="J8" s="88"/>
+      <c r="K8" s="89"/>
+      <c r="L8" s="89"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E9" s="57" t="s">
+      <c r="E9" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="60">
+      <c r="F9" s="72">
         <v>-0.73</v>
       </c>
-      <c r="G9" s="62">
+      <c r="G9" s="74">
         <v>-0.68</v>
       </c>
-      <c r="H9" s="62">
+      <c r="H9" s="74">
         <v>-0.12</v>
       </c>
-      <c r="I9" s="61">
+      <c r="I9" s="73">
         <v>1.01</v>
       </c>
-      <c r="J9" s="73">
+      <c r="J9" s="88">
         <f>+ABS(F9*10)</f>
         <v>7.3</v>
       </c>
-      <c r="K9" s="71">
+      <c r="K9" s="89">
         <f>+ABS(G9*10)</f>
         <v>6.8000000000000007</v>
       </c>
-      <c r="L9" s="71">
+      <c r="L9" s="89">
         <f>+ABS(H9*10)</f>
         <v>1.2</v>
       </c>
@@ -2157,14 +3183,14 @@
       </c>
     </row>
     <row r="10" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E10" s="57"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="73"/>
-      <c r="K10" s="71"/>
-      <c r="L10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73"/>
+      <c r="J10" s="88"/>
+      <c r="K10" s="89"/>
+      <c r="L10" s="89"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2175,51 +3201,51 @@
       <c r="H11" s="9"/>
     </row>
     <row r="12" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E12" s="75" t="s">
+      <c r="E12" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="76"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="76"/>
-      <c r="I12" s="76"/>
-      <c r="J12" s="76"/>
-      <c r="K12" s="76"/>
-      <c r="L12" s="76"/>
-      <c r="M12" s="76"/>
-      <c r="N12" s="76"/>
-      <c r="O12" s="77"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="84"/>
+      <c r="J12" s="84"/>
+      <c r="K12" s="84"/>
+      <c r="L12" s="84"/>
+      <c r="M12" s="84"/>
+      <c r="N12" s="84"/>
+      <c r="O12" s="85"/>
     </row>
     <row r="13" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="E13" s="57" t="s">
+      <c r="E13" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="75" t="s">
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="76"/>
-      <c r="L13" s="76"/>
-      <c r="M13" s="76"/>
-      <c r="N13" s="76"/>
-      <c r="O13" s="77"/>
+      <c r="K13" s="84"/>
+      <c r="L13" s="84"/>
+      <c r="M13" s="84"/>
+      <c r="N13" s="84"/>
+      <c r="O13" s="85"/>
     </row>
     <row r="14" spans="4:15" x14ac:dyDescent="0.2">
       <c r="E14" s="2"/>
-      <c r="F14" s="57" t="s">
+      <c r="F14" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57" t="s">
+      <c r="G14" s="71"/>
+      <c r="H14" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="I14" s="57"/>
-      <c r="J14" s="57" t="s">
+      <c r="I14" s="71"/>
+      <c r="J14" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="K14" s="57"/>
+      <c r="K14" s="71"/>
       <c r="L14" s="2"/>
       <c r="M14" s="26" t="s">
         <v>63</v>
@@ -2232,7 +3258,7 @@
       </c>
     </row>
     <row r="15" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D15" s="69"/>
+      <c r="D15" s="81"/>
       <c r="E15" s="29" t="s">
         <v>12</v>
       </c>
@@ -2269,7 +3295,7 @@
       <c r="O15" s="26"/>
     </row>
     <row r="16" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D16" s="69"/>
+      <c r="D16" s="81"/>
       <c r="E16" s="29" t="s">
         <v>13</v>
       </c>
@@ -2302,7 +3328,7 @@
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D17" s="69"/>
+      <c r="D17" s="81"/>
       <c r="E17" s="29" t="s">
         <v>14</v>
       </c>
@@ -2335,7 +3361,7 @@
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D18" s="69"/>
+      <c r="D18" s="81"/>
       <c r="E18" s="2" t="s">
         <v>15</v>
       </c>
@@ -2378,7 +3404,7 @@
       </c>
     </row>
     <row r="19" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D19" s="69"/>
+      <c r="D19" s="81"/>
       <c r="E19" s="2" t="s">
         <v>16</v>
       </c>
@@ -2401,41 +3427,41 @@
       <c r="P19" s="27"/>
     </row>
     <row r="21" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E21" s="70" t="s">
+      <c r="E21" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="F21" s="54"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="54"/>
-      <c r="K21" s="54"/>
-      <c r="L21" s="54"/>
-      <c r="M21" s="54"/>
-      <c r="N21" s="54"/>
-      <c r="O21" s="54"/>
-      <c r="P21" s="54"/>
-      <c r="Q21" s="54"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
+      <c r="L21" s="68"/>
+      <c r="M21" s="68"/>
+      <c r="N21" s="68"/>
+      <c r="O21" s="68"/>
+      <c r="P21" s="68"/>
+      <c r="Q21" s="68"/>
     </row>
     <row r="22" spans="4:17" x14ac:dyDescent="0.2">
       <c r="E22" s="2"/>
-      <c r="F22" s="57" t="s">
+      <c r="F22" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="G22" s="57"/>
-      <c r="H22" s="57" t="s">
+      <c r="G22" s="71"/>
+      <c r="H22" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="I22" s="57"/>
-      <c r="J22" s="57" t="s">
+      <c r="I22" s="71"/>
+      <c r="J22" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="K22" s="57"/>
+      <c r="K22" s="71"/>
       <c r="L22" s="2"/>
-      <c r="M22" s="57" t="s">
+      <c r="M22" s="71" t="s">
         <v>70</v>
       </c>
-      <c r="N22" s="57"/>
+      <c r="N22" s="71"/>
       <c r="O22" s="26" t="s">
         <v>55</v>
       </c>
@@ -2447,7 +3473,7 @@
       </c>
     </row>
     <row r="23" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="69"/>
+      <c r="D23" s="81"/>
       <c r="E23" s="29" t="s">
         <v>12</v>
       </c>
@@ -2488,7 +3514,7 @@
       <c r="Q23" s="2"/>
     </row>
     <row r="24" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="69"/>
+      <c r="D24" s="81"/>
       <c r="E24" s="29" t="s">
         <v>13</v>
       </c>
@@ -2529,7 +3555,7 @@
       <c r="Q24" s="2"/>
     </row>
     <row r="25" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="69"/>
+      <c r="D25" s="81"/>
       <c r="E25" s="29" t="s">
         <v>14</v>
       </c>
@@ -2570,7 +3596,7 @@
       <c r="Q25" s="2"/>
     </row>
     <row r="26" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D26" s="69"/>
+      <c r="D26" s="81"/>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
@@ -2621,7 +3647,7 @@
       </c>
     </row>
     <row r="27" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D27" s="69"/>
+      <c r="D27" s="81"/>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
@@ -2655,41 +3681,41 @@
       <c r="Q27" s="2"/>
     </row>
     <row r="29" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E29" s="70" t="s">
+      <c r="E29" s="82" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="54"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="54"/>
-      <c r="J29" s="54"/>
-      <c r="K29" s="54"/>
-      <c r="L29" s="54"/>
-      <c r="M29" s="54"/>
-      <c r="N29" s="54"/>
-      <c r="O29" s="54"/>
-      <c r="P29" s="54"/>
-      <c r="Q29" s="54"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="68"/>
+      <c r="L29" s="68"/>
+      <c r="M29" s="68"/>
+      <c r="N29" s="68"/>
+      <c r="O29" s="68"/>
+      <c r="P29" s="68"/>
+      <c r="Q29" s="68"/>
     </row>
     <row r="30" spans="4:17" ht="25.5" x14ac:dyDescent="0.2">
       <c r="E30" s="2"/>
-      <c r="F30" s="57" t="s">
+      <c r="F30" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57" t="s">
+      <c r="G30" s="71"/>
+      <c r="H30" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="I30" s="57"/>
-      <c r="J30" s="57" t="s">
+      <c r="I30" s="71"/>
+      <c r="J30" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="K30" s="57"/>
+      <c r="K30" s="71"/>
       <c r="L30" s="2"/>
-      <c r="M30" s="57" t="s">
+      <c r="M30" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="N30" s="57"/>
+      <c r="N30" s="71"/>
       <c r="O30" s="26" t="s">
         <v>55</v>
       </c>
@@ -2701,7 +3727,7 @@
       </c>
     </row>
     <row r="31" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D31" s="69"/>
+      <c r="D31" s="81"/>
       <c r="E31" s="29" t="s">
         <v>12</v>
       </c>
@@ -2742,7 +3768,7 @@
       <c r="Q31" s="2"/>
     </row>
     <row r="32" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D32" s="69"/>
+      <c r="D32" s="81"/>
       <c r="E32" s="29" t="s">
         <v>13</v>
       </c>
@@ -2783,7 +3809,7 @@
       <c r="Q32" s="2"/>
     </row>
     <row r="33" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D33" s="69"/>
+      <c r="D33" s="81"/>
       <c r="E33" s="29" t="s">
         <v>14</v>
       </c>
@@ -2824,7 +3850,7 @@
       <c r="Q33" s="2"/>
     </row>
     <row r="34" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D34" s="69"/>
+      <c r="D34" s="81"/>
       <c r="E34" s="2" t="s">
         <v>15</v>
       </c>
@@ -2875,7 +3901,7 @@
       </c>
     </row>
     <row r="35" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D35" s="69"/>
+      <c r="D35" s="81"/>
       <c r="E35" s="2" t="s">
         <v>16</v>
       </c>
@@ -2909,43 +3935,43 @@
       <c r="Q35" s="2"/>
     </row>
     <row r="38" spans="4:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E38" s="57" t="s">
+      <c r="E38" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="F38" s="57"/>
-      <c r="G38" s="57"/>
-      <c r="H38" s="75" t="s">
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="I38" s="76"/>
-      <c r="J38" s="76"/>
-      <c r="K38" s="76"/>
-      <c r="L38" s="76"/>
-      <c r="M38" s="76"/>
-      <c r="N38" s="76"/>
-      <c r="O38" s="76"/>
-      <c r="P38" s="76"/>
-      <c r="Q38" s="77"/>
+      <c r="I38" s="84"/>
+      <c r="J38" s="84"/>
+      <c r="K38" s="84"/>
+      <c r="L38" s="84"/>
+      <c r="M38" s="84"/>
+      <c r="N38" s="84"/>
+      <c r="O38" s="84"/>
+      <c r="P38" s="84"/>
+      <c r="Q38" s="85"/>
     </row>
     <row r="39" spans="4:17" ht="25.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="E39" s="2"/>
-      <c r="F39" s="57" t="s">
+      <c r="F39" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="G39" s="57"/>
-      <c r="H39" s="57" t="s">
+      <c r="G39" s="71"/>
+      <c r="H39" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="I39" s="57"/>
-      <c r="J39" s="57" t="s">
+      <c r="I39" s="71"/>
+      <c r="J39" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="K39" s="57"/>
+      <c r="K39" s="71"/>
       <c r="L39" s="2"/>
-      <c r="M39" s="57" t="s">
+      <c r="M39" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="N39" s="57"/>
+      <c r="N39" s="71"/>
       <c r="O39" s="19" t="s">
         <v>66</v>
       </c>
@@ -3156,12 +4182,11 @@
     </row>
     <row r="50" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G50" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="H38:Q38"/>
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="J7:J8"/>
@@ -3171,8 +4196,11 @@
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="L7:L8"/>
     <mergeCell ref="L9:L10"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="E12:O12"/>
+    <mergeCell ref="J13:O13"/>
+    <mergeCell ref="E13:I13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="E29:Q29"/>
     <mergeCell ref="M39:N39"/>
     <mergeCell ref="E38:G38"/>
     <mergeCell ref="H14:I14"/>
@@ -3180,11 +4208,7 @@
     <mergeCell ref="F39:G39"/>
     <mergeCell ref="H39:I39"/>
     <mergeCell ref="J39:K39"/>
-    <mergeCell ref="E12:O12"/>
-    <mergeCell ref="J13:O13"/>
-    <mergeCell ref="E13:I13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="E29:Q29"/>
+    <mergeCell ref="H38:Q38"/>
     <mergeCell ref="D15:D19"/>
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="H30:I30"/>
@@ -3211,6 +4235,8 @@
     <mergeCell ref="G7:G8"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="E5:E6"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="E9:E10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3351,7 +4377,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BD7E673-853E-4343-94E1-725EDA103DB7}">
-  <dimension ref="B2:J19"/>
+  <dimension ref="B2:N44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.42578125" customWidth="1"/>
@@ -3362,27 +4388,28 @@
     <col min="9" max="9" width="29" customWidth="1"/>
     <col min="10" max="10" width="36" customWidth="1"/>
     <col min="12" max="13" width="9.140625" customWidth="1"/>
+    <col min="14" max="14" width="189.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H2" s="78" t="s">
+      <c r="H2" s="90" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="78"/>
+      <c r="I2" s="90"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
     </row>
     <row r="4" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="91" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="91"/>
       <c r="E4" s="7"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
     </row>
     <row r="5" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
@@ -3395,8 +4422,8 @@
         <v>75</v>
       </c>
       <c r="E5" s="7"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="37" t="s">
@@ -3410,8 +4437,8 @@
         <v>1.008</v>
       </c>
       <c r="E6" s="7"/>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="39" t="s">
@@ -3427,14 +4454,14 @@
       <c r="E7" s="7"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H8" s="78" t="s">
+      <c r="H8" s="90" t="s">
         <v>78</v>
       </c>
-      <c r="I8" s="78"/>
+      <c r="I8" s="90"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H9" s="78"/>
-      <c r="I9" s="78"/>
+      <c r="H9" s="90"/>
+      <c r="I9" s="90"/>
     </row>
     <row r="10" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B10" s="36" t="s">
@@ -3452,8 +4479,8 @@
       <c r="F10" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="H10" s="78"/>
-      <c r="I10" s="78"/>
+      <c r="H10" s="90"/>
+      <c r="I10" s="90"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="37" t="s">
@@ -3473,8 +4500,8 @@
         <f>C11*D11</f>
         <v>1.1876860800000002</v>
       </c>
-      <c r="H11" s="78"/>
-      <c r="I11" s="78"/>
+      <c r="H11" s="90"/>
+      <c r="I11" s="90"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="37" t="s">
@@ -3496,8 +4523,8 @@
         <v>0.38300260320000001</v>
       </c>
       <c r="G12" s="43"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
+      <c r="H12" s="90"/>
+      <c r="I12" s="90"/>
     </row>
     <row r="13" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B13" s="44" t="s">
@@ -3530,8 +4557,8 @@
       </c>
     </row>
     <row r="15" spans="2:10" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="80"/>
-      <c r="C15" s="80"/>
+      <c r="B15" s="92"/>
+      <c r="C15" s="92"/>
       <c r="H15" s="45" t="s">
         <v>91</v>
       </c>
@@ -3555,7 +4582,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="2:10" ht="57" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="57" x14ac:dyDescent="0.25">
       <c r="B17" s="50"/>
       <c r="C17" s="51"/>
       <c r="H17" s="45" t="s">
@@ -3568,20 +4595,231 @@
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="50"/>
       <c r="C18" s="51"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="52"/>
       <c r="C19" s="51"/>
     </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="H21" s="92" t="s">
+        <v>138</v>
+      </c>
+      <c r="I21" s="92"/>
+    </row>
+    <row r="22" spans="2:14" ht="306" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H22" s="94" t="s">
+        <v>137</v>
+      </c>
+      <c r="I22" s="94"/>
+      <c r="J22" s="94"/>
+      <c r="K22" s="93"/>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="H23" s="93"/>
+      <c r="I23" s="93"/>
+      <c r="J23" s="93"/>
+      <c r="K23" s="93"/>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="H24" s="93"/>
+      <c r="I24" s="93"/>
+      <c r="J24" s="93"/>
+      <c r="K24" s="93"/>
+    </row>
+    <row r="25" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H25" s="95" t="s">
+        <v>139</v>
+      </c>
+      <c r="I25" s="96"/>
+      <c r="J25" s="96"/>
+      <c r="K25" s="96"/>
+      <c r="L25" s="96"/>
+      <c r="M25" s="96"/>
+      <c r="N25" s="96"/>
+    </row>
+    <row r="26" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H26" s="96"/>
+      <c r="I26" s="96"/>
+      <c r="J26" s="96"/>
+      <c r="K26" s="96"/>
+      <c r="L26" s="96"/>
+      <c r="M26" s="96"/>
+      <c r="N26" s="96"/>
+    </row>
+    <row r="27" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H27" s="96"/>
+      <c r="I27" s="96"/>
+      <c r="J27" s="96"/>
+      <c r="K27" s="96"/>
+      <c r="L27" s="96"/>
+      <c r="M27" s="96"/>
+      <c r="N27" s="96"/>
+    </row>
+    <row r="28" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H28" s="96"/>
+      <c r="I28" s="96"/>
+      <c r="J28" s="96"/>
+      <c r="K28" s="96"/>
+      <c r="L28" s="96"/>
+      <c r="M28" s="96"/>
+      <c r="N28" s="96"/>
+    </row>
+    <row r="29" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H29" s="96"/>
+      <c r="I29" s="96"/>
+      <c r="J29" s="96"/>
+      <c r="K29" s="96"/>
+      <c r="L29" s="96"/>
+      <c r="M29" s="96"/>
+      <c r="N29" s="96"/>
+    </row>
+    <row r="30" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H30" s="96"/>
+      <c r="I30" s="96"/>
+      <c r="J30" s="96"/>
+      <c r="K30" s="96"/>
+      <c r="L30" s="96"/>
+      <c r="M30" s="96"/>
+      <c r="N30" s="96"/>
+    </row>
+    <row r="31" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H31" s="96"/>
+      <c r="I31" s="96"/>
+      <c r="J31" s="96"/>
+      <c r="K31" s="96"/>
+      <c r="L31" s="96"/>
+      <c r="M31" s="96"/>
+      <c r="N31" s="96"/>
+    </row>
+    <row r="32" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H32" s="96"/>
+      <c r="I32" s="96"/>
+      <c r="J32" s="96"/>
+      <c r="K32" s="96"/>
+      <c r="L32" s="96"/>
+      <c r="M32" s="96"/>
+      <c r="N32" s="96"/>
+    </row>
+    <row r="33" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H33" s="96"/>
+      <c r="I33" s="96"/>
+      <c r="J33" s="96"/>
+      <c r="K33" s="96"/>
+      <c r="L33" s="96"/>
+      <c r="M33" s="96"/>
+      <c r="N33" s="96"/>
+    </row>
+    <row r="34" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H34" s="96"/>
+      <c r="I34" s="96"/>
+      <c r="J34" s="96"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="96"/>
+      <c r="M34" s="96"/>
+      <c r="N34" s="96"/>
+    </row>
+    <row r="35" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H35" s="96"/>
+      <c r="I35" s="96"/>
+      <c r="J35" s="96"/>
+      <c r="K35" s="96"/>
+      <c r="L35" s="96"/>
+      <c r="M35" s="96"/>
+      <c r="N35" s="96"/>
+    </row>
+    <row r="36" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H36" s="96"/>
+      <c r="I36" s="96"/>
+      <c r="J36" s="96"/>
+      <c r="K36" s="96"/>
+      <c r="L36" s="96"/>
+      <c r="M36" s="96"/>
+      <c r="N36" s="96"/>
+    </row>
+    <row r="37" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H37" s="96"/>
+      <c r="I37" s="96"/>
+      <c r="J37" s="96"/>
+      <c r="K37" s="96"/>
+      <c r="L37" s="96"/>
+      <c r="M37" s="96"/>
+      <c r="N37" s="96"/>
+    </row>
+    <row r="38" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H38" s="96"/>
+      <c r="I38" s="96"/>
+      <c r="J38" s="96"/>
+      <c r="K38" s="96"/>
+      <c r="L38" s="96"/>
+      <c r="M38" s="96"/>
+      <c r="N38" s="96"/>
+    </row>
+    <row r="39" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H39" s="96"/>
+      <c r="I39" s="96"/>
+      <c r="J39" s="96"/>
+      <c r="K39" s="96"/>
+      <c r="L39" s="96"/>
+      <c r="M39" s="96"/>
+      <c r="N39" s="96"/>
+    </row>
+    <row r="40" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H40" s="96"/>
+      <c r="I40" s="96"/>
+      <c r="J40" s="96"/>
+      <c r="K40" s="96"/>
+      <c r="L40" s="96"/>
+      <c r="M40" s="96"/>
+      <c r="N40" s="96"/>
+    </row>
+    <row r="41" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H41" s="96"/>
+      <c r="I41" s="96"/>
+      <c r="J41" s="96"/>
+      <c r="K41" s="96"/>
+      <c r="L41" s="96"/>
+      <c r="M41" s="96"/>
+      <c r="N41" s="96"/>
+    </row>
+    <row r="42" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H42" s="96"/>
+      <c r="I42" s="96"/>
+      <c r="J42" s="96"/>
+      <c r="K42" s="96"/>
+      <c r="L42" s="96"/>
+      <c r="M42" s="96"/>
+      <c r="N42" s="96"/>
+    </row>
+    <row r="43" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H43" s="96"/>
+      <c r="I43" s="96"/>
+      <c r="J43" s="96"/>
+      <c r="K43" s="96"/>
+      <c r="L43" s="96"/>
+      <c r="M43" s="96"/>
+      <c r="N43" s="96"/>
+    </row>
+    <row r="44" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H44" s="96"/>
+      <c r="I44" s="96"/>
+      <c r="J44" s="96"/>
+      <c r="K44" s="96"/>
+      <c r="L44" s="96"/>
+      <c r="M44" s="96"/>
+      <c r="N44" s="96"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
+    <mergeCell ref="H25:N44"/>
     <mergeCell ref="H2:I6"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="H8:I12"/>
     <mergeCell ref="B15:C15"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H21:I21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/Color/LogicDocs/formulas y funciones .xlsx
+++ b/Color/LogicDocs/formulas y funciones .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coatsplc-my.sharepoint.com/personal/elkinduvan_quebradaguapacha_coats_com/Documents/Escritorio/Colorimetria/Color/LogicDocs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1132" documentId="8_{9F78D261-5971-4E36-A791-098E2ABB119D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A586577-7C02-4391-B8F9-780D0F2601CF}"/>
+  <xr:revisionPtr revIDLastSave="1143" documentId="8_{9F78D261-5971-4E36-A791-098E2ABB119D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B68B66F-6FCE-4FD7-8586-FF8367F09E94}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="1" activeTab="3" xr2:uid="{74F1A0B1-3ED8-4C59-B930-9B261CE40F5C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{74F1A0B1-3ED8-4C59-B930-9B261CE40F5C}"/>
   </bookViews>
   <sheets>
     <sheet name="CALCULO SAMPLE COMPARISON " sheetId="3" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <externalReference r:id="rId5"/>
   </externalReferences>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="139">
   <si>
     <t>CMC(2.1)</t>
   </si>
@@ -375,9 +376,6 @@
   </si>
   <si>
     <t>b</t>
-  </si>
-  <si>
-    <t>(((ll-ls)/ls)*100)</t>
   </si>
   <si>
     <t xml:space="preserve">dl </t>
@@ -881,7 +879,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1047,6 +1045,18 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1054,12 +1064,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1116,6 +1120,12 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1126,16 +1136,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2143,7 +2144,7 @@
     <col min="4" max="5" width="11.140625" customWidth="1"/>
     <col min="6" max="6" width="20.42578125" customWidth="1"/>
     <col min="8" max="8" width="20.85546875" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="9" max="9" width="40.85546875" customWidth="1"/>
     <col min="10" max="10" width="11.5703125" customWidth="1"/>
     <col min="11" max="11" width="10.5703125" customWidth="1"/>
     <col min="12" max="12" width="11.140625" customWidth="1"/>
@@ -2157,13 +2158,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="68" t="s">
-        <v>107</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
+      <c r="A1" s="72" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -2178,16 +2179,16 @@
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G2" s="1"/>
-      <c r="H2" s="71" t="s">
+      <c r="H2" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="71"/>
+      <c r="I2" s="73"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -2196,30 +2197,30 @@
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B3" s="33">
         <v>82.83</v>
       </c>
       <c r="C3" s="33">
-        <v>80.599999999999994</v>
+        <v>80.680000000000007</v>
       </c>
       <c r="D3" s="54">
         <f>+(B3-C3)/B3</f>
-        <v>2.6922612579983147E-2</v>
+        <v>2.5956778944826651E-2</v>
       </c>
       <c r="E3" s="54">
         <f>+ABS(D3)</f>
-        <v>2.6922612579983147E-2</v>
+        <v>2.5956778944826651E-2</v>
       </c>
       <c r="F3" s="55">
         <f>E3/100%</f>
-        <v>2.6922612579983147E-2</v>
+        <v>2.5956778944826651E-2</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="13">
         <f>+E3/B3</f>
-        <v>3.2503455970038812E-4</v>
+        <v>3.1337412706539483E-4</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>28</v>
@@ -2255,12 +2256,16 @@
       <c r="I4" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="M4">
+        <f>-14.24-(-13.01)</f>
+        <v>-1.2300000000000004</v>
+      </c>
     </row>
     <row r="5" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="68">
         <v>-3.6</v>
       </c>
       <c r="C5" s="33">
@@ -2743,13 +2748,13 @@
     </row>
     <row r="23" spans="2:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="24" spans="2:21" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2759,25 +2764,25 @@
     </row>
     <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="38" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F38" s="58" t="s">
+        <v>111</v>
+      </c>
+      <c r="I38" s="71" t="s">
         <v>112</v>
       </c>
-      <c r="I38" s="67" t="s">
+      <c r="L38" t="s">
         <v>113</v>
-      </c>
-      <c r="L38" t="s">
-        <v>114</v>
       </c>
       <c r="M38" s="59"/>
       <c r="N38" s="59"/>
@@ -2785,31 +2790,31 @@
         <v>79</v>
       </c>
       <c r="P38" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q38" s="61" t="s">
         <v>115</v>
       </c>
-      <c r="Q38" s="61" t="s">
+      <c r="R38" s="61" t="s">
         <v>116</v>
-      </c>
-      <c r="R38" s="61" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39" t="s">
         <v>104</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>105</v>
       </c>
-      <c r="D39" t="s">
-        <v>106</v>
-      </c>
       <c r="F39" s="58" t="s">
+        <v>117</v>
+      </c>
+      <c r="I39" s="71"/>
+      <c r="L39" t="s">
         <v>118</v>
-      </c>
-      <c r="I39" s="67"/>
-      <c r="L39" t="s">
-        <v>119</v>
       </c>
       <c r="M39" s="62"/>
       <c r="N39" s="62"/>
@@ -2817,36 +2822,36 @@
         <v>32</v>
       </c>
       <c r="P39" s="64" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q39" s="64" t="s">
         <v>120</v>
       </c>
-      <c r="Q39" s="64" t="s">
+      <c r="R39" s="63" t="s">
         <v>121</v>
-      </c>
-      <c r="R39" s="63" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>122</v>
+      </c>
+      <c r="B40" t="s">
         <v>123</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
+        <v>123</v>
+      </c>
+      <c r="D40" t="s">
+        <v>123</v>
+      </c>
+      <c r="F40" s="58" t="s">
         <v>124</v>
       </c>
-      <c r="C40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D40" t="s">
-        <v>124</v>
-      </c>
-      <c r="F40" s="58" t="s">
+      <c r="I40" s="71" t="s">
         <v>125</v>
       </c>
-      <c r="I40" s="67" t="s">
+      <c r="L40" t="s">
         <v>126</v>
-      </c>
-      <c r="L40" t="s">
-        <v>127</v>
       </c>
       <c r="M40" s="62"/>
       <c r="N40" s="62"/>
@@ -2854,71 +2859,69 @@
         <v>33</v>
       </c>
       <c r="P40" s="64" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q40" s="64" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R40" s="65"/>
     </row>
     <row r="41" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
+        <v>128</v>
+      </c>
+      <c r="C41" t="s">
+        <v>123</v>
+      </c>
+      <c r="D41" t="s">
+        <v>123</v>
+      </c>
+      <c r="F41" s="58" t="s">
         <v>129</v>
       </c>
-      <c r="C41" t="s">
-        <v>124</v>
-      </c>
-      <c r="D41" t="s">
-        <v>124</v>
-      </c>
-      <c r="F41" s="58" t="s">
+      <c r="I41" s="71"/>
+      <c r="L41" t="s">
         <v>130</v>
-      </c>
-      <c r="I41" s="67"/>
-      <c r="L41" t="s">
-        <v>131</v>
       </c>
       <c r="M41" s="62"/>
       <c r="N41" s="62"/>
       <c r="O41" s="66" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P41" s="64" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q41" s="64" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="R41" s="64" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
+        <v>133</v>
+      </c>
+      <c r="D44" t="s">
         <v>134</v>
-      </c>
-      <c r="D44" t="s">
-        <v>135</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="J15:J16"/>
     <mergeCell ref="N19:N20"/>
     <mergeCell ref="O19:O20"/>
     <mergeCell ref="H2:I2"/>
@@ -2933,24 +2936,26 @@
     <mergeCell ref="O15:O16"/>
     <mergeCell ref="K17:K18"/>
     <mergeCell ref="K15:K16"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="I19:I20"/>
     <mergeCell ref="I38:I39"/>
     <mergeCell ref="I40:I41"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I15:I16"/>
     <mergeCell ref="M19:M20"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="G19:G20"/>
     <mergeCell ref="J19:J20"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="I19:I20"/>
     <mergeCell ref="J17:J18"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="G15:G16"/>
     <mergeCell ref="H15:H16"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="J15:J16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2959,7 +2964,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F05E7DF8-3200-46CC-8D04-8DEE3E3EFF1F}">
-  <dimension ref="D2:Q50"/>
+  <dimension ref="D2:Q44"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="9.140625" style="1" customWidth="1"/>
@@ -2980,13 +2985,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E2" s="71" t="s">
+      <c r="E2" s="73" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
     </row>
     <row r="3" spans="4:15" x14ac:dyDescent="0.2">
       <c r="E3" s="2"/>
@@ -3034,30 +3039,30 @@
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="4:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E5" s="80" t="s">
+      <c r="E5" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="77">
+      <c r="F5" s="79">
         <v>-0.78</v>
       </c>
-      <c r="G5" s="77">
+      <c r="G5" s="79">
         <v>-0.86</v>
       </c>
-      <c r="H5" s="79">
+      <c r="H5" s="81">
         <v>0.17</v>
       </c>
-      <c r="I5" s="75">
+      <c r="I5" s="77">
         <v>1.17</v>
       </c>
-      <c r="J5" s="87">
+      <c r="J5" s="89">
         <f>+ABS(F5*10)</f>
         <v>7.8000000000000007</v>
       </c>
-      <c r="K5" s="86">
+      <c r="K5" s="88">
         <f>+ABS(G5*10)</f>
         <v>8.6</v>
       </c>
-      <c r="L5" s="86">
+      <c r="L5" s="88">
         <f>+ABS(H5*10)</f>
         <v>1.7000000000000002</v>
       </c>
@@ -3075,43 +3080,43 @@
       </c>
     </row>
     <row r="6" spans="4:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E6" s="80"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78"/>
-      <c r="H6" s="78"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="87"/>
-      <c r="K6" s="86"/>
-      <c r="L6" s="86"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="78"/>
+      <c r="J6" s="89"/>
+      <c r="K6" s="88"/>
+      <c r="L6" s="88"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
     <row r="7" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E7" s="71" t="s">
+      <c r="E7" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="72">
+      <c r="F7" s="74">
         <v>-0.74</v>
       </c>
-      <c r="G7" s="74">
+      <c r="G7" s="76">
         <v>-0.54</v>
       </c>
-      <c r="H7" s="74">
+      <c r="H7" s="76">
         <v>0.1</v>
       </c>
-      <c r="I7" s="73">
+      <c r="I7" s="75">
         <v>0.92</v>
       </c>
-      <c r="J7" s="88">
+      <c r="J7" s="90">
         <f>+ABS(F7*10)</f>
         <v>7.4</v>
       </c>
-      <c r="K7" s="89">
+      <c r="K7" s="91">
         <f>+ABS(G7*10)</f>
         <v>5.4</v>
       </c>
-      <c r="L7" s="89">
+      <c r="L7" s="91">
         <f>+ABS(H7*10)</f>
         <v>1</v>
       </c>
@@ -3129,43 +3134,43 @@
       </c>
     </row>
     <row r="8" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E8" s="71"/>
-      <c r="F8" s="73"/>
-      <c r="G8" s="73"/>
-      <c r="H8" s="73"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="88"/>
-      <c r="K8" s="89"/>
-      <c r="L8" s="89"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="75"/>
+      <c r="J8" s="90"/>
+      <c r="K8" s="91"/>
+      <c r="L8" s="91"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E9" s="71" t="s">
+      <c r="E9" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="72">
+      <c r="F9" s="74">
         <v>-0.73</v>
       </c>
-      <c r="G9" s="74">
+      <c r="G9" s="76">
         <v>-0.68</v>
       </c>
-      <c r="H9" s="74">
+      <c r="H9" s="76">
         <v>-0.12</v>
       </c>
-      <c r="I9" s="73">
+      <c r="I9" s="75">
         <v>1.01</v>
       </c>
-      <c r="J9" s="88">
+      <c r="J9" s="90">
         <f>+ABS(F9*10)</f>
         <v>7.3</v>
       </c>
-      <c r="K9" s="89">
+      <c r="K9" s="91">
         <f>+ABS(G9*10)</f>
         <v>6.8000000000000007</v>
       </c>
-      <c r="L9" s="89">
+      <c r="L9" s="91">
         <f>+ABS(H9*10)</f>
         <v>1.2</v>
       </c>
@@ -3183,14 +3188,14 @@
       </c>
     </row>
     <row r="10" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E10" s="71"/>
-      <c r="F10" s="73"/>
-      <c r="G10" s="73"/>
-      <c r="H10" s="73"/>
-      <c r="I10" s="73"/>
-      <c r="J10" s="88"/>
-      <c r="K10" s="89"/>
-      <c r="L10" s="89"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
+      <c r="J10" s="90"/>
+      <c r="K10" s="91"/>
+      <c r="L10" s="91"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3201,51 +3206,51 @@
       <c r="H11" s="9"/>
     </row>
     <row r="12" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E12" s="83" t="s">
+      <c r="E12" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="84"/>
-      <c r="G12" s="84"/>
-      <c r="H12" s="84"/>
-      <c r="I12" s="84"/>
-      <c r="J12" s="84"/>
-      <c r="K12" s="84"/>
-      <c r="L12" s="84"/>
-      <c r="M12" s="84"/>
-      <c r="N12" s="84"/>
-      <c r="O12" s="85"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="86"/>
+      <c r="H12" s="86"/>
+      <c r="I12" s="86"/>
+      <c r="J12" s="86"/>
+      <c r="K12" s="86"/>
+      <c r="L12" s="86"/>
+      <c r="M12" s="86"/>
+      <c r="N12" s="86"/>
+      <c r="O12" s="87"/>
     </row>
     <row r="13" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="E13" s="71" t="s">
+      <c r="E13" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="83" t="s">
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="73"/>
+      <c r="J13" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="84"/>
-      <c r="L13" s="84"/>
-      <c r="M13" s="84"/>
-      <c r="N13" s="84"/>
-      <c r="O13" s="85"/>
+      <c r="K13" s="86"/>
+      <c r="L13" s="86"/>
+      <c r="M13" s="86"/>
+      <c r="N13" s="86"/>
+      <c r="O13" s="87"/>
     </row>
     <row r="14" spans="4:15" x14ac:dyDescent="0.2">
       <c r="E14" s="2"/>
-      <c r="F14" s="71" t="s">
+      <c r="F14" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71" t="s">
+      <c r="G14" s="73"/>
+      <c r="H14" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="I14" s="71"/>
-      <c r="J14" s="71" t="s">
+      <c r="I14" s="73"/>
+      <c r="J14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="K14" s="71"/>
+      <c r="K14" s="73"/>
       <c r="L14" s="2"/>
       <c r="M14" s="26" t="s">
         <v>63</v>
@@ -3258,7 +3263,7 @@
       </c>
     </row>
     <row r="15" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D15" s="81"/>
+      <c r="D15" s="83"/>
       <c r="E15" s="29" t="s">
         <v>12</v>
       </c>
@@ -3295,7 +3300,7 @@
       <c r="O15" s="26"/>
     </row>
     <row r="16" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D16" s="81"/>
+      <c r="D16" s="83"/>
       <c r="E16" s="29" t="s">
         <v>13</v>
       </c>
@@ -3328,7 +3333,7 @@
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D17" s="81"/>
+      <c r="D17" s="83"/>
       <c r="E17" s="29" t="s">
         <v>14</v>
       </c>
@@ -3361,7 +3366,7 @@
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D18" s="81"/>
+      <c r="D18" s="83"/>
       <c r="E18" s="2" t="s">
         <v>15</v>
       </c>
@@ -3404,7 +3409,7 @@
       </c>
     </row>
     <row r="19" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D19" s="81"/>
+      <c r="D19" s="83"/>
       <c r="E19" s="2" t="s">
         <v>16</v>
       </c>
@@ -3427,41 +3432,41 @@
       <c r="P19" s="27"/>
     </row>
     <row r="21" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E21" s="82" t="s">
+      <c r="E21" s="84" t="s">
         <v>50</v>
       </c>
-      <c r="F21" s="68"/>
-      <c r="G21" s="68"/>
-      <c r="H21" s="68"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="68"/>
-      <c r="K21" s="68"/>
-      <c r="L21" s="68"/>
-      <c r="M21" s="68"/>
-      <c r="N21" s="68"/>
-      <c r="O21" s="68"/>
-      <c r="P21" s="68"/>
-      <c r="Q21" s="68"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="72"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="72"/>
+      <c r="M21" s="72"/>
+      <c r="N21" s="72"/>
+      <c r="O21" s="72"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
     </row>
     <row r="22" spans="4:17" x14ac:dyDescent="0.2">
       <c r="E22" s="2"/>
-      <c r="F22" s="71" t="s">
+      <c r="F22" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="G22" s="71"/>
-      <c r="H22" s="71" t="s">
+      <c r="G22" s="73"/>
+      <c r="H22" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="I22" s="71"/>
-      <c r="J22" s="71" t="s">
+      <c r="I22" s="73"/>
+      <c r="J22" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="K22" s="71"/>
+      <c r="K22" s="73"/>
       <c r="L22" s="2"/>
-      <c r="M22" s="71" t="s">
+      <c r="M22" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="N22" s="71"/>
+      <c r="N22" s="73"/>
       <c r="O22" s="26" t="s">
         <v>55</v>
       </c>
@@ -3473,7 +3478,7 @@
       </c>
     </row>
     <row r="23" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="81"/>
+      <c r="D23" s="83"/>
       <c r="E23" s="29" t="s">
         <v>12</v>
       </c>
@@ -3514,7 +3519,7 @@
       <c r="Q23" s="2"/>
     </row>
     <row r="24" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="81"/>
+      <c r="D24" s="83"/>
       <c r="E24" s="29" t="s">
         <v>13</v>
       </c>
@@ -3555,7 +3560,7 @@
       <c r="Q24" s="2"/>
     </row>
     <row r="25" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="81"/>
+      <c r="D25" s="83"/>
       <c r="E25" s="29" t="s">
         <v>14</v>
       </c>
@@ -3596,7 +3601,7 @@
       <c r="Q25" s="2"/>
     </row>
     <row r="26" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D26" s="81"/>
+      <c r="D26" s="83"/>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
@@ -3647,7 +3652,7 @@
       </c>
     </row>
     <row r="27" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D27" s="81"/>
+      <c r="D27" s="83"/>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
@@ -3681,41 +3686,41 @@
       <c r="Q27" s="2"/>
     </row>
     <row r="29" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E29" s="82" t="s">
+      <c r="E29" s="84" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="68"/>
-      <c r="G29" s="68"/>
-      <c r="H29" s="68"/>
-      <c r="I29" s="68"/>
-      <c r="J29" s="68"/>
-      <c r="K29" s="68"/>
-      <c r="L29" s="68"/>
-      <c r="M29" s="68"/>
-      <c r="N29" s="68"/>
-      <c r="O29" s="68"/>
-      <c r="P29" s="68"/>
-      <c r="Q29" s="68"/>
+      <c r="F29" s="72"/>
+      <c r="G29" s="72"/>
+      <c r="H29" s="72"/>
+      <c r="I29" s="72"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="72"/>
+      <c r="M29" s="72"/>
+      <c r="N29" s="72"/>
+      <c r="O29" s="72"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
     </row>
     <row r="30" spans="4:17" ht="25.5" x14ac:dyDescent="0.2">
       <c r="E30" s="2"/>
-      <c r="F30" s="71" t="s">
+      <c r="F30" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="G30" s="71"/>
-      <c r="H30" s="71" t="s">
+      <c r="G30" s="73"/>
+      <c r="H30" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="I30" s="71"/>
-      <c r="J30" s="71" t="s">
+      <c r="I30" s="73"/>
+      <c r="J30" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="K30" s="71"/>
+      <c r="K30" s="73"/>
       <c r="L30" s="2"/>
-      <c r="M30" s="71" t="s">
+      <c r="M30" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="N30" s="71"/>
+      <c r="N30" s="73"/>
       <c r="O30" s="26" t="s">
         <v>55</v>
       </c>
@@ -3727,7 +3732,7 @@
       </c>
     </row>
     <row r="31" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D31" s="81"/>
+      <c r="D31" s="83"/>
       <c r="E31" s="29" t="s">
         <v>12</v>
       </c>
@@ -3768,7 +3773,7 @@
       <c r="Q31" s="2"/>
     </row>
     <row r="32" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D32" s="81"/>
+      <c r="D32" s="83"/>
       <c r="E32" s="29" t="s">
         <v>13</v>
       </c>
@@ -3809,7 +3814,7 @@
       <c r="Q32" s="2"/>
     </row>
     <row r="33" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D33" s="81"/>
+      <c r="D33" s="83"/>
       <c r="E33" s="29" t="s">
         <v>14</v>
       </c>
@@ -3850,7 +3855,7 @@
       <c r="Q33" s="2"/>
     </row>
     <row r="34" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D34" s="81"/>
+      <c r="D34" s="83"/>
       <c r="E34" s="2" t="s">
         <v>15</v>
       </c>
@@ -3901,7 +3906,7 @@
       </c>
     </row>
     <row r="35" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D35" s="81"/>
+      <c r="D35" s="83"/>
       <c r="E35" s="2" t="s">
         <v>16</v>
       </c>
@@ -3935,43 +3940,43 @@
       <c r="Q35" s="2"/>
     </row>
     <row r="38" spans="4:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E38" s="71" t="s">
+      <c r="E38" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="F38" s="71"/>
-      <c r="G38" s="71"/>
-      <c r="H38" s="83" t="s">
+      <c r="F38" s="73"/>
+      <c r="G38" s="73"/>
+      <c r="H38" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="I38" s="84"/>
-      <c r="J38" s="84"/>
-      <c r="K38" s="84"/>
-      <c r="L38" s="84"/>
-      <c r="M38" s="84"/>
-      <c r="N38" s="84"/>
-      <c r="O38" s="84"/>
-      <c r="P38" s="84"/>
-      <c r="Q38" s="85"/>
+      <c r="I38" s="86"/>
+      <c r="J38" s="86"/>
+      <c r="K38" s="86"/>
+      <c r="L38" s="86"/>
+      <c r="M38" s="86"/>
+      <c r="N38" s="86"/>
+      <c r="O38" s="86"/>
+      <c r="P38" s="86"/>
+      <c r="Q38" s="87"/>
     </row>
     <row r="39" spans="4:17" ht="25.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="E39" s="2"/>
-      <c r="F39" s="71" t="s">
+      <c r="F39" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="G39" s="71"/>
-      <c r="H39" s="71" t="s">
+      <c r="G39" s="73"/>
+      <c r="H39" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="I39" s="71"/>
-      <c r="J39" s="71" t="s">
+      <c r="I39" s="73"/>
+      <c r="J39" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="K39" s="71"/>
+      <c r="K39" s="73"/>
       <c r="L39" s="2"/>
-      <c r="M39" s="71" t="s">
+      <c r="M39" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="N39" s="71"/>
+      <c r="N39" s="73"/>
       <c r="O39" s="19" t="s">
         <v>66</v>
       </c>
@@ -4179,11 +4184,6 @@
       <c r="O44" s="2"/>
       <c r="P44" s="2"/>
       <c r="Q44" s="2"/>
-    </row>
-    <row r="50" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G50" s="1" t="s">
-        <v>103</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="50">
@@ -4392,24 +4392,24 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H2" s="90" t="s">
+      <c r="H2" s="94" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="90"/>
+      <c r="I2" s="94"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
+      <c r="H3" s="94"/>
+      <c r="I3" s="94"/>
     </row>
     <row r="4" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="91" t="s">
+      <c r="B4" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="91"/>
-      <c r="D4" s="91"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
       <c r="E4" s="7"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="90"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="94"/>
     </row>
     <row r="5" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
@@ -4422,8 +4422,8 @@
         <v>75</v>
       </c>
       <c r="E5" s="7"/>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="94"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="37" t="s">
@@ -4437,8 +4437,8 @@
         <v>1.008</v>
       </c>
       <c r="E6" s="7"/>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="H6" s="94"/>
+      <c r="I6" s="94"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="39" t="s">
@@ -4454,14 +4454,14 @@
       <c r="E7" s="7"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H8" s="90" t="s">
+      <c r="H8" s="94" t="s">
         <v>78</v>
       </c>
-      <c r="I8" s="90"/>
+      <c r="I8" s="94"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H9" s="90"/>
-      <c r="I9" s="90"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="94"/>
     </row>
     <row r="10" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B10" s="36" t="s">
@@ -4479,8 +4479,8 @@
       <c r="F10" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="H10" s="90"/>
-      <c r="I10" s="90"/>
+      <c r="H10" s="94"/>
+      <c r="I10" s="94"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="37" t="s">
@@ -4500,8 +4500,8 @@
         <f>C11*D11</f>
         <v>1.1876860800000002</v>
       </c>
-      <c r="H11" s="90"/>
-      <c r="I11" s="90"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="94"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="37" t="s">
@@ -4523,8 +4523,8 @@
         <v>0.38300260320000001</v>
       </c>
       <c r="G12" s="43"/>
-      <c r="H12" s="90"/>
-      <c r="I12" s="90"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="94"/>
     </row>
     <row r="13" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B13" s="44" t="s">
@@ -4557,8 +4557,8 @@
       </c>
     </row>
     <row r="15" spans="2:10" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="92"/>
-      <c r="C15" s="92"/>
+      <c r="B15" s="96"/>
+      <c r="C15" s="96"/>
       <c r="H15" s="45" t="s">
         <v>91</v>
       </c>
@@ -4604,212 +4604,212 @@
       <c r="C19" s="51"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="H21" s="92" t="s">
+      <c r="H21" s="96" t="s">
+        <v>137</v>
+      </c>
+      <c r="I21" s="96"/>
+    </row>
+    <row r="22" spans="2:14" ht="306" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H22" s="97" t="s">
+        <v>136</v>
+      </c>
+      <c r="I22" s="97"/>
+      <c r="J22" s="97"/>
+      <c r="K22" s="67"/>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="H23" s="67"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="67"/>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="H24" s="67"/>
+      <c r="I24" s="67"/>
+      <c r="J24" s="67"/>
+      <c r="K24" s="67"/>
+    </row>
+    <row r="25" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H25" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="I21" s="92"/>
-    </row>
-    <row r="22" spans="2:14" ht="306" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H22" s="94" t="s">
-        <v>137</v>
-      </c>
-      <c r="I22" s="94"/>
-      <c r="J22" s="94"/>
-      <c r="K22" s="93"/>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="H23" s="93"/>
-      <c r="I23" s="93"/>
-      <c r="J23" s="93"/>
-      <c r="K23" s="93"/>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="H24" s="93"/>
-      <c r="I24" s="93"/>
-      <c r="J24" s="93"/>
-      <c r="K24" s="93"/>
-    </row>
-    <row r="25" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H25" s="95" t="s">
-        <v>139</v>
-      </c>
-      <c r="I25" s="96"/>
-      <c r="J25" s="96"/>
-      <c r="K25" s="96"/>
-      <c r="L25" s="96"/>
-      <c r="M25" s="96"/>
-      <c r="N25" s="96"/>
+      <c r="I25" s="93"/>
+      <c r="J25" s="93"/>
+      <c r="K25" s="93"/>
+      <c r="L25" s="93"/>
+      <c r="M25" s="93"/>
+      <c r="N25" s="93"/>
     </row>
     <row r="26" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H26" s="96"/>
-      <c r="I26" s="96"/>
-      <c r="J26" s="96"/>
-      <c r="K26" s="96"/>
-      <c r="L26" s="96"/>
-      <c r="M26" s="96"/>
-      <c r="N26" s="96"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="93"/>
+      <c r="J26" s="93"/>
+      <c r="K26" s="93"/>
+      <c r="L26" s="93"/>
+      <c r="M26" s="93"/>
+      <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H27" s="96"/>
-      <c r="I27" s="96"/>
-      <c r="J27" s="96"/>
-      <c r="K27" s="96"/>
-      <c r="L27" s="96"/>
-      <c r="M27" s="96"/>
-      <c r="N27" s="96"/>
+      <c r="H27" s="93"/>
+      <c r="I27" s="93"/>
+      <c r="J27" s="93"/>
+      <c r="K27" s="93"/>
+      <c r="L27" s="93"/>
+      <c r="M27" s="93"/>
+      <c r="N27" s="93"/>
     </row>
     <row r="28" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H28" s="96"/>
-      <c r="I28" s="96"/>
-      <c r="J28" s="96"/>
-      <c r="K28" s="96"/>
-      <c r="L28" s="96"/>
-      <c r="M28" s="96"/>
-      <c r="N28" s="96"/>
+      <c r="H28" s="93"/>
+      <c r="I28" s="93"/>
+      <c r="J28" s="93"/>
+      <c r="K28" s="93"/>
+      <c r="L28" s="93"/>
+      <c r="M28" s="93"/>
+      <c r="N28" s="93"/>
     </row>
     <row r="29" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H29" s="96"/>
-      <c r="I29" s="96"/>
-      <c r="J29" s="96"/>
-      <c r="K29" s="96"/>
-      <c r="L29" s="96"/>
-      <c r="M29" s="96"/>
-      <c r="N29" s="96"/>
+      <c r="H29" s="93"/>
+      <c r="I29" s="93"/>
+      <c r="J29" s="93"/>
+      <c r="K29" s="93"/>
+      <c r="L29" s="93"/>
+      <c r="M29" s="93"/>
+      <c r="N29" s="93"/>
     </row>
     <row r="30" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H30" s="96"/>
-      <c r="I30" s="96"/>
-      <c r="J30" s="96"/>
-      <c r="K30" s="96"/>
-      <c r="L30" s="96"/>
-      <c r="M30" s="96"/>
-      <c r="N30" s="96"/>
+      <c r="H30" s="93"/>
+      <c r="I30" s="93"/>
+      <c r="J30" s="93"/>
+      <c r="K30" s="93"/>
+      <c r="L30" s="93"/>
+      <c r="M30" s="93"/>
+      <c r="N30" s="93"/>
     </row>
     <row r="31" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H31" s="96"/>
-      <c r="I31" s="96"/>
-      <c r="J31" s="96"/>
-      <c r="K31" s="96"/>
-      <c r="L31" s="96"/>
-      <c r="M31" s="96"/>
-      <c r="N31" s="96"/>
+      <c r="H31" s="93"/>
+      <c r="I31" s="93"/>
+      <c r="J31" s="93"/>
+      <c r="K31" s="93"/>
+      <c r="L31" s="93"/>
+      <c r="M31" s="93"/>
+      <c r="N31" s="93"/>
     </row>
     <row r="32" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H32" s="96"/>
-      <c r="I32" s="96"/>
-      <c r="J32" s="96"/>
-      <c r="K32" s="96"/>
-      <c r="L32" s="96"/>
-      <c r="M32" s="96"/>
-      <c r="N32" s="96"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="93"/>
+      <c r="J32" s="93"/>
+      <c r="K32" s="93"/>
+      <c r="L32" s="93"/>
+      <c r="M32" s="93"/>
+      <c r="N32" s="93"/>
     </row>
     <row r="33" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H33" s="96"/>
-      <c r="I33" s="96"/>
-      <c r="J33" s="96"/>
-      <c r="K33" s="96"/>
-      <c r="L33" s="96"/>
-      <c r="M33" s="96"/>
-      <c r="N33" s="96"/>
+      <c r="H33" s="93"/>
+      <c r="I33" s="93"/>
+      <c r="J33" s="93"/>
+      <c r="K33" s="93"/>
+      <c r="L33" s="93"/>
+      <c r="M33" s="93"/>
+      <c r="N33" s="93"/>
     </row>
     <row r="34" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H34" s="96"/>
-      <c r="I34" s="96"/>
-      <c r="J34" s="96"/>
-      <c r="K34" s="96"/>
-      <c r="L34" s="96"/>
-      <c r="M34" s="96"/>
-      <c r="N34" s="96"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="93"/>
+      <c r="J34" s="93"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="93"/>
+      <c r="M34" s="93"/>
+      <c r="N34" s="93"/>
     </row>
     <row r="35" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H35" s="96"/>
-      <c r="I35" s="96"/>
-      <c r="J35" s="96"/>
-      <c r="K35" s="96"/>
-      <c r="L35" s="96"/>
-      <c r="M35" s="96"/>
-      <c r="N35" s="96"/>
+      <c r="H35" s="93"/>
+      <c r="I35" s="93"/>
+      <c r="J35" s="93"/>
+      <c r="K35" s="93"/>
+      <c r="L35" s="93"/>
+      <c r="M35" s="93"/>
+      <c r="N35" s="93"/>
     </row>
     <row r="36" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H36" s="96"/>
-      <c r="I36" s="96"/>
-      <c r="J36" s="96"/>
-      <c r="K36" s="96"/>
-      <c r="L36" s="96"/>
-      <c r="M36" s="96"/>
-      <c r="N36" s="96"/>
+      <c r="H36" s="93"/>
+      <c r="I36" s="93"/>
+      <c r="J36" s="93"/>
+      <c r="K36" s="93"/>
+      <c r="L36" s="93"/>
+      <c r="M36" s="93"/>
+      <c r="N36" s="93"/>
     </row>
     <row r="37" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H37" s="96"/>
-      <c r="I37" s="96"/>
-      <c r="J37" s="96"/>
-      <c r="K37" s="96"/>
-      <c r="L37" s="96"/>
-      <c r="M37" s="96"/>
-      <c r="N37" s="96"/>
+      <c r="H37" s="93"/>
+      <c r="I37" s="93"/>
+      <c r="J37" s="93"/>
+      <c r="K37" s="93"/>
+      <c r="L37" s="93"/>
+      <c r="M37" s="93"/>
+      <c r="N37" s="93"/>
     </row>
     <row r="38" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H38" s="96"/>
-      <c r="I38" s="96"/>
-      <c r="J38" s="96"/>
-      <c r="K38" s="96"/>
-      <c r="L38" s="96"/>
-      <c r="M38" s="96"/>
-      <c r="N38" s="96"/>
+      <c r="H38" s="93"/>
+      <c r="I38" s="93"/>
+      <c r="J38" s="93"/>
+      <c r="K38" s="93"/>
+      <c r="L38" s="93"/>
+      <c r="M38" s="93"/>
+      <c r="N38" s="93"/>
     </row>
     <row r="39" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H39" s="96"/>
-      <c r="I39" s="96"/>
-      <c r="J39" s="96"/>
-      <c r="K39" s="96"/>
-      <c r="L39" s="96"/>
-      <c r="M39" s="96"/>
-      <c r="N39" s="96"/>
+      <c r="H39" s="93"/>
+      <c r="I39" s="93"/>
+      <c r="J39" s="93"/>
+      <c r="K39" s="93"/>
+      <c r="L39" s="93"/>
+      <c r="M39" s="93"/>
+      <c r="N39" s="93"/>
     </row>
     <row r="40" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H40" s="96"/>
-      <c r="I40" s="96"/>
-      <c r="J40" s="96"/>
-      <c r="K40" s="96"/>
-      <c r="L40" s="96"/>
-      <c r="M40" s="96"/>
-      <c r="N40" s="96"/>
+      <c r="H40" s="93"/>
+      <c r="I40" s="93"/>
+      <c r="J40" s="93"/>
+      <c r="K40" s="93"/>
+      <c r="L40" s="93"/>
+      <c r="M40" s="93"/>
+      <c r="N40" s="93"/>
     </row>
     <row r="41" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H41" s="96"/>
-      <c r="I41" s="96"/>
-      <c r="J41" s="96"/>
-      <c r="K41" s="96"/>
-      <c r="L41" s="96"/>
-      <c r="M41" s="96"/>
-      <c r="N41" s="96"/>
+      <c r="H41" s="93"/>
+      <c r="I41" s="93"/>
+      <c r="J41" s="93"/>
+      <c r="K41" s="93"/>
+      <c r="L41" s="93"/>
+      <c r="M41" s="93"/>
+      <c r="N41" s="93"/>
     </row>
     <row r="42" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H42" s="96"/>
-      <c r="I42" s="96"/>
-      <c r="J42" s="96"/>
-      <c r="K42" s="96"/>
-      <c r="L42" s="96"/>
-      <c r="M42" s="96"/>
-      <c r="N42" s="96"/>
+      <c r="H42" s="93"/>
+      <c r="I42" s="93"/>
+      <c r="J42" s="93"/>
+      <c r="K42" s="93"/>
+      <c r="L42" s="93"/>
+      <c r="M42" s="93"/>
+      <c r="N42" s="93"/>
     </row>
     <row r="43" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H43" s="96"/>
-      <c r="I43" s="96"/>
-      <c r="J43" s="96"/>
-      <c r="K43" s="96"/>
-      <c r="L43" s="96"/>
-      <c r="M43" s="96"/>
-      <c r="N43" s="96"/>
+      <c r="H43" s="93"/>
+      <c r="I43" s="93"/>
+      <c r="J43" s="93"/>
+      <c r="K43" s="93"/>
+      <c r="L43" s="93"/>
+      <c r="M43" s="93"/>
+      <c r="N43" s="93"/>
     </row>
     <row r="44" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H44" s="96"/>
-      <c r="I44" s="96"/>
-      <c r="J44" s="96"/>
-      <c r="K44" s="96"/>
-      <c r="L44" s="96"/>
-      <c r="M44" s="96"/>
-      <c r="N44" s="96"/>
+      <c r="H44" s="93"/>
+      <c r="I44" s="93"/>
+      <c r="J44" s="93"/>
+      <c r="K44" s="93"/>
+      <c r="L44" s="93"/>
+      <c r="M44" s="93"/>
+      <c r="N44" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/Color/LogicDocs/formulas y funciones .xlsx
+++ b/Color/LogicDocs/formulas y funciones .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coatsplc-my.sharepoint.com/personal/elkinduvan_quebradaguapacha_coats_com/Documents/Escritorio/Colorimetria/Color/LogicDocs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1143" documentId="8_{9F78D261-5971-4E36-A791-098E2ABB119D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B68B66F-6FCE-4FD7-8586-FF8367F09E94}"/>
+  <xr:revisionPtr revIDLastSave="1144" documentId="8_{9F78D261-5971-4E36-A791-098E2ABB119D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C0C68D5-F948-4CA4-B3FC-EEF6520EB04A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{74F1A0B1-3ED8-4C59-B930-9B261CE40F5C}"/>
+    <workbookView minimized="1" xWindow="8340" yWindow="840" windowWidth="12525" windowHeight="11940" activeTab="2" xr2:uid="{74F1A0B1-3ED8-4C59-B930-9B261CE40F5C}"/>
   </bookViews>
   <sheets>
     <sheet name="CALCULO SAMPLE COMPARISON " sheetId="3" r:id="rId1"/>
@@ -2256,10 +2256,6 @@
       <c r="I4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M4">
-        <f>-14.24-(-13.01)</f>
-        <v>-1.2300000000000004</v>
-      </c>
     </row>
     <row r="5" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">

--- a/Color/LogicDocs/formulas y funciones .xlsx
+++ b/Color/LogicDocs/formulas y funciones .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coatsplc-my.sharepoint.com/personal/elkinduvan_quebradaguapacha_coats_com/Documents/Escritorio/Colorimetria/Color/LogicDocs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1144" documentId="8_{9F78D261-5971-4E36-A791-098E2ABB119D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C0C68D5-F948-4CA4-B3FC-EEF6520EB04A}"/>
+  <xr:revisionPtr revIDLastSave="1210" documentId="8_{9F78D261-5971-4E36-A791-098E2ABB119D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9822D49A-3328-4804-A480-D0E4CEAD375C}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="8340" yWindow="840" windowWidth="12525" windowHeight="11940" activeTab="2" xr2:uid="{74F1A0B1-3ED8-4C59-B930-9B261CE40F5C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="1" activeTab="3" xr2:uid="{74F1A0B1-3ED8-4C59-B930-9B261CE40F5C}"/>
   </bookViews>
   <sheets>
     <sheet name="CALCULO SAMPLE COMPARISON " sheetId="3" r:id="rId1"/>
@@ -22,7 +22,6 @@
     <externalReference r:id="rId5"/>
   </externalReferences>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="136">
   <si>
     <t>CMC(2.1)</t>
   </si>
@@ -127,15 +126,6 @@
   </si>
   <si>
     <t>Porcentaje a corregir</t>
-  </si>
-  <si>
-    <t>Oscuro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rojo (disminui) o Verde (aumentar) </t>
-  </si>
-  <si>
-    <t>Azul (disminuir) o Amarillo (aumentar)</t>
   </si>
   <si>
     <t>L</t>
@@ -1051,11 +1041,32 @@
     <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1063,7 +1074,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1092,51 +1127,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2158,13 +2148,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
-        <v>106</v>
-      </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
+      <c r="A1" s="79" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -2179,16 +2169,16 @@
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G2" s="1"/>
-      <c r="H2" s="73" t="s">
+      <c r="H2" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="73"/>
+      <c r="I2" s="77"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -2197,7 +2187,7 @@
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B3" s="33">
         <v>82.83</v>
@@ -2222,13 +2212,14 @@
         <f>+E3/B3</f>
         <v>3.1337412706539483E-4</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>28</v>
+      <c r="I3" s="2" t="str">
+        <f>IF(C3-B3&gt;0,"Claro","Oscuro")</f>
+        <v>Oscuro</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B4" s="33">
         <v>-14.24</v>
@@ -2253,13 +2244,14 @@
         <f>+E4/B4</f>
         <v>-6.0657587425830091E-3</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>29</v>
+      <c r="I4" s="2" t="str">
+        <f>IF(B11&gt;=0,"Brillante","Opaco")</f>
+        <v>Opaco</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B5" s="68">
         <v>-3.6</v>
@@ -2284,14 +2276,15 @@
         <f>+E5/B5</f>
         <v>-1.0030864197530855E-2</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>30</v>
+      <c r="I5" s="2" t="str">
+        <f>IF(B12&gt;=0,"Azul","Amarillo")</f>
+        <v>Azul</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B7" s="15">
         <f>SQRT(B4^2+B5^2)</f>
@@ -2300,7 +2293,7 @@
     </row>
     <row r="8" spans="1:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B8" s="16">
         <f>SQRT(C4^2+C5^2)</f>
@@ -2309,7 +2302,7 @@
     </row>
     <row r="9" spans="1:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B9" s="16">
         <f>MOD(ATAN2(B4,B5)*180/PI(),360)</f>
@@ -2322,7 +2315,7 @@
     </row>
     <row r="10" spans="1:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B10" s="16">
         <f>MOD(ATAN2(C4,C5)*180/PI(),360)</f>
@@ -2331,7 +2324,7 @@
     </row>
     <row r="11" spans="1:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B11" s="16">
         <f>B8-B7</f>
@@ -2340,7 +2333,7 @@
     </row>
     <row r="12" spans="1:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B12" s="15">
         <f>SQRT(MAX(0,SQRT(D3^2+D4^2+D5^2)^2-D3^2-(B8-B7)^2))</f>
@@ -2355,62 +2348,62 @@
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="G14" s="7" t="s">
+      <c r="H14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="K14" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="L14" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="M14" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K14" s="7" t="s">
+      <c r="N14" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="O14" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="M14" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>42</v>
-      </c>
       <c r="P14" s="17" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="Q14" s="17" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="R14" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="S14" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="T14" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="U14" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="S14" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="T14" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="U14" s="17" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="15" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="69" t="s">
+      <c r="B15" s="76" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="7" t="s">
@@ -2425,39 +2418,39 @@
       <c r="F15" s="28">
         <v>-3.6</v>
       </c>
-      <c r="G15" s="69">
+      <c r="G15" s="76">
         <f>+(D15-D16)/D15</f>
         <v>2.5956778944826651E-2</v>
       </c>
-      <c r="H15" s="69">
+      <c r="H15" s="76">
         <f>+(E15-E16)/E15</f>
         <v>8.6376404494382053E-2</v>
       </c>
-      <c r="I15" s="69">
+      <c r="I15" s="76">
         <f>+(F15-F16)/F15</f>
         <v>3.611111111111108E-2</v>
       </c>
-      <c r="J15" s="69">
+      <c r="J15" s="76">
         <f>+ABS(G15)</f>
         <v>2.5956778944826651E-2</v>
       </c>
-      <c r="K15" s="69">
+      <c r="K15" s="76">
         <f>+ABS(H15)</f>
         <v>8.6376404494382053E-2</v>
       </c>
-      <c r="L15" s="69">
+      <c r="L15" s="76">
         <f>+ABS(I15)</f>
         <v>3.611111111111108E-2</v>
       </c>
-      <c r="M15" s="70">
+      <c r="M15" s="75">
         <f>+K15/F15</f>
         <v>-2.3993445692883902E-2</v>
       </c>
-      <c r="N15" s="70">
+      <c r="N15" s="75">
         <f>+K15/E15</f>
         <v>-6.0657587425830091E-3</v>
       </c>
-      <c r="O15" s="70">
+      <c r="O15" s="75">
         <f>+L15/F15</f>
         <v>-1.0030864197530855E-2</v>
       </c>
@@ -2487,7 +2480,7 @@
       </c>
     </row>
     <row r="16" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="69"/>
+      <c r="B16" s="76"/>
       <c r="C16" s="7" t="s">
         <v>26</v>
       </c>
@@ -2500,15 +2493,15 @@
       <c r="F16" s="28">
         <v>-3.47</v>
       </c>
-      <c r="G16" s="69"/>
-      <c r="H16" s="69"/>
-      <c r="I16" s="69"/>
-      <c r="J16" s="69"/>
-      <c r="K16" s="69"/>
-      <c r="L16" s="69"/>
-      <c r="M16" s="69"/>
-      <c r="N16" s="69"/>
-      <c r="O16" s="69"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="76"/>
+      <c r="I16" s="76"/>
+      <c r="J16" s="76"/>
+      <c r="K16" s="76"/>
+      <c r="L16" s="76"/>
+      <c r="M16" s="76"/>
+      <c r="N16" s="76"/>
+      <c r="O16" s="76"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
@@ -2517,7 +2510,7 @@
       <c r="U16" s="7"/>
     </row>
     <row r="17" spans="2:21" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="69" t="s">
+      <c r="B17" s="76" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="7" t="s">
@@ -2532,39 +2525,39 @@
       <c r="F17" s="28">
         <v>5.0599999999999996</v>
       </c>
-      <c r="G17" s="69">
+      <c r="G17" s="76">
         <f>+(D17-D18)/D17</f>
         <v>2.4813592470358161E-2</v>
       </c>
-      <c r="H17" s="69">
+      <c r="H17" s="76">
         <f>+(E17-E18)/E17</f>
         <v>5.7165231010180145E-2</v>
       </c>
-      <c r="I17" s="69">
+      <c r="I17" s="76">
         <f>+(F17-F18)/F17</f>
         <v>1.8557312252964429</v>
       </c>
-      <c r="J17" s="69">
+      <c r="J17" s="76">
         <f>+ABS(G17)</f>
         <v>2.4813592470358161E-2</v>
       </c>
-      <c r="K17" s="69">
+      <c r="K17" s="76">
         <f>+ABS(H17)</f>
         <v>5.7165231010180145E-2</v>
       </c>
-      <c r="L17" s="69">
+      <c r="L17" s="76">
         <f>+ABS(I17)</f>
         <v>1.8557312252964429</v>
       </c>
-      <c r="M17" s="70">
+      <c r="M17" s="75">
         <f>+J17/D17</f>
         <v>3.0330757206158365E-4</v>
       </c>
-      <c r="N17" s="70">
+      <c r="N17" s="75">
         <f>+K17/E17</f>
         <v>-4.4765255293798076E-3</v>
       </c>
-      <c r="O17" s="70">
+      <c r="O17" s="75">
         <f>+L17/F17</f>
         <v>0.36674530144198481</v>
       </c>
@@ -2594,7 +2587,7 @@
       </c>
     </row>
     <row r="18" spans="2:21" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="69"/>
+      <c r="B18" s="76"/>
       <c r="C18" s="7" t="s">
         <v>26</v>
       </c>
@@ -2607,15 +2600,15 @@
       <c r="F18" s="28">
         <v>-4.33</v>
       </c>
-      <c r="G18" s="69"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="69"/>
-      <c r="J18" s="69"/>
-      <c r="K18" s="69"/>
-      <c r="L18" s="69"/>
-      <c r="M18" s="69"/>
-      <c r="N18" s="69"/>
-      <c r="O18" s="69"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="76"/>
+      <c r="I18" s="76"/>
+      <c r="J18" s="76"/>
+      <c r="K18" s="76"/>
+      <c r="L18" s="76"/>
+      <c r="M18" s="76"/>
+      <c r="N18" s="76"/>
+      <c r="O18" s="76"/>
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
       <c r="R18" s="7"/>
@@ -2624,8 +2617,8 @@
       <c r="U18" s="7"/>
     </row>
     <row r="19" spans="2:21" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="69" t="s">
-        <v>32</v>
+      <c r="B19" s="76" t="s">
+        <v>29</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>25</v>
@@ -2639,39 +2632,39 @@
       <c r="F19" s="28">
         <v>7.39</v>
       </c>
-      <c r="G19" s="69">
+      <c r="G19" s="76">
         <f>+(D19-D20)/D19</f>
         <v>4.9419322955275513E-2</v>
       </c>
-      <c r="H19" s="69">
+      <c r="H19" s="76">
         <f>+(E19-E20)/E19</f>
         <v>5.7884231536926095E-2</v>
       </c>
-      <c r="I19" s="69">
+      <c r="I19" s="76">
         <f>+(F19-F20)/F19</f>
         <v>7.9837618403247615E-2</v>
       </c>
-      <c r="J19" s="69">
+      <c r="J19" s="76">
         <f>+ABS(G19)</f>
         <v>4.9419322955275513E-2</v>
       </c>
-      <c r="K19" s="69">
+      <c r="K19" s="76">
         <f>+ABS(H19)</f>
         <v>5.7884231536926095E-2</v>
       </c>
-      <c r="L19" s="69">
+      <c r="L19" s="76">
         <f>+ABS(I19)</f>
         <v>7.9837618403247615E-2</v>
       </c>
-      <c r="M19" s="70">
+      <c r="M19" s="75">
         <f>+J19/D19</f>
         <v>6.1056737033945529E-4</v>
       </c>
-      <c r="N19" s="70">
+      <c r="N19" s="75">
         <f>+K19/E19</f>
         <v>-3.8512462765752562E-3</v>
       </c>
-      <c r="O19" s="70">
+      <c r="O19" s="75">
         <f>+L19/F19</f>
         <v>1.0803466631021328E-2</v>
       </c>
@@ -2701,7 +2694,7 @@
       </c>
     </row>
     <row r="20" spans="2:21" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="69"/>
+      <c r="B20" s="76"/>
       <c r="C20" s="7" t="s">
         <v>26</v>
       </c>
@@ -2714,15 +2707,15 @@
       <c r="F20" s="28">
         <v>6.8</v>
       </c>
-      <c r="G20" s="69"/>
-      <c r="H20" s="69"/>
-      <c r="I20" s="69"/>
-      <c r="J20" s="69"/>
-      <c r="K20" s="69"/>
-      <c r="L20" s="69"/>
-      <c r="M20" s="69"/>
-      <c r="N20" s="69"/>
-      <c r="O20" s="69"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="76"/>
+      <c r="I20" s="76"/>
+      <c r="J20" s="76"/>
+      <c r="K20" s="76"/>
+      <c r="L20" s="76"/>
+      <c r="M20" s="76"/>
+      <c r="N20" s="76"/>
+      <c r="O20" s="76"/>
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
       <c r="R20" s="7"/>
@@ -2733,24 +2726,24 @@
     <row r="21" spans="2:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="2:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="2:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="2:21" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2760,164 +2753,182 @@
     </row>
     <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="38" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F38" s="58" t="s">
-        <v>111</v>
-      </c>
-      <c r="I38" s="71" t="s">
-        <v>112</v>
+        <v>108</v>
+      </c>
+      <c r="I38" s="78" t="s">
+        <v>109</v>
       </c>
       <c r="L38" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="M38" s="59"/>
       <c r="N38" s="59"/>
       <c r="O38" s="60" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P38" s="61" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Q38" s="61" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="R38" s="61" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D39" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F39" s="58" t="s">
-        <v>117</v>
-      </c>
-      <c r="I39" s="71"/>
+        <v>114</v>
+      </c>
+      <c r="I39" s="78"/>
       <c r="L39" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="M39" s="62"/>
       <c r="N39" s="62"/>
       <c r="O39" s="63" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="P39" s="64" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q39" s="64" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="R39" s="63" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>119</v>
+      </c>
+      <c r="B40" t="s">
+        <v>120</v>
+      </c>
+      <c r="C40" t="s">
+        <v>120</v>
+      </c>
+      <c r="D40" t="s">
+        <v>120</v>
+      </c>
+      <c r="F40" s="58" t="s">
+        <v>121</v>
+      </c>
+      <c r="I40" s="78" t="s">
         <v>122</v>
       </c>
-      <c r="B40" t="s">
+      <c r="L40" t="s">
         <v>123</v>
-      </c>
-      <c r="C40" t="s">
-        <v>123</v>
-      </c>
-      <c r="D40" t="s">
-        <v>123</v>
-      </c>
-      <c r="F40" s="58" t="s">
-        <v>124</v>
-      </c>
-      <c r="I40" s="71" t="s">
-        <v>125</v>
-      </c>
-      <c r="L40" t="s">
-        <v>126</v>
       </c>
       <c r="M40" s="62"/>
       <c r="N40" s="62"/>
       <c r="O40" s="63" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="P40" s="64" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="Q40" s="64" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R40" s="65"/>
     </row>
     <row r="41" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C41" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D41" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F41" s="58" t="s">
-        <v>129</v>
-      </c>
-      <c r="I41" s="71"/>
+        <v>126</v>
+      </c>
+      <c r="I41" s="78"/>
       <c r="L41" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="M41" s="62"/>
       <c r="N41" s="62"/>
       <c r="O41" s="66" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="P41" s="64" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Q41" s="64" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="R41" s="64" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B42" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C42" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D42" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D44" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="I19:I20"/>
     <mergeCell ref="N19:N20"/>
     <mergeCell ref="O19:O20"/>
     <mergeCell ref="H2:I2"/>
@@ -2932,26 +2943,8 @@
     <mergeCell ref="O15:O16"/>
     <mergeCell ref="K17:K18"/>
     <mergeCell ref="K15:K16"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I15:I16"/>
     <mergeCell ref="M19:M20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="G19:G20"/>
     <mergeCell ref="J19:J20"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="J15:J16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2981,13 +2974,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E2" s="73" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
+      <c r="E2" s="77" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="3" spans="4:15" x14ac:dyDescent="0.2">
       <c r="E3" s="2"/>
@@ -2998,13 +2991,13 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="M3" s="19" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N3" s="19" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3028,39 +3021,39 @@
         <v>5</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="4:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E5" s="82" t="s">
+      <c r="E5" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="79">
+      <c r="F5" s="94">
         <v>-0.78</v>
       </c>
-      <c r="G5" s="79">
+      <c r="G5" s="94">
         <v>-0.86</v>
       </c>
-      <c r="H5" s="81">
+      <c r="H5" s="96">
         <v>0.17</v>
       </c>
-      <c r="I5" s="77">
+      <c r="I5" s="92">
         <v>1.17</v>
       </c>
-      <c r="J5" s="89">
-        <f>+ABS(F5*10)</f>
-        <v>7.8000000000000007</v>
-      </c>
-      <c r="K5" s="88">
-        <f>+ABS(G5*10)</f>
-        <v>8.6</v>
-      </c>
-      <c r="L5" s="88">
-        <f>+ABS(H5*10)</f>
-        <v>1.7000000000000002</v>
+      <c r="J5" s="81">
+        <f>+ABS(F5)</f>
+        <v>0.78</v>
+      </c>
+      <c r="K5" s="80">
+        <f>+ABS(G5)</f>
+        <v>0.86</v>
+      </c>
+      <c r="L5" s="80">
+        <f>+ABS(H5)</f>
+        <v>0.17</v>
       </c>
       <c r="M5" s="20">
         <f>MOD(ATAN2('[1]CALCULO SAMPLE COMPARISON '!E14,'[1]CALCULO SAMPLE COMPARISON '!F14)*180/PI(),360)</f>
@@ -3076,45 +3069,45 @@
       </c>
     </row>
     <row r="6" spans="4:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E6" s="82"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="78"/>
-      <c r="J6" s="89"/>
-      <c r="K6" s="88"/>
-      <c r="L6" s="88"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="81"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="80"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
     <row r="7" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E7" s="73" t="s">
+      <c r="E7" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="74">
+      <c r="F7" s="89">
         <v>-0.74</v>
       </c>
-      <c r="G7" s="76">
+      <c r="G7" s="91">
         <v>-0.54</v>
       </c>
-      <c r="H7" s="76">
+      <c r="H7" s="91">
         <v>0.1</v>
       </c>
-      <c r="I7" s="75">
+      <c r="I7" s="90">
         <v>0.92</v>
       </c>
-      <c r="J7" s="90">
-        <f>+ABS(F7*10)</f>
-        <v>7.4</v>
-      </c>
-      <c r="K7" s="91">
-        <f>+ABS(G7*10)</f>
-        <v>5.4</v>
-      </c>
-      <c r="L7" s="91">
-        <f>+ABS(H7*10)</f>
-        <v>1</v>
+      <c r="J7" s="82">
+        <f>+ABS(F7)</f>
+        <v>0.74</v>
+      </c>
+      <c r="K7" s="83">
+        <f>+ABS(G7)</f>
+        <v>0.54</v>
+      </c>
+      <c r="L7" s="83">
+        <f>+ABS(H7)</f>
+        <v>0.1</v>
       </c>
       <c r="M7" s="20">
         <f>MOD(ATAN2('[1]CALCULO SAMPLE COMPARISON '!E16,'[1]CALCULO SAMPLE COMPARISON '!F16)*180/PI(),360)</f>
@@ -3130,45 +3123,45 @@
       </c>
     </row>
     <row r="8" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E8" s="73"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
-      <c r="J8" s="90"/>
-      <c r="K8" s="91"/>
-      <c r="L8" s="91"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="90"/>
+      <c r="G8" s="90"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="90"/>
+      <c r="J8" s="82"/>
+      <c r="K8" s="83"/>
+      <c r="L8" s="83"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E9" s="73" t="s">
+      <c r="E9" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="74">
+      <c r="F9" s="89">
         <v>-0.73</v>
       </c>
-      <c r="G9" s="76">
+      <c r="G9" s="91">
         <v>-0.68</v>
       </c>
-      <c r="H9" s="76">
+      <c r="H9" s="91">
         <v>-0.12</v>
       </c>
-      <c r="I9" s="75">
+      <c r="I9" s="90">
         <v>1.01</v>
       </c>
-      <c r="J9" s="90">
-        <f>+ABS(F9*10)</f>
-        <v>7.3</v>
-      </c>
-      <c r="K9" s="91">
-        <f>+ABS(G9*10)</f>
-        <v>6.8000000000000007</v>
-      </c>
-      <c r="L9" s="91">
-        <f>+ABS(H9*10)</f>
-        <v>1.2</v>
+      <c r="J9" s="82">
+        <f>+ABS(F9)</f>
+        <v>0.73</v>
+      </c>
+      <c r="K9" s="83">
+        <f>+ABS(G9)</f>
+        <v>0.68</v>
+      </c>
+      <c r="L9" s="83">
+        <f>+ABS(H9)</f>
+        <v>0.12</v>
       </c>
       <c r="M9" s="20">
         <f>MOD(ATAN2('[1]CALCULO SAMPLE COMPARISON '!E18,'[1]CALCULO SAMPLE COMPARISON '!F18)*180/PI(),360)</f>
@@ -3184,14 +3177,14 @@
       </c>
     </row>
     <row r="10" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E10" s="73"/>
-      <c r="F10" s="75"/>
-      <c r="G10" s="75"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="75"/>
-      <c r="J10" s="90"/>
-      <c r="K10" s="91"/>
-      <c r="L10" s="91"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="90"/>
+      <c r="G10" s="90"/>
+      <c r="H10" s="90"/>
+      <c r="I10" s="90"/>
+      <c r="J10" s="82"/>
+      <c r="K10" s="83"/>
+      <c r="L10" s="83"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3202,64 +3195,64 @@
       <c r="H11" s="9"/>
     </row>
     <row r="12" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E12" s="85" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="86"/>
-      <c r="G12" s="86"/>
-      <c r="H12" s="86"/>
-      <c r="I12" s="86"/>
-      <c r="J12" s="86"/>
-      <c r="K12" s="86"/>
-      <c r="L12" s="86"/>
-      <c r="M12" s="86"/>
-      <c r="N12" s="86"/>
-      <c r="O12" s="87"/>
+      <c r="E12" s="84" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="85"/>
+      <c r="G12" s="85"/>
+      <c r="H12" s="85"/>
+      <c r="I12" s="85"/>
+      <c r="J12" s="85"/>
+      <c r="K12" s="85"/>
+      <c r="L12" s="85"/>
+      <c r="M12" s="85"/>
+      <c r="N12" s="85"/>
+      <c r="O12" s="86"/>
     </row>
     <row r="13" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="E13" s="73" t="s">
-        <v>47</v>
-      </c>
-      <c r="F13" s="73"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="73"/>
-      <c r="I13" s="73"/>
-      <c r="J13" s="85" t="s">
+      <c r="E13" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="86"/>
-      <c r="L13" s="86"/>
-      <c r="M13" s="86"/>
-      <c r="N13" s="86"/>
-      <c r="O13" s="87"/>
+      <c r="K13" s="85"/>
+      <c r="L13" s="85"/>
+      <c r="M13" s="85"/>
+      <c r="N13" s="85"/>
+      <c r="O13" s="86"/>
     </row>
     <row r="14" spans="4:15" x14ac:dyDescent="0.2">
       <c r="E14" s="2"/>
-      <c r="F14" s="73" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73" t="s">
-        <v>43</v>
-      </c>
-      <c r="I14" s="73"/>
-      <c r="J14" s="73" t="s">
+      <c r="F14" s="77" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="I14" s="77"/>
+      <c r="J14" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="K14" s="73"/>
+      <c r="K14" s="77"/>
       <c r="L14" s="2"/>
       <c r="M14" s="26" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N14" s="26" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O14" s="26" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D15" s="83"/>
+      <c r="D15" s="88"/>
       <c r="E15" s="29" t="s">
         <v>12</v>
       </c>
@@ -3272,7 +3265,7 @@
       </c>
       <c r="H15" s="4">
         <f>+F15*(1-$J$5/100)</f>
-        <v>1.08635572</v>
+        <v>1.1690695719999999</v>
       </c>
       <c r="I15" s="23">
         <f>H15/$H$18</f>
@@ -3280,23 +3273,23 @@
       </c>
       <c r="J15" s="4">
         <f>+$H$15*(1-$K$5/100)</f>
-        <v>0.99292912808000011</v>
+        <v>1.1590155736807999</v>
       </c>
       <c r="K15" s="23">
         <f>+$J$15/$J$18</f>
-        <v>0.60805259681281487</v>
+        <v>0.60805259681281476</v>
       </c>
       <c r="L15" s="23"/>
       <c r="M15" s="26" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N15" s="26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="O15" s="26"/>
     </row>
     <row r="16" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D16" s="83"/>
+      <c r="D16" s="88"/>
       <c r="E16" s="29" t="s">
         <v>13</v>
       </c>
@@ -3309,7 +3302,7 @@
       </c>
       <c r="H16" s="4">
         <f>+$F$16*(1-$J$5/100)</f>
-        <v>0.35450899999999996</v>
+        <v>0.38150089999999998</v>
       </c>
       <c r="I16" s="23">
         <f>H16/$H$18</f>
@@ -3317,7 +3310,7 @@
       </c>
       <c r="J16" s="4">
         <f>+$H$16*(1-$K$5/100)</f>
-        <v>0.324021226</v>
+        <v>0.37821999225999997</v>
       </c>
       <c r="K16" s="23">
         <f>+$J$16/$J$18</f>
@@ -3329,7 +3322,7 @@
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D17" s="83"/>
+      <c r="D17" s="88"/>
       <c r="E17" s="29" t="s">
         <v>14</v>
       </c>
@@ -3342,7 +3335,7 @@
       </c>
       <c r="H17" s="4">
         <f>+$F$17*(1-$J$5/100)</f>
-        <v>0.34575</v>
+        <v>0.37207499999999999</v>
       </c>
       <c r="I17" s="23">
         <f>H17/$H$18</f>
@@ -3350,7 +3343,7 @@
       </c>
       <c r="J17" s="4">
         <f>+$H$17*(1-$K$5/100)</f>
-        <v>0.3160155</v>
+        <v>0.36887515499999995</v>
       </c>
       <c r="K17" s="23">
         <f>+$J$17/$J$18</f>
@@ -3362,7 +3355,7 @@
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D18" s="83"/>
+      <c r="D18" s="88"/>
       <c r="E18" s="2" t="s">
         <v>15</v>
       </c>
@@ -3376,7 +3369,7 @@
       </c>
       <c r="H18" s="24">
         <f>SUM($H$15:$H$17)</f>
-        <v>1.78661472</v>
+        <v>1.9226454719999999</v>
       </c>
       <c r="I18" s="3">
         <f>SUM(I15:I17)</f>
@@ -3384,7 +3377,7 @@
       </c>
       <c r="J18" s="24">
         <f>SUM($J$15:$J$17)</f>
-        <v>1.6329658540800001</v>
+        <v>1.9061107209407999</v>
       </c>
       <c r="K18" s="3">
         <f>SUM($K$15:$K$17)</f>
@@ -3405,7 +3398,7 @@
       </c>
     </row>
     <row r="19" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D19" s="83"/>
+      <c r="D19" s="88"/>
       <c r="E19" s="2" t="s">
         <v>16</v>
       </c>
@@ -3413,12 +3406,12 @@
       <c r="G19" s="2"/>
       <c r="H19" s="53">
         <f>+H18/F18-1</f>
-        <v>-7.8000000000000069E-2</v>
+        <v>-7.8000000000001402E-3</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="23">
         <f>+$J$18/$I$18-1</f>
-        <v>0.63296585408000006</v>
+        <v>0.90611072094079992</v>
       </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
@@ -3428,53 +3421,53 @@
       <c r="P19" s="27"/>
     </row>
     <row r="21" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E21" s="84" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" s="72"/>
-      <c r="G21" s="72"/>
-      <c r="H21" s="72"/>
-      <c r="I21" s="72"/>
-      <c r="J21" s="72"/>
-      <c r="K21" s="72"/>
-      <c r="L21" s="72"/>
-      <c r="M21" s="72"/>
-      <c r="N21" s="72"/>
-      <c r="O21" s="72"/>
-      <c r="P21" s="72"/>
-      <c r="Q21" s="72"/>
+      <c r="E21" s="87" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" s="79"/>
+      <c r="G21" s="79"/>
+      <c r="H21" s="79"/>
+      <c r="I21" s="79"/>
+      <c r="J21" s="79"/>
+      <c r="K21" s="79"/>
+      <c r="L21" s="79"/>
+      <c r="M21" s="79"/>
+      <c r="N21" s="79"/>
+      <c r="O21" s="79"/>
+      <c r="P21" s="79"/>
+      <c r="Q21" s="79"/>
     </row>
     <row r="22" spans="4:17" x14ac:dyDescent="0.2">
       <c r="E22" s="2"/>
-      <c r="F22" s="73" t="s">
+      <c r="F22" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="G22" s="73"/>
-      <c r="H22" s="73" t="s">
+      <c r="G22" s="77"/>
+      <c r="H22" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="I22" s="73"/>
-      <c r="J22" s="73" t="s">
+      <c r="I22" s="77"/>
+      <c r="J22" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="K22" s="73"/>
+      <c r="K22" s="77"/>
       <c r="L22" s="2"/>
-      <c r="M22" s="73" t="s">
-        <v>70</v>
-      </c>
-      <c r="N22" s="73"/>
+      <c r="M22" s="77" t="s">
+        <v>67</v>
+      </c>
+      <c r="N22" s="77"/>
       <c r="O22" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="P22" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q22" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="P22" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q22" s="26" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="23" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="83"/>
+      <c r="D23" s="88"/>
       <c r="E23" s="29" t="s">
         <v>12</v>
       </c>
@@ -3487,7 +3480,7 @@
       </c>
       <c r="H23" s="4">
         <f>+$F$23*(1-$J$7/100)</f>
-        <v>1.09106876</v>
+        <v>1.1695408760000001</v>
       </c>
       <c r="I23" s="23">
         <f>H23/$H$26</f>
@@ -3495,7 +3488,7 @@
       </c>
       <c r="J23" s="4">
         <f>+$H$23*(1-$K$7/100)</f>
-        <v>1.0321510469599999</v>
+        <v>1.1632253552696001</v>
       </c>
       <c r="K23" s="23">
         <f>+$J$23/$J$26</f>
@@ -3504,18 +3497,18 @@
       <c r="L23" s="23"/>
       <c r="M23" s="4">
         <f>+$H$15*(1-$K$7/100)</f>
-        <v>1.0276925111199999</v>
+        <v>1.1627565963112001</v>
       </c>
       <c r="N23" s="23">
-        <f>+M23/$J$26</f>
-        <v>0.60542601972075083</v>
+        <f>M23/M$26</f>
+        <v>0.60805259681281487</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
       <c r="Q23" s="2"/>
     </row>
     <row r="24" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="83"/>
+      <c r="D24" s="88"/>
       <c r="E24" s="29" t="s">
         <v>13</v>
       </c>
@@ -3528,15 +3521,15 @@
       </c>
       <c r="H24" s="4">
         <f>+$F$24*(1-$J$7/100)</f>
-        <v>0.356047</v>
+        <v>0.38165470000000001</v>
       </c>
       <c r="I24" s="23">
         <f>H24/$H$26</f>
-        <v>0.19842498555032614</v>
+        <v>0.19842498555032612</v>
       </c>
       <c r="J24" s="4">
         <f>+$H$24*(1-$K$7/100)</f>
-        <v>0.33682046199999999</v>
+        <v>0.37959376462000005</v>
       </c>
       <c r="K24" s="23">
         <f>+$J$24/$J$26</f>
@@ -3545,18 +3538,18 @@
       <c r="L24" s="23"/>
       <c r="M24" s="4">
         <f>$H$16*(1-$K$7/100)</f>
-        <v>0.33536551399999998</v>
+        <v>0.37944079514000001</v>
       </c>
       <c r="N24" s="23">
-        <f>+M24/$J$26</f>
-        <v>0.19756785818293812</v>
+        <f>M24/M$26</f>
+        <v>0.19842498555032614</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
       <c r="Q24" s="2"/>
     </row>
     <row r="25" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="83"/>
+      <c r="D25" s="88"/>
       <c r="E25" s="29" t="s">
         <v>14</v>
       </c>
@@ -3569,35 +3562,35 @@
       </c>
       <c r="H25" s="4">
         <f>+$F$25*(1-$J$7/100)</f>
-        <v>0.34724999999999995</v>
+        <v>0.37222500000000003</v>
       </c>
       <c r="I25" s="23">
         <f>H25/$H$26</f>
-        <v>0.19352241763685901</v>
+        <v>0.19352241763685904</v>
       </c>
       <c r="J25" s="4">
         <f>+$H$25*(1-$K$7/100)</f>
-        <v>0.32849849999999992</v>
+        <v>0.37021498500000005</v>
       </c>
       <c r="K25" s="23">
         <f>+$J$25/$J$26</f>
-        <v>0.19352241763685901</v>
+        <v>0.19352241763685907</v>
       </c>
       <c r="L25" s="23"/>
       <c r="M25" s="4">
         <f>+$H$17*(1-$K$7/100)</f>
-        <v>0.32707949999999997</v>
+        <v>0.37006579500000003</v>
       </c>
       <c r="N25" s="23">
-        <f>+M25/$J$26</f>
-        <v>0.19268646766866526</v>
+        <f>M25/M$26</f>
+        <v>0.19352241763685907</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
     </row>
     <row r="26" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D26" s="83"/>
+      <c r="D26" s="88"/>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
@@ -3611,7 +3604,7 @@
       </c>
       <c r="H26" s="4">
         <f>+$F$26*(1-$J$7/100)</f>
-        <v>1.79436576</v>
+        <v>1.9234205760000003</v>
       </c>
       <c r="I26" s="3">
         <f>SUM(I23:I25)</f>
@@ -3619,7 +3612,7 @@
       </c>
       <c r="J26" s="24">
         <f>SUM(J23:J25)</f>
-        <v>1.6974700089599999</v>
+        <v>1.9130341048896002</v>
       </c>
       <c r="K26" s="3">
         <f>SUM(K23:K25)</f>
@@ -3628,11 +3621,11 @@
       <c r="L26" s="3"/>
       <c r="M26" s="24">
         <f>SUM(M23:M25)</f>
-        <v>1.6901375251199999</v>
+        <v>1.9122631864512001</v>
       </c>
       <c r="N26" s="3">
         <f>SUM(N23:N25)</f>
-        <v>0.99568034557235419</v>
+        <v>1</v>
       </c>
       <c r="O26" s="26">
         <f>M7</f>
@@ -3648,7 +3641,7 @@
       </c>
     </row>
     <row r="27" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D27" s="83"/>
+      <c r="D27" s="88"/>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
@@ -3658,22 +3651,22 @@
       </c>
       <c r="H27" s="23">
         <f>+$H$26/$F$26-1</f>
-        <v>-7.4000000000000066E-2</v>
+        <v>-7.3999999999999622E-3</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="23">
         <f>+J26/I26-1</f>
-        <v>0.69747000895999989</v>
+        <v>0.91303410488960024</v>
       </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="23">
         <f>+M26/K26-1</f>
-        <v>0.69013752511999993</v>
+        <v>0.91226318645120008</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="26" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="P27" s="26">
         <f>O7</f>
@@ -3682,53 +3675,53 @@
       <c r="Q27" s="2"/>
     </row>
     <row r="29" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E29" s="84" t="s">
-        <v>51</v>
-      </c>
-      <c r="F29" s="72"/>
-      <c r="G29" s="72"/>
-      <c r="H29" s="72"/>
-      <c r="I29" s="72"/>
-      <c r="J29" s="72"/>
-      <c r="K29" s="72"/>
-      <c r="L29" s="72"/>
-      <c r="M29" s="72"/>
-      <c r="N29" s="72"/>
-      <c r="O29" s="72"/>
-      <c r="P29" s="72"/>
-      <c r="Q29" s="72"/>
+      <c r="E29" s="87" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" s="79"/>
+      <c r="G29" s="79"/>
+      <c r="H29" s="79"/>
+      <c r="I29" s="79"/>
+      <c r="J29" s="79"/>
+      <c r="K29" s="79"/>
+      <c r="L29" s="79"/>
+      <c r="M29" s="79"/>
+      <c r="N29" s="79"/>
+      <c r="O29" s="79"/>
+      <c r="P29" s="79"/>
+      <c r="Q29" s="79"/>
     </row>
     <row r="30" spans="4:17" ht="25.5" x14ac:dyDescent="0.2">
       <c r="E30" s="2"/>
-      <c r="F30" s="73" t="s">
+      <c r="F30" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73" t="s">
+      <c r="G30" s="77"/>
+      <c r="H30" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="I30" s="73"/>
-      <c r="J30" s="73" t="s">
+      <c r="I30" s="77"/>
+      <c r="J30" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="K30" s="73"/>
+      <c r="K30" s="77"/>
       <c r="L30" s="2"/>
-      <c r="M30" s="73" t="s">
+      <c r="M30" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="N30" s="73"/>
+      <c r="N30" s="77"/>
       <c r="O30" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="P30" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q30" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="P30" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q30" s="19" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="31" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D31" s="83"/>
+      <c r="D31" s="88"/>
       <c r="E31" s="29" t="s">
         <v>12</v>
       </c>
@@ -3741,15 +3734,15 @@
       </c>
       <c r="H31" s="4">
         <f>+$F$31*(1-$J$9/100)</f>
-        <v>1.0922470200000001</v>
+        <v>1.1696587020000002</v>
       </c>
       <c r="I31" s="23">
         <f>$H$31/$H$34</f>
-        <v>0.60805259681281476</v>
+        <v>0.60805259681281487</v>
       </c>
       <c r="J31" s="4">
         <f>+$H$31*(1-$K$9/100)</f>
-        <v>1.0179742226399999</v>
+        <v>1.1617050228264001</v>
       </c>
       <c r="K31" s="23">
         <f>+$J$31/$J$34</f>
@@ -3758,18 +3751,18 @@
       <c r="L31" s="23"/>
       <c r="M31" s="4">
         <f>+$H$15*(1-$K$9/100)</f>
-        <v>1.01248353104</v>
+        <v>1.1611198989103999</v>
       </c>
       <c r="N31" s="23">
-        <f>+M31/$J$34</f>
-        <v>0.60477291721835513</v>
+        <f>M31/M$34</f>
+        <v>0.60805259681281476</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
       <c r="Q31" s="2"/>
     </row>
     <row r="32" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D32" s="83"/>
+      <c r="D32" s="88"/>
       <c r="E32" s="29" t="s">
         <v>13</v>
       </c>
@@ -3782,7 +3775,7 @@
       </c>
       <c r="H32" s="4">
         <f>+$F$32*(1-$J$9/100)</f>
-        <v>0.35643150000000001</v>
+        <v>0.38169315000000004</v>
       </c>
       <c r="I32" s="23">
         <f>$H$32/$H$34</f>
@@ -3790,27 +3783,27 @@
       </c>
       <c r="J32" s="4">
         <f>+$H$32*(1-$K$9/100)</f>
-        <v>0.33219415800000002</v>
+        <v>0.37909763658000001</v>
       </c>
       <c r="K32" s="23">
         <f>+$J$32/$J$34</f>
-        <v>0.19842498555032617</v>
+        <v>0.19842498555032614</v>
       </c>
       <c r="L32" s="23"/>
       <c r="M32" s="4">
         <f>+$H$16*(1-$K$9/100)</f>
-        <v>0.33040238799999994</v>
+        <v>0.37890669387999998</v>
       </c>
       <c r="N32" s="23">
-        <f>+M32/$J$34</f>
-        <v>0.19735473212233082</v>
+        <f>M32/M$34</f>
+        <v>0.19842498555032614</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
       <c r="Q32" s="2"/>
     </row>
     <row r="33" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D33" s="83"/>
+      <c r="D33" s="88"/>
       <c r="E33" s="29" t="s">
         <v>14</v>
       </c>
@@ -3823,7 +3816,7 @@
       </c>
       <c r="H33" s="4">
         <f>+$F$33*(1-$J$9/100)</f>
-        <v>0.34762500000000002</v>
+        <v>0.3722625</v>
       </c>
       <c r="I33" s="23">
         <f>$H$33/$H$34</f>
@@ -3831,27 +3824,27 @@
       </c>
       <c r="J33" s="4">
         <f>+$H$33*(1-$K$9/100)</f>
-        <v>0.32398650000000001</v>
+        <v>0.369731115</v>
       </c>
       <c r="K33" s="23">
         <f>+$J$33/$J$34</f>
-        <v>0.19352241763685907</v>
+        <v>0.19352241763685904</v>
       </c>
       <c r="L33" s="23"/>
       <c r="M33" s="4">
         <f>+$H$17*(1-$K$9/100)</f>
-        <v>0.322239</v>
+        <v>0.36954488999999996</v>
       </c>
       <c r="N33" s="23">
-        <f>+M33/$J$34</f>
-        <v>0.19247860740149306</v>
+        <f>M33/M$34</f>
+        <v>0.19352241763685904</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
       <c r="Q33" s="2"/>
     </row>
     <row r="34" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D34" s="83"/>
+      <c r="D34" s="88"/>
       <c r="E34" s="2" t="s">
         <v>15</v>
       </c>
@@ -3865,7 +3858,7 @@
       </c>
       <c r="H34" s="24">
         <f>SUM(H31:H33)</f>
-        <v>1.7963035200000002</v>
+        <v>1.9236143520000002</v>
       </c>
       <c r="I34" s="3">
         <f>SUM(I31:I33)</f>
@@ -3873,7 +3866,7 @@
       </c>
       <c r="J34" s="24">
         <f>SUM(J31:J33)</f>
-        <v>1.67415488064</v>
+        <v>1.9105337744064002</v>
       </c>
       <c r="K34" s="3">
         <f>+J34/$J$34</f>
@@ -3882,11 +3875,11 @@
       <c r="L34" s="3"/>
       <c r="M34" s="24">
         <f>SUM(M31:M33)</f>
-        <v>1.6651249190399999</v>
+        <v>1.9095714827904</v>
       </c>
       <c r="N34" s="3">
-        <f>+M34/$J$34</f>
-        <v>0.99460625674217906</v>
+        <f>SUM(N31:N33)</f>
+        <v>1</v>
       </c>
       <c r="O34" s="26">
         <f>M9</f>
@@ -3902,7 +3895,7 @@
       </c>
     </row>
     <row r="35" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D35" s="83"/>
+      <c r="D35" s="88"/>
       <c r="E35" s="2" t="s">
         <v>16</v>
       </c>
@@ -3912,22 +3905,22 @@
       </c>
       <c r="H35" s="23">
         <f>+$H$34/$F$34-1</f>
-        <v>-7.2999999999999954E-2</v>
+        <v>-7.2999999999999732E-3</v>
       </c>
       <c r="I35" s="2"/>
       <c r="J35" s="23">
         <f>+J34/I34-1</f>
-        <v>0.67415488063999995</v>
+        <v>0.91053377440640015</v>
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
       <c r="M35" s="23">
         <f>+M34/K34-1</f>
-        <v>0.66512491903999993</v>
+        <v>0.90957148279040001</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="26" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="P35" s="20">
         <f>O9</f>
@@ -3936,51 +3929,51 @@
       <c r="Q35" s="2"/>
     </row>
     <row r="38" spans="4:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E38" s="73" t="s">
-        <v>52</v>
-      </c>
-      <c r="F38" s="73"/>
-      <c r="G38" s="73"/>
-      <c r="H38" s="85" t="s">
+      <c r="E38" s="77" t="s">
+        <v>49</v>
+      </c>
+      <c r="F38" s="77"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="I38" s="86"/>
-      <c r="J38" s="86"/>
-      <c r="K38" s="86"/>
-      <c r="L38" s="86"/>
-      <c r="M38" s="86"/>
-      <c r="N38" s="86"/>
-      <c r="O38" s="86"/>
-      <c r="P38" s="86"/>
-      <c r="Q38" s="87"/>
+      <c r="I38" s="85"/>
+      <c r="J38" s="85"/>
+      <c r="K38" s="85"/>
+      <c r="L38" s="85"/>
+      <c r="M38" s="85"/>
+      <c r="N38" s="85"/>
+      <c r="O38" s="85"/>
+      <c r="P38" s="85"/>
+      <c r="Q38" s="86"/>
     </row>
     <row r="39" spans="4:17" ht="25.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="E39" s="2"/>
-      <c r="F39" s="73" t="s">
+      <c r="F39" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="G39" s="73"/>
-      <c r="H39" s="73" t="s">
-        <v>43</v>
-      </c>
-      <c r="I39" s="73"/>
-      <c r="J39" s="73" t="s">
-        <v>44</v>
-      </c>
-      <c r="K39" s="73"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="I39" s="77"/>
+      <c r="J39" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="K39" s="77"/>
       <c r="L39" s="2"/>
-      <c r="M39" s="73" t="s">
-        <v>45</v>
-      </c>
-      <c r="N39" s="73"/>
+      <c r="M39" s="77" t="s">
+        <v>42</v>
+      </c>
+      <c r="N39" s="77"/>
       <c r="O39" s="19" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P39" s="19" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="Q39" s="19" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="4:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3996,7 +3989,7 @@
       </c>
       <c r="H40" s="4">
         <f>+$F$40*(1-$J$5/100)</f>
-        <v>1.08635572</v>
+        <v>1.1690695719999999</v>
       </c>
       <c r="I40" s="23">
         <f>$H$40/$H$18</f>
@@ -4004,7 +3997,7 @@
       </c>
       <c r="J40" s="4">
         <f>+$F$23*(1-$J$7/100)</f>
-        <v>1.09106876</v>
+        <v>1.1695408760000001</v>
       </c>
       <c r="K40" s="23">
         <f>J40/$H$26</f>
@@ -4013,11 +4006,11 @@
       <c r="L40" s="23"/>
       <c r="M40" s="4">
         <f>+$F$31*(1-$J$9/100)</f>
-        <v>1.0922470200000001</v>
+        <v>1.1696587020000002</v>
       </c>
       <c r="N40" s="23">
         <f>$H$31/$H$34</f>
-        <v>0.60805259681281476</v>
+        <v>0.60805259681281487</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
@@ -4036,7 +4029,7 @@
       </c>
       <c r="H41" s="4">
         <f>+$F$41*(1-$J$5/100)</f>
-        <v>0.35450899999999996</v>
+        <v>0.38150089999999998</v>
       </c>
       <c r="I41" s="23">
         <f>$H$41/$H$18</f>
@@ -4044,16 +4037,16 @@
       </c>
       <c r="J41" s="4">
         <f>+$F$24*(1-$J$7/100)</f>
-        <v>0.356047</v>
+        <v>0.38165470000000001</v>
       </c>
       <c r="K41" s="23">
         <f>J41/$H$26</f>
-        <v>0.19842498555032614</v>
+        <v>0.19842498555032612</v>
       </c>
       <c r="L41" s="23"/>
       <c r="M41" s="4">
         <f>+$F$32*(1-$J$9/100)</f>
-        <v>0.35643150000000001</v>
+        <v>0.38169315000000004</v>
       </c>
       <c r="N41" s="23">
         <f>$H$32/$H$34</f>
@@ -4076,7 +4069,7 @@
       </c>
       <c r="H42" s="4">
         <f>+$F$42*(1-$J$5/100)</f>
-        <v>0.34575</v>
+        <v>0.37207499999999999</v>
       </c>
       <c r="I42" s="23">
         <f>$H$42/$H$18</f>
@@ -4084,16 +4077,16 @@
       </c>
       <c r="J42" s="4">
         <f>+$F$25*(1-$J$7/100)</f>
-        <v>0.34724999999999995</v>
+        <v>0.37222500000000003</v>
       </c>
       <c r="K42" s="23">
         <f>J42/$H$26</f>
-        <v>0.19352241763685901</v>
+        <v>0.19352241763685904</v>
       </c>
       <c r="L42" s="23"/>
       <c r="M42" s="4">
         <f>+$F$33*(1-$J$9/100)</f>
-        <v>0.34762500000000002</v>
+        <v>0.3722625</v>
       </c>
       <c r="N42" s="23">
         <f>$H$33/$H$34</f>
@@ -4117,7 +4110,7 @@
       </c>
       <c r="H43" s="24">
         <f>SUM($H$40:$H$42)</f>
-        <v>1.78661472</v>
+        <v>1.9226454719999999</v>
       </c>
       <c r="I43" s="3">
         <f>SUM($I$40:$I$42)</f>
@@ -4125,7 +4118,7 @@
       </c>
       <c r="J43" s="4">
         <f>+$F$26*(1-$J$7/100)</f>
-        <v>1.79436576</v>
+        <v>1.9234205760000003</v>
       </c>
       <c r="K43" s="3">
         <f>SUM(K40:K42)</f>
@@ -4134,7 +4127,7 @@
       <c r="L43" s="3"/>
       <c r="M43" s="24">
         <f>SUM(M40:M42)</f>
-        <v>1.7963035200000002</v>
+        <v>1.9236143520000002</v>
       </c>
       <c r="N43" s="3">
         <f>SUM(N40:N42)</f>
@@ -4163,18 +4156,18 @@
       </c>
       <c r="H44" s="25">
         <f>+$H$43/$F$43-1</f>
-        <v>-7.8000000000000069E-2</v>
+        <v>-7.8000000000001402E-3</v>
       </c>
       <c r="I44" s="2"/>
       <c r="J44" s="23">
         <f>+$H$26/$F$26-1</f>
-        <v>-7.4000000000000066E-2</v>
+        <v>-7.3999999999999622E-3</v>
       </c>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
       <c r="M44" s="23">
         <f>+$H$34/$F$34-1</f>
-        <v>-7.2999999999999954E-2</v>
+        <v>-7.2999999999999732E-3</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -4183,40 +4176,6 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="E12:O12"/>
-    <mergeCell ref="J13:O13"/>
-    <mergeCell ref="E13:I13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="E29:Q29"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="H38:Q38"/>
-    <mergeCell ref="D15:D19"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="E21:Q21"/>
-    <mergeCell ref="D31:D35"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="D23:D27"/>
     <mergeCell ref="E2:I2"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="G9:G10"/>
@@ -4233,6 +4192,40 @@
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="E9:E10"/>
+    <mergeCell ref="D31:D35"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="D23:D27"/>
+    <mergeCell ref="D15:D19"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="E21:Q21"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="H38:Q38"/>
+    <mergeCell ref="E12:O12"/>
+    <mergeCell ref="J13:O13"/>
+    <mergeCell ref="E13:I13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="E29:Q29"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="L9:L10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4388,42 +4381,42 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H2" s="94" t="s">
-        <v>71</v>
-      </c>
-      <c r="I2" s="94"/>
+      <c r="H2" s="71" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2" s="71"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H3" s="94"/>
-      <c r="I3" s="94"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
     </row>
     <row r="4" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="95" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
+      <c r="B4" s="72" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
       <c r="E4" s="7"/>
-      <c r="H4" s="94"/>
-      <c r="I4" s="94"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
     </row>
     <row r="5" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E5" s="7"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="37" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C6" s="38">
         <v>0.8</v>
@@ -4433,12 +4426,12 @@
         <v>1.008</v>
       </c>
       <c r="E6" s="7"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="94"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="39" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C7" s="38">
         <v>-1.18</v>
@@ -4450,37 +4443,37 @@
       <c r="E7" s="7"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H8" s="94" t="s">
-        <v>78</v>
-      </c>
-      <c r="I8" s="94"/>
+      <c r="H8" s="71" t="s">
+        <v>75</v>
+      </c>
+      <c r="I8" s="71"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H9" s="94"/>
-      <c r="I9" s="94"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
     </row>
     <row r="10" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B10" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="F10" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="D10" s="41" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="41" t="s">
-        <v>82</v>
-      </c>
-      <c r="F10" s="41" t="s">
-        <v>83</v>
-      </c>
-      <c r="H10" s="94"/>
-      <c r="I10" s="94"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="37" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C11" s="7">
         <v>1.1782600000000001</v>
@@ -4490,18 +4483,18 @@
         <v>1.008</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F11" s="42">
         <f>C11*D11</f>
         <v>1.1876860800000002</v>
       </c>
-      <c r="H11" s="94"/>
-      <c r="I11" s="94"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="37" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C12" s="42">
         <v>0.38450000000000001</v>
@@ -4519,12 +4512,12 @@
         <v>0.38300260320000001</v>
       </c>
       <c r="G12" s="43"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
     </row>
     <row r="13" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B13" s="44" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C13" s="42">
         <v>0.375</v>
@@ -4534,7 +4527,7 @@
         <v>1.008</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F13" s="42">
         <f>C13*D13</f>
@@ -4543,52 +4536,52 @@
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="H14" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I14" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="J14" s="48" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="73"/>
+      <c r="C15" s="73"/>
+      <c r="H15" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="I14" s="47" t="s">
+      <c r="I15" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="J15" s="46" t="s">
         <v>89</v>
-      </c>
-      <c r="J14" s="48" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="96"/>
-      <c r="C15" s="96"/>
-      <c r="H15" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="I15" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="J15" s="46" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="42.75" x14ac:dyDescent="0.25">
       <c r="B16" s="6"/>
       <c r="C16" s="49"/>
       <c r="H16" s="45" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I16" s="45" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J16" s="45" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="2:14" ht="57" x14ac:dyDescent="0.25">
       <c r="B17" s="50"/>
       <c r="C17" s="51"/>
       <c r="H17" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="I17" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="I17" s="45" t="s">
-        <v>98</v>
-      </c>
       <c r="J17" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -4600,17 +4593,17 @@
       <c r="C19" s="51"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="H21" s="96" t="s">
-        <v>137</v>
-      </c>
-      <c r="I21" s="96"/>
+      <c r="H21" s="73" t="s">
+        <v>134</v>
+      </c>
+      <c r="I21" s="73"/>
     </row>
     <row r="22" spans="2:14" ht="306" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H22" s="97" t="s">
-        <v>136</v>
-      </c>
-      <c r="I22" s="97"/>
-      <c r="J22" s="97"/>
+      <c r="H22" s="74" t="s">
+        <v>133</v>
+      </c>
+      <c r="I22" s="74"/>
+      <c r="J22" s="74"/>
       <c r="K22" s="67"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
@@ -4626,186 +4619,186 @@
       <c r="K24" s="67"/>
     </row>
     <row r="25" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H25" s="92" t="s">
-        <v>138</v>
-      </c>
-      <c r="I25" s="93"/>
-      <c r="J25" s="93"/>
-      <c r="K25" s="93"/>
-      <c r="L25" s="93"/>
-      <c r="M25" s="93"/>
-      <c r="N25" s="93"/>
+      <c r="H25" s="69" t="s">
+        <v>135</v>
+      </c>
+      <c r="I25" s="70"/>
+      <c r="J25" s="70"/>
+      <c r="K25" s="70"/>
+      <c r="L25" s="70"/>
+      <c r="M25" s="70"/>
+      <c r="N25" s="70"/>
     </row>
     <row r="26" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H26" s="93"/>
-      <c r="I26" s="93"/>
-      <c r="J26" s="93"/>
-      <c r="K26" s="93"/>
-      <c r="L26" s="93"/>
-      <c r="M26" s="93"/>
-      <c r="N26" s="93"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="70"/>
+      <c r="K26" s="70"/>
+      <c r="L26" s="70"/>
+      <c r="M26" s="70"/>
+      <c r="N26" s="70"/>
     </row>
     <row r="27" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H27" s="93"/>
-      <c r="I27" s="93"/>
-      <c r="J27" s="93"/>
-      <c r="K27" s="93"/>
-      <c r="L27" s="93"/>
-      <c r="M27" s="93"/>
-      <c r="N27" s="93"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="70"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="70"/>
+      <c r="M27" s="70"/>
+      <c r="N27" s="70"/>
     </row>
     <row r="28" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H28" s="93"/>
-      <c r="I28" s="93"/>
-      <c r="J28" s="93"/>
-      <c r="K28" s="93"/>
-      <c r="L28" s="93"/>
-      <c r="M28" s="93"/>
-      <c r="N28" s="93"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="70"/>
+      <c r="K28" s="70"/>
+      <c r="L28" s="70"/>
+      <c r="M28" s="70"/>
+      <c r="N28" s="70"/>
     </row>
     <row r="29" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H29" s="93"/>
-      <c r="I29" s="93"/>
-      <c r="J29" s="93"/>
-      <c r="K29" s="93"/>
-      <c r="L29" s="93"/>
-      <c r="M29" s="93"/>
-      <c r="N29" s="93"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="70"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="70"/>
+      <c r="M29" s="70"/>
+      <c r="N29" s="70"/>
     </row>
     <row r="30" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H30" s="93"/>
-      <c r="I30" s="93"/>
-      <c r="J30" s="93"/>
-      <c r="K30" s="93"/>
-      <c r="L30" s="93"/>
-      <c r="M30" s="93"/>
-      <c r="N30" s="93"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="70"/>
+      <c r="K30" s="70"/>
+      <c r="L30" s="70"/>
+      <c r="M30" s="70"/>
+      <c r="N30" s="70"/>
     </row>
     <row r="31" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H31" s="93"/>
-      <c r="I31" s="93"/>
-      <c r="J31" s="93"/>
-      <c r="K31" s="93"/>
-      <c r="L31" s="93"/>
-      <c r="M31" s="93"/>
-      <c r="N31" s="93"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="70"/>
+      <c r="K31" s="70"/>
+      <c r="L31" s="70"/>
+      <c r="M31" s="70"/>
+      <c r="N31" s="70"/>
     </row>
     <row r="32" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H32" s="93"/>
-      <c r="I32" s="93"/>
-      <c r="J32" s="93"/>
-      <c r="K32" s="93"/>
-      <c r="L32" s="93"/>
-      <c r="M32" s="93"/>
-      <c r="N32" s="93"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="70"/>
+      <c r="K32" s="70"/>
+      <c r="L32" s="70"/>
+      <c r="M32" s="70"/>
+      <c r="N32" s="70"/>
     </row>
     <row r="33" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H33" s="93"/>
-      <c r="I33" s="93"/>
-      <c r="J33" s="93"/>
-      <c r="K33" s="93"/>
-      <c r="L33" s="93"/>
-      <c r="M33" s="93"/>
-      <c r="N33" s="93"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="70"/>
+      <c r="K33" s="70"/>
+      <c r="L33" s="70"/>
+      <c r="M33" s="70"/>
+      <c r="N33" s="70"/>
     </row>
     <row r="34" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H34" s="93"/>
-      <c r="I34" s="93"/>
-      <c r="J34" s="93"/>
-      <c r="K34" s="93"/>
-      <c r="L34" s="93"/>
-      <c r="M34" s="93"/>
-      <c r="N34" s="93"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70"/>
+      <c r="J34" s="70"/>
+      <c r="K34" s="70"/>
+      <c r="L34" s="70"/>
+      <c r="M34" s="70"/>
+      <c r="N34" s="70"/>
     </row>
     <row r="35" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H35" s="93"/>
-      <c r="I35" s="93"/>
-      <c r="J35" s="93"/>
-      <c r="K35" s="93"/>
-      <c r="L35" s="93"/>
-      <c r="M35" s="93"/>
-      <c r="N35" s="93"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="70"/>
+      <c r="K35" s="70"/>
+      <c r="L35" s="70"/>
+      <c r="M35" s="70"/>
+      <c r="N35" s="70"/>
     </row>
     <row r="36" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H36" s="93"/>
-      <c r="I36" s="93"/>
-      <c r="J36" s="93"/>
-      <c r="K36" s="93"/>
-      <c r="L36" s="93"/>
-      <c r="M36" s="93"/>
-      <c r="N36" s="93"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="70"/>
+      <c r="K36" s="70"/>
+      <c r="L36" s="70"/>
+      <c r="M36" s="70"/>
+      <c r="N36" s="70"/>
     </row>
     <row r="37" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H37" s="93"/>
-      <c r="I37" s="93"/>
-      <c r="J37" s="93"/>
-      <c r="K37" s="93"/>
-      <c r="L37" s="93"/>
-      <c r="M37" s="93"/>
-      <c r="N37" s="93"/>
+      <c r="H37" s="70"/>
+      <c r="I37" s="70"/>
+      <c r="J37" s="70"/>
+      <c r="K37" s="70"/>
+      <c r="L37" s="70"/>
+      <c r="M37" s="70"/>
+      <c r="N37" s="70"/>
     </row>
     <row r="38" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H38" s="93"/>
-      <c r="I38" s="93"/>
-      <c r="J38" s="93"/>
-      <c r="K38" s="93"/>
-      <c r="L38" s="93"/>
-      <c r="M38" s="93"/>
-      <c r="N38" s="93"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="70"/>
+      <c r="M38" s="70"/>
+      <c r="N38" s="70"/>
     </row>
     <row r="39" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H39" s="93"/>
-      <c r="I39" s="93"/>
-      <c r="J39" s="93"/>
-      <c r="K39" s="93"/>
-      <c r="L39" s="93"/>
-      <c r="M39" s="93"/>
-      <c r="N39" s="93"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="70"/>
+      <c r="M39" s="70"/>
+      <c r="N39" s="70"/>
     </row>
     <row r="40" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H40" s="93"/>
-      <c r="I40" s="93"/>
-      <c r="J40" s="93"/>
-      <c r="K40" s="93"/>
-      <c r="L40" s="93"/>
-      <c r="M40" s="93"/>
-      <c r="N40" s="93"/>
+      <c r="H40" s="70"/>
+      <c r="I40" s="70"/>
+      <c r="J40" s="70"/>
+      <c r="K40" s="70"/>
+      <c r="L40" s="70"/>
+      <c r="M40" s="70"/>
+      <c r="N40" s="70"/>
     </row>
     <row r="41" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H41" s="93"/>
-      <c r="I41" s="93"/>
-      <c r="J41" s="93"/>
-      <c r="K41" s="93"/>
-      <c r="L41" s="93"/>
-      <c r="M41" s="93"/>
-      <c r="N41" s="93"/>
+      <c r="H41" s="70"/>
+      <c r="I41" s="70"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="70"/>
+      <c r="M41" s="70"/>
+      <c r="N41" s="70"/>
     </row>
     <row r="42" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H42" s="93"/>
-      <c r="I42" s="93"/>
-      <c r="J42" s="93"/>
-      <c r="K42" s="93"/>
-      <c r="L42" s="93"/>
-      <c r="M42" s="93"/>
-      <c r="N42" s="93"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="70"/>
+      <c r="K42" s="70"/>
+      <c r="L42" s="70"/>
+      <c r="M42" s="70"/>
+      <c r="N42" s="70"/>
     </row>
     <row r="43" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H43" s="93"/>
-      <c r="I43" s="93"/>
-      <c r="J43" s="93"/>
-      <c r="K43" s="93"/>
-      <c r="L43" s="93"/>
-      <c r="M43" s="93"/>
-      <c r="N43" s="93"/>
+      <c r="H43" s="70"/>
+      <c r="I43" s="70"/>
+      <c r="J43" s="70"/>
+      <c r="K43" s="70"/>
+      <c r="L43" s="70"/>
+      <c r="M43" s="70"/>
+      <c r="N43" s="70"/>
     </row>
     <row r="44" spans="8:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H44" s="93"/>
-      <c r="I44" s="93"/>
-      <c r="J44" s="93"/>
-      <c r="K44" s="93"/>
-      <c r="L44" s="93"/>
-      <c r="M44" s="93"/>
-      <c r="N44" s="93"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="70"/>
+      <c r="K44" s="70"/>
+      <c r="L44" s="70"/>
+      <c r="M44" s="70"/>
+      <c r="N44" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/Color/LogicDocs/formulas y funciones .xlsx
+++ b/Color/LogicDocs/formulas y funciones .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coatsplc-my.sharepoint.com/personal/elkinduvan_quebradaguapacha_coats_com/Documents/Escritorio/Colorimetria/Color/LogicDocs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1210" documentId="8_{9F78D261-5971-4E36-A791-098E2ABB119D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9822D49A-3328-4804-A480-D0E4CEAD375C}"/>
+  <xr:revisionPtr revIDLastSave="1213" documentId="8_{9F78D261-5971-4E36-A791-098E2ABB119D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77A91586-CA46-57E8-8B9F-E084E9B7481B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="1" activeTab="3" xr2:uid="{74F1A0B1-3ED8-4C59-B930-9B261CE40F5C}"/>
   </bookViews>
@@ -1059,19 +1059,61 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1084,48 +1126,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1806,10 +1806,6 @@
 </externalLink>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2148,13 +2144,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -2175,10 +2171,10 @@
         <v>132</v>
       </c>
       <c r="G2" s="1"/>
-      <c r="H2" s="77" t="s">
+      <c r="H2" s="79" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="77"/>
+      <c r="I2" s="79"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -2403,7 +2399,7 @@
       </c>
     </row>
     <row r="15" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="76" t="s">
+      <c r="B15" s="75" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="7" t="s">
@@ -2418,39 +2414,39 @@
       <c r="F15" s="28">
         <v>-3.6</v>
       </c>
-      <c r="G15" s="76">
+      <c r="G15" s="75">
         <f>+(D15-D16)/D15</f>
         <v>2.5956778944826651E-2</v>
       </c>
-      <c r="H15" s="76">
+      <c r="H15" s="75">
         <f>+(E15-E16)/E15</f>
         <v>8.6376404494382053E-2</v>
       </c>
-      <c r="I15" s="76">
+      <c r="I15" s="75">
         <f>+(F15-F16)/F15</f>
         <v>3.611111111111108E-2</v>
       </c>
-      <c r="J15" s="76">
+      <c r="J15" s="75">
         <f>+ABS(G15)</f>
         <v>2.5956778944826651E-2</v>
       </c>
-      <c r="K15" s="76">
+      <c r="K15" s="75">
         <f>+ABS(H15)</f>
         <v>8.6376404494382053E-2</v>
       </c>
-      <c r="L15" s="76">
+      <c r="L15" s="75">
         <f>+ABS(I15)</f>
         <v>3.611111111111108E-2</v>
       </c>
-      <c r="M15" s="75">
+      <c r="M15" s="78">
         <f>+K15/F15</f>
         <v>-2.3993445692883902E-2</v>
       </c>
-      <c r="N15" s="75">
+      <c r="N15" s="78">
         <f>+K15/E15</f>
         <v>-6.0657587425830091E-3</v>
       </c>
-      <c r="O15" s="75">
+      <c r="O15" s="78">
         <f>+L15/F15</f>
         <v>-1.0030864197530855E-2</v>
       </c>
@@ -2480,7 +2476,7 @@
       </c>
     </row>
     <row r="16" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="76"/>
+      <c r="B16" s="75"/>
       <c r="C16" s="7" t="s">
         <v>26</v>
       </c>
@@ -2493,15 +2489,15 @@
       <c r="F16" s="28">
         <v>-3.47</v>
       </c>
-      <c r="G16" s="76"/>
-      <c r="H16" s="76"/>
-      <c r="I16" s="76"/>
-      <c r="J16" s="76"/>
-      <c r="K16" s="76"/>
-      <c r="L16" s="76"/>
-      <c r="M16" s="76"/>
-      <c r="N16" s="76"/>
-      <c r="O16" s="76"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="75"/>
+      <c r="I16" s="75"/>
+      <c r="J16" s="75"/>
+      <c r="K16" s="75"/>
+      <c r="L16" s="75"/>
+      <c r="M16" s="75"/>
+      <c r="N16" s="75"/>
+      <c r="O16" s="75"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
@@ -2510,7 +2506,7 @@
       <c r="U16" s="7"/>
     </row>
     <row r="17" spans="2:21" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="76" t="s">
+      <c r="B17" s="75" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="7" t="s">
@@ -2525,39 +2521,39 @@
       <c r="F17" s="28">
         <v>5.0599999999999996</v>
       </c>
-      <c r="G17" s="76">
+      <c r="G17" s="75">
         <f>+(D17-D18)/D17</f>
         <v>2.4813592470358161E-2</v>
       </c>
-      <c r="H17" s="76">
+      <c r="H17" s="75">
         <f>+(E17-E18)/E17</f>
         <v>5.7165231010180145E-2</v>
       </c>
-      <c r="I17" s="76">
+      <c r="I17" s="75">
         <f>+(F17-F18)/F17</f>
         <v>1.8557312252964429</v>
       </c>
-      <c r="J17" s="76">
+      <c r="J17" s="75">
         <f>+ABS(G17)</f>
         <v>2.4813592470358161E-2</v>
       </c>
-      <c r="K17" s="76">
+      <c r="K17" s="75">
         <f>+ABS(H17)</f>
         <v>5.7165231010180145E-2</v>
       </c>
-      <c r="L17" s="76">
+      <c r="L17" s="75">
         <f>+ABS(I17)</f>
         <v>1.8557312252964429</v>
       </c>
-      <c r="M17" s="75">
+      <c r="M17" s="78">
         <f>+J17/D17</f>
         <v>3.0330757206158365E-4</v>
       </c>
-      <c r="N17" s="75">
+      <c r="N17" s="78">
         <f>+K17/E17</f>
         <v>-4.4765255293798076E-3</v>
       </c>
-      <c r="O17" s="75">
+      <c r="O17" s="78">
         <f>+L17/F17</f>
         <v>0.36674530144198481</v>
       </c>
@@ -2587,7 +2583,7 @@
       </c>
     </row>
     <row r="18" spans="2:21" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="76"/>
+      <c r="B18" s="75"/>
       <c r="C18" s="7" t="s">
         <v>26</v>
       </c>
@@ -2600,15 +2596,15 @@
       <c r="F18" s="28">
         <v>-4.33</v>
       </c>
-      <c r="G18" s="76"/>
-      <c r="H18" s="76"/>
-      <c r="I18" s="76"/>
-      <c r="J18" s="76"/>
-      <c r="K18" s="76"/>
-      <c r="L18" s="76"/>
-      <c r="M18" s="76"/>
-      <c r="N18" s="76"/>
-      <c r="O18" s="76"/>
+      <c r="G18" s="75"/>
+      <c r="H18" s="75"/>
+      <c r="I18" s="75"/>
+      <c r="J18" s="75"/>
+      <c r="K18" s="75"/>
+      <c r="L18" s="75"/>
+      <c r="M18" s="75"/>
+      <c r="N18" s="75"/>
+      <c r="O18" s="75"/>
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
       <c r="R18" s="7"/>
@@ -2617,7 +2613,7 @@
       <c r="U18" s="7"/>
     </row>
     <row r="19" spans="2:21" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="76" t="s">
+      <c r="B19" s="75" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="7" t="s">
@@ -2632,39 +2628,39 @@
       <c r="F19" s="28">
         <v>7.39</v>
       </c>
-      <c r="G19" s="76">
+      <c r="G19" s="75">
         <f>+(D19-D20)/D19</f>
         <v>4.9419322955275513E-2</v>
       </c>
-      <c r="H19" s="76">
+      <c r="H19" s="75">
         <f>+(E19-E20)/E19</f>
         <v>5.7884231536926095E-2</v>
       </c>
-      <c r="I19" s="76">
+      <c r="I19" s="75">
         <f>+(F19-F20)/F19</f>
         <v>7.9837618403247615E-2</v>
       </c>
-      <c r="J19" s="76">
+      <c r="J19" s="75">
         <f>+ABS(G19)</f>
         <v>4.9419322955275513E-2</v>
       </c>
-      <c r="K19" s="76">
+      <c r="K19" s="75">
         <f>+ABS(H19)</f>
         <v>5.7884231536926095E-2</v>
       </c>
-      <c r="L19" s="76">
+      <c r="L19" s="75">
         <f>+ABS(I19)</f>
         <v>7.9837618403247615E-2</v>
       </c>
-      <c r="M19" s="75">
+      <c r="M19" s="78">
         <f>+J19/D19</f>
         <v>6.1056737033945529E-4</v>
       </c>
-      <c r="N19" s="75">
+      <c r="N19" s="78">
         <f>+K19/E19</f>
         <v>-3.8512462765752562E-3</v>
       </c>
-      <c r="O19" s="75">
+      <c r="O19" s="78">
         <f>+L19/F19</f>
         <v>1.0803466631021328E-2</v>
       </c>
@@ -2694,7 +2690,7 @@
       </c>
     </row>
     <row r="20" spans="2:21" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="76"/>
+      <c r="B20" s="75"/>
       <c r="C20" s="7" t="s">
         <v>26</v>
       </c>
@@ -2707,15 +2703,15 @@
       <c r="F20" s="28">
         <v>6.8</v>
       </c>
-      <c r="G20" s="76"/>
-      <c r="H20" s="76"/>
-      <c r="I20" s="76"/>
-      <c r="J20" s="76"/>
-      <c r="K20" s="76"/>
-      <c r="L20" s="76"/>
-      <c r="M20" s="76"/>
-      <c r="N20" s="76"/>
-      <c r="O20" s="76"/>
+      <c r="G20" s="75"/>
+      <c r="H20" s="75"/>
+      <c r="I20" s="75"/>
+      <c r="J20" s="75"/>
+      <c r="K20" s="75"/>
+      <c r="L20" s="75"/>
+      <c r="M20" s="75"/>
+      <c r="N20" s="75"/>
+      <c r="O20" s="75"/>
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
       <c r="R20" s="7"/>
@@ -2767,7 +2763,7 @@
       <c r="F38" s="58" t="s">
         <v>108</v>
       </c>
-      <c r="I38" s="78" t="s">
+      <c r="I38" s="76" t="s">
         <v>109</v>
       </c>
       <c r="L38" t="s">
@@ -2801,7 +2797,7 @@
       <c r="F39" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="I39" s="78"/>
+      <c r="I39" s="76"/>
       <c r="L39" t="s">
         <v>115</v>
       </c>
@@ -2836,7 +2832,7 @@
       <c r="F40" s="58" t="s">
         <v>121</v>
       </c>
-      <c r="I40" s="78" t="s">
+      <c r="I40" s="76" t="s">
         <v>122</v>
       </c>
       <c r="L40" t="s">
@@ -2868,7 +2864,7 @@
       <c r="F41" s="58" t="s">
         <v>126</v>
       </c>
-      <c r="I41" s="78"/>
+      <c r="I41" s="76"/>
       <c r="L41" t="s">
         <v>127</v>
       </c>
@@ -2911,24 +2907,6 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="I19:I20"/>
     <mergeCell ref="N19:N20"/>
     <mergeCell ref="O19:O20"/>
     <mergeCell ref="H2:I2"/>
@@ -2945,6 +2923,24 @@
     <mergeCell ref="K15:K16"/>
     <mergeCell ref="M19:M20"/>
     <mergeCell ref="J19:J20"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="J15:J16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2974,13 +2970,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E2" s="77" t="s">
+      <c r="E2" s="79" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
     </row>
     <row r="3" spans="4:15" x14ac:dyDescent="0.2">
       <c r="E3" s="2"/>
@@ -3028,30 +3024,30 @@
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="4:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E5" s="97" t="s">
+      <c r="E5" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="94">
+      <c r="F5" s="85">
         <v>-0.78</v>
       </c>
-      <c r="G5" s="94">
+      <c r="G5" s="85">
         <v>-0.86</v>
       </c>
-      <c r="H5" s="96">
+      <c r="H5" s="87">
         <v>0.17</v>
       </c>
-      <c r="I5" s="92">
+      <c r="I5" s="83">
         <v>1.17</v>
       </c>
-      <c r="J5" s="81">
+      <c r="J5" s="95">
         <f>+ABS(F5)</f>
         <v>0.78</v>
       </c>
-      <c r="K5" s="80">
+      <c r="K5" s="94">
         <f>+ABS(G5)</f>
         <v>0.86</v>
       </c>
-      <c r="L5" s="80">
+      <c r="L5" s="94">
         <f>+ABS(H5)</f>
         <v>0.17</v>
       </c>
@@ -3069,43 +3065,43 @@
       </c>
     </row>
     <row r="6" spans="4:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E6" s="97"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="93"/>
-      <c r="J6" s="81"/>
-      <c r="K6" s="80"/>
-      <c r="L6" s="80"/>
+      <c r="E6" s="88"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="86"/>
+      <c r="H6" s="86"/>
+      <c r="I6" s="84"/>
+      <c r="J6" s="95"/>
+      <c r="K6" s="94"/>
+      <c r="L6" s="94"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
     <row r="7" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E7" s="77" t="s">
+      <c r="E7" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="89">
+      <c r="F7" s="80">
         <v>-0.74</v>
       </c>
-      <c r="G7" s="91">
+      <c r="G7" s="82">
         <v>-0.54</v>
       </c>
-      <c r="H7" s="91">
+      <c r="H7" s="82">
         <v>0.1</v>
       </c>
-      <c r="I7" s="90">
+      <c r="I7" s="81">
         <v>0.92</v>
       </c>
-      <c r="J7" s="82">
+      <c r="J7" s="96">
         <f>+ABS(F7)</f>
         <v>0.74</v>
       </c>
-      <c r="K7" s="83">
+      <c r="K7" s="97">
         <f>+ABS(G7)</f>
         <v>0.54</v>
       </c>
-      <c r="L7" s="83">
+      <c r="L7" s="97">
         <f>+ABS(H7)</f>
         <v>0.1</v>
       </c>
@@ -3123,43 +3119,43 @@
       </c>
     </row>
     <row r="8" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E8" s="77"/>
-      <c r="F8" s="90"/>
-      <c r="G8" s="90"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="90"/>
-      <c r="J8" s="82"/>
-      <c r="K8" s="83"/>
-      <c r="L8" s="83"/>
+      <c r="E8" s="79"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="96"/>
+      <c r="K8" s="97"/>
+      <c r="L8" s="97"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E9" s="77" t="s">
+      <c r="E9" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="89">
+      <c r="F9" s="80">
         <v>-0.73</v>
       </c>
-      <c r="G9" s="91">
+      <c r="G9" s="82">
         <v>-0.68</v>
       </c>
-      <c r="H9" s="91">
+      <c r="H9" s="82">
         <v>-0.12</v>
       </c>
-      <c r="I9" s="90">
+      <c r="I9" s="81">
         <v>1.01</v>
       </c>
-      <c r="J9" s="82">
+      <c r="J9" s="96">
         <f>+ABS(F9)</f>
         <v>0.73</v>
       </c>
-      <c r="K9" s="83">
+      <c r="K9" s="97">
         <f>+ABS(G9)</f>
         <v>0.68</v>
       </c>
-      <c r="L9" s="83">
+      <c r="L9" s="97">
         <f>+ABS(H9)</f>
         <v>0.12</v>
       </c>
@@ -3177,14 +3173,14 @@
       </c>
     </row>
     <row r="10" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E10" s="77"/>
-      <c r="F10" s="90"/>
-      <c r="G10" s="90"/>
-      <c r="H10" s="90"/>
-      <c r="I10" s="90"/>
-      <c r="J10" s="82"/>
-      <c r="K10" s="83"/>
-      <c r="L10" s="83"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="96"/>
+      <c r="K10" s="97"/>
+      <c r="L10" s="97"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3195,51 +3191,51 @@
       <c r="H11" s="9"/>
     </row>
     <row r="12" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E12" s="84" t="s">
+      <c r="E12" s="91" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="85"/>
-      <c r="G12" s="85"/>
-      <c r="H12" s="85"/>
-      <c r="I12" s="85"/>
-      <c r="J12" s="85"/>
-      <c r="K12" s="85"/>
-      <c r="L12" s="85"/>
-      <c r="M12" s="85"/>
-      <c r="N12" s="85"/>
-      <c r="O12" s="86"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="92"/>
+      <c r="H12" s="92"/>
+      <c r="I12" s="92"/>
+      <c r="J12" s="92"/>
+      <c r="K12" s="92"/>
+      <c r="L12" s="92"/>
+      <c r="M12" s="92"/>
+      <c r="N12" s="92"/>
+      <c r="O12" s="93"/>
     </row>
     <row r="13" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="E13" s="77" t="s">
+      <c r="E13" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="84" t="s">
+      <c r="F13" s="79"/>
+      <c r="G13" s="79"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="85"/>
-      <c r="L13" s="85"/>
-      <c r="M13" s="85"/>
-      <c r="N13" s="85"/>
-      <c r="O13" s="86"/>
+      <c r="K13" s="92"/>
+      <c r="L13" s="92"/>
+      <c r="M13" s="92"/>
+      <c r="N13" s="92"/>
+      <c r="O13" s="93"/>
     </row>
     <row r="14" spans="4:15" x14ac:dyDescent="0.2">
       <c r="E14" s="2"/>
-      <c r="F14" s="77" t="s">
+      <c r="F14" s="79" t="s">
         <v>46</v>
       </c>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77" t="s">
+      <c r="G14" s="79"/>
+      <c r="H14" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="I14" s="77"/>
-      <c r="J14" s="77" t="s">
+      <c r="I14" s="79"/>
+      <c r="J14" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="K14" s="77"/>
+      <c r="K14" s="79"/>
       <c r="L14" s="2"/>
       <c r="M14" s="26" t="s">
         <v>60</v>
@@ -3252,7 +3248,7 @@
       </c>
     </row>
     <row r="15" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D15" s="88"/>
+      <c r="D15" s="89"/>
       <c r="E15" s="29" t="s">
         <v>12</v>
       </c>
@@ -3289,7 +3285,7 @@
       <c r="O15" s="26"/>
     </row>
     <row r="16" spans="4:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D16" s="88"/>
+      <c r="D16" s="89"/>
       <c r="E16" s="29" t="s">
         <v>13</v>
       </c>
@@ -3322,7 +3318,7 @@
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D17" s="88"/>
+      <c r="D17" s="89"/>
       <c r="E17" s="29" t="s">
         <v>14</v>
       </c>
@@ -3355,7 +3351,7 @@
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D18" s="88"/>
+      <c r="D18" s="89"/>
       <c r="E18" s="2" t="s">
         <v>15</v>
       </c>
@@ -3398,7 +3394,7 @@
       </c>
     </row>
     <row r="19" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D19" s="88"/>
+      <c r="D19" s="89"/>
       <c r="E19" s="2" t="s">
         <v>16</v>
       </c>
@@ -3421,41 +3417,41 @@
       <c r="P19" s="27"/>
     </row>
     <row r="21" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E21" s="87" t="s">
+      <c r="E21" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="F21" s="79"/>
-      <c r="G21" s="79"/>
-      <c r="H21" s="79"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="79"/>
-      <c r="K21" s="79"/>
-      <c r="L21" s="79"/>
-      <c r="M21" s="79"/>
-      <c r="N21" s="79"/>
-      <c r="O21" s="79"/>
-      <c r="P21" s="79"/>
-      <c r="Q21" s="79"/>
+      <c r="F21" s="77"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="77"/>
+      <c r="J21" s="77"/>
+      <c r="K21" s="77"/>
+      <c r="L21" s="77"/>
+      <c r="M21" s="77"/>
+      <c r="N21" s="77"/>
+      <c r="O21" s="77"/>
+      <c r="P21" s="77"/>
+      <c r="Q21" s="77"/>
     </row>
     <row r="22" spans="4:17" x14ac:dyDescent="0.2">
       <c r="E22" s="2"/>
-      <c r="F22" s="77" t="s">
+      <c r="F22" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77" t="s">
+      <c r="G22" s="79"/>
+      <c r="H22" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="I22" s="77"/>
-      <c r="J22" s="77" t="s">
+      <c r="I22" s="79"/>
+      <c r="J22" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="K22" s="77"/>
+      <c r="K22" s="79"/>
       <c r="L22" s="2"/>
-      <c r="M22" s="77" t="s">
+      <c r="M22" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="N22" s="77"/>
+      <c r="N22" s="79"/>
       <c r="O22" s="26" t="s">
         <v>52</v>
       </c>
@@ -3467,7 +3463,7 @@
       </c>
     </row>
     <row r="23" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="88"/>
+      <c r="D23" s="89"/>
       <c r="E23" s="29" t="s">
         <v>12</v>
       </c>
@@ -3508,7 +3504,7 @@
       <c r="Q23" s="2"/>
     </row>
     <row r="24" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="88"/>
+      <c r="D24" s="89"/>
       <c r="E24" s="29" t="s">
         <v>13</v>
       </c>
@@ -3549,7 +3545,7 @@
       <c r="Q24" s="2"/>
     </row>
     <row r="25" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="88"/>
+      <c r="D25" s="89"/>
       <c r="E25" s="29" t="s">
         <v>14</v>
       </c>
@@ -3590,7 +3586,7 @@
       <c r="Q25" s="2"/>
     </row>
     <row r="26" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D26" s="88"/>
+      <c r="D26" s="89"/>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
@@ -3641,7 +3637,7 @@
       </c>
     </row>
     <row r="27" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D27" s="88"/>
+      <c r="D27" s="89"/>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
@@ -3675,41 +3671,41 @@
       <c r="Q27" s="2"/>
     </row>
     <row r="29" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E29" s="87" t="s">
+      <c r="E29" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="F29" s="79"/>
-      <c r="G29" s="79"/>
-      <c r="H29" s="79"/>
-      <c r="I29" s="79"/>
-      <c r="J29" s="79"/>
-      <c r="K29" s="79"/>
-      <c r="L29" s="79"/>
-      <c r="M29" s="79"/>
-      <c r="N29" s="79"/>
-      <c r="O29" s="79"/>
-      <c r="P29" s="79"/>
-      <c r="Q29" s="79"/>
+      <c r="F29" s="77"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="77"/>
+      <c r="I29" s="77"/>
+      <c r="J29" s="77"/>
+      <c r="K29" s="77"/>
+      <c r="L29" s="77"/>
+      <c r="M29" s="77"/>
+      <c r="N29" s="77"/>
+      <c r="O29" s="77"/>
+      <c r="P29" s="77"/>
+      <c r="Q29" s="77"/>
     </row>
     <row r="30" spans="4:17" ht="25.5" x14ac:dyDescent="0.2">
       <c r="E30" s="2"/>
-      <c r="F30" s="77" t="s">
+      <c r="F30" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="G30" s="77"/>
-      <c r="H30" s="77" t="s">
+      <c r="G30" s="79"/>
+      <c r="H30" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="I30" s="77"/>
-      <c r="J30" s="77" t="s">
+      <c r="I30" s="79"/>
+      <c r="J30" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="K30" s="77"/>
+      <c r="K30" s="79"/>
       <c r="L30" s="2"/>
-      <c r="M30" s="77" t="s">
+      <c r="M30" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="N30" s="77"/>
+      <c r="N30" s="79"/>
       <c r="O30" s="26" t="s">
         <v>52</v>
       </c>
@@ -3721,7 +3717,7 @@
       </c>
     </row>
     <row r="31" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D31" s="88"/>
+      <c r="D31" s="89"/>
       <c r="E31" s="29" t="s">
         <v>12</v>
       </c>
@@ -3762,7 +3758,7 @@
       <c r="Q31" s="2"/>
     </row>
     <row r="32" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D32" s="88"/>
+      <c r="D32" s="89"/>
       <c r="E32" s="29" t="s">
         <v>13</v>
       </c>
@@ -3803,7 +3799,7 @@
       <c r="Q32" s="2"/>
     </row>
     <row r="33" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D33" s="88"/>
+      <c r="D33" s="89"/>
       <c r="E33" s="29" t="s">
         <v>14</v>
       </c>
@@ -3844,7 +3840,7 @@
       <c r="Q33" s="2"/>
     </row>
     <row r="34" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D34" s="88"/>
+      <c r="D34" s="89"/>
       <c r="E34" s="2" t="s">
         <v>15</v>
       </c>
@@ -3895,7 +3891,7 @@
       </c>
     </row>
     <row r="35" spans="4:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D35" s="88"/>
+      <c r="D35" s="89"/>
       <c r="E35" s="2" t="s">
         <v>16</v>
       </c>
@@ -3929,43 +3925,43 @@
       <c r="Q35" s="2"/>
     </row>
     <row r="38" spans="4:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E38" s="77" t="s">
+      <c r="E38" s="79" t="s">
         <v>49</v>
       </c>
-      <c r="F38" s="77"/>
-      <c r="G38" s="77"/>
-      <c r="H38" s="84" t="s">
+      <c r="F38" s="79"/>
+      <c r="G38" s="79"/>
+      <c r="H38" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="I38" s="85"/>
-      <c r="J38" s="85"/>
-      <c r="K38" s="85"/>
-      <c r="L38" s="85"/>
-      <c r="M38" s="85"/>
-      <c r="N38" s="85"/>
-      <c r="O38" s="85"/>
-      <c r="P38" s="85"/>
-      <c r="Q38" s="86"/>
+      <c r="I38" s="92"/>
+      <c r="J38" s="92"/>
+      <c r="K38" s="92"/>
+      <c r="L38" s="92"/>
+      <c r="M38" s="92"/>
+      <c r="N38" s="92"/>
+      <c r="O38" s="92"/>
+      <c r="P38" s="92"/>
+      <c r="Q38" s="93"/>
     </row>
     <row r="39" spans="4:17" ht="25.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="E39" s="2"/>
-      <c r="F39" s="77" t="s">
+      <c r="F39" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77" t="s">
+      <c r="G39" s="79"/>
+      <c r="H39" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="I39" s="77"/>
-      <c r="J39" s="77" t="s">
+      <c r="I39" s="79"/>
+      <c r="J39" s="79" t="s">
         <v>41</v>
       </c>
-      <c r="K39" s="77"/>
+      <c r="K39" s="79"/>
       <c r="L39" s="2"/>
-      <c r="M39" s="77" t="s">
+      <c r="M39" s="79" t="s">
         <v>42</v>
       </c>
-      <c r="N39" s="77"/>
+      <c r="N39" s="79"/>
       <c r="O39" s="19" t="s">
         <v>63</v>
       </c>
@@ -4176,6 +4172,40 @@
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="E12:O12"/>
+    <mergeCell ref="J13:O13"/>
+    <mergeCell ref="E13:I13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="E29:Q29"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="H38:Q38"/>
+    <mergeCell ref="D15:D19"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="E21:Q21"/>
+    <mergeCell ref="D31:D35"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="D23:D27"/>
     <mergeCell ref="E2:I2"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="G9:G10"/>
@@ -4192,40 +4222,6 @@
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="E9:E10"/>
-    <mergeCell ref="D31:D35"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="D23:D27"/>
-    <mergeCell ref="D15:D19"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="E21:Q21"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="H38:Q38"/>
-    <mergeCell ref="E12:O12"/>
-    <mergeCell ref="J13:O13"/>
-    <mergeCell ref="E13:I13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="E29:Q29"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="L9:L10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Color/LogicDocs/formulas y funciones .xlsx
+++ b/Color/LogicDocs/formulas y funciones .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coatsplc-my.sharepoint.com/personal/elkinduvan_quebradaguapacha_coats_com/Documents/Escritorio/Colorimetria/Color/LogicDocs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1226" documentId="8_{9F78D261-5971-4E36-A791-098E2ABB119D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDA06FF1-4140-4466-BBD6-67C59A208200}"/>
+  <xr:revisionPtr revIDLastSave="1227" documentId="8_{9F78D261-5971-4E36-A791-098E2ABB119D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E7DC9B8-9282-4C94-B4FF-940AEA46B31A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="2" xr2:uid="{74F1A0B1-3ED8-4C59-B930-9B261CE40F5C}"/>
+    <workbookView xWindow="345" yWindow="840" windowWidth="12525" windowHeight="11940" activeTab="2" xr2:uid="{74F1A0B1-3ED8-4C59-B930-9B261CE40F5C}"/>
   </bookViews>
   <sheets>
     <sheet name="CMC" sheetId="5" r:id="rId1"/>
@@ -19,7 +19,6 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId4"/>
-    <externalReference r:id="rId5"/>
   </externalReferences>
   <calcPr calcId="191028"/>
   <extLst>
@@ -1097,72 +1096,6 @@
     <xf numFmtId="167" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="28" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="30" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="30" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="30" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="30" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="30" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="30" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1170,6 +1103,72 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="28" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2352,42 +2351,6 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="CMC"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="CMC_Calculator"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="16">
-          <cell r="E16">
-            <v>6.67</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="E17">
-            <v>7.11</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2794,12 +2757,12 @@
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="13"/>
-      <c r="O6" s="66" t="s">
+      <c r="O6" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="P6" s="66"/>
-      <c r="Q6" s="66"/>
-      <c r="R6" s="66"/>
+      <c r="P6" s="91"/>
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
     </row>
     <row r="7" spans="2:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
@@ -2858,7 +2821,7 @@
       </c>
       <c r="L8" s="12"/>
       <c r="M8" s="13"/>
-      <c r="O8" s="67">
+      <c r="O8" s="92">
         <v>1.2</v>
       </c>
       <c r="P8" s="19">
@@ -2896,7 +2859,7 @@
       </c>
       <c r="L9" s="12"/>
       <c r="M9" s="13"/>
-      <c r="O9" s="68"/>
+      <c r="O9" s="93"/>
       <c r="P9" s="22">
         <f>+P8*-1</f>
         <v>-0.69282032302755092</v>
@@ -2993,10 +2956,10 @@
       <c r="N15" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="O15" s="69" t="s">
+      <c r="O15" s="82" t="s">
         <v>33</v>
       </c>
-      <c r="P15" s="69"/>
+      <c r="P15" s="82"/>
     </row>
     <row r="16" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
@@ -3019,24 +2982,24 @@
         <f>MOD(DEGREES(ATAN2(D16, E16)),360)</f>
         <v>137.42529199615964</v>
       </c>
-      <c r="L16" s="70">
+      <c r="L16" s="83">
         <f>C20/(2*L20)</f>
         <v>0.35546916060255679</v>
       </c>
-      <c r="M16" s="70">
+      <c r="M16" s="83">
         <f>H20/(1*M20)</f>
         <v>1.9097043522295685E-4</v>
       </c>
-      <c r="N16" s="70">
+      <c r="N16" s="83">
         <f>I20/O20</f>
         <v>-0.66185554204483898</v>
       </c>
-      <c r="O16" s="71">
+      <c r="O16" s="84">
         <f>SQRT(L16^2+M16^2+N16^2)</f>
         <v>0.75127299907867118</v>
       </c>
-      <c r="P16" s="71"/>
-      <c r="Q16" s="72" t="str">
+      <c r="P16" s="84"/>
+      <c r="Q16" s="85" t="str">
         <f>+B15</f>
         <v>D65</v>
       </c>
@@ -3062,12 +3025,12 @@
         <f>MOD(DEGREES(ATAN2(D17, E17)),360)</f>
         <v>133.84930693757883</v>
       </c>
-      <c r="L17" s="70"/>
-      <c r="M17" s="70"/>
-      <c r="N17" s="70"/>
-      <c r="O17" s="71"/>
-      <c r="P17" s="71"/>
-      <c r="Q17" s="72"/>
+      <c r="L17" s="83"/>
+      <c r="M17" s="83"/>
+      <c r="N17" s="83"/>
+      <c r="O17" s="84"/>
+      <c r="P17" s="84"/>
+      <c r="Q17" s="85"/>
     </row>
     <row r="18" spans="2:17" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L18" s="35"/>
@@ -3075,7 +3038,7 @@
       <c r="N18" s="35"/>
     </row>
     <row r="19" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="73" t="s">
+      <c r="B19" s="72" t="s">
         <v>36</v>
       </c>
       <c r="C19" s="36" t="s">
@@ -3113,7 +3076,7 @@
       </c>
     </row>
     <row r="20" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="73"/>
+      <c r="B20" s="72"/>
       <c r="C20" s="38">
         <f>+C17-C16</f>
         <v>0.75</v>
@@ -3160,7 +3123,7 @@
       </c>
     </row>
     <row r="21" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="73"/>
+      <c r="B21" s="72"/>
       <c r="C21" s="41" t="str">
         <f>+IF(C20&gt;0,C62,C63)</f>
         <v>Claro (Thin)</v>
@@ -3183,7 +3146,7 @@
     </row>
     <row r="22" spans="2:17" ht="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="2:17" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="73" t="s">
         <v>49</v>
       </c>
       <c r="C23" s="45" t="str">
@@ -3212,18 +3175,18 @@
         <f>+_xlfn.XLOOKUP(I21,C70:C78,D70:D78,"")</f>
         <v>Bluer (Greener)</v>
       </c>
-      <c r="L23" s="76" t="str">
+      <c r="L23" s="86" t="str">
         <f>+IF(L35&gt;O25,"FALLA",IF(L35&gt;L25,"alerta","ok"))</f>
         <v>ok</v>
       </c>
-      <c r="M23" s="77"/>
-      <c r="N23" s="77"/>
-      <c r="O23" s="77"/>
-      <c r="P23" s="77"/>
-      <c r="Q23" s="78"/>
+      <c r="M23" s="87"/>
+      <c r="N23" s="87"/>
+      <c r="O23" s="87"/>
+      <c r="P23" s="87"/>
+      <c r="Q23" s="88"/>
     </row>
     <row r="24" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="75"/>
+      <c r="B24" s="74"/>
       <c r="C24" s="48">
         <f>+ABS(C20)/C16</f>
         <v>1.5893197711379529E-2</v>
@@ -3244,26 +3207,26 @@
         <f>+ABS(I20)*0.1</f>
         <v>6.1522349428154724E-2</v>
       </c>
-      <c r="L24" s="79" t="s">
+      <c r="L24" s="89" t="s">
         <v>50</v>
       </c>
-      <c r="M24" s="79"/>
-      <c r="N24" s="79"/>
-      <c r="O24" s="79"/>
-      <c r="P24" s="79"/>
-      <c r="Q24" s="79"/>
+      <c r="M24" s="89"/>
+      <c r="N24" s="89"/>
+      <c r="O24" s="89"/>
+      <c r="P24" s="89"/>
+      <c r="Q24" s="89"/>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="L25" s="80">
+      <c r="L25" s="90">
         <v>0.8</v>
       </c>
-      <c r="M25" s="80"/>
-      <c r="N25" s="80"/>
-      <c r="O25" s="80">
+      <c r="M25" s="90"/>
+      <c r="N25" s="90"/>
+      <c r="O25" s="90">
         <v>1.2</v>
       </c>
-      <c r="P25" s="80"/>
-      <c r="Q25" s="80"/>
+      <c r="P25" s="90"/>
+      <c r="Q25" s="90"/>
     </row>
     <row r="26" spans="2:17" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Q26" s="2"/>
@@ -3296,10 +3259,10 @@
       <c r="N27" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="O27" s="69" t="s">
+      <c r="O27" s="82" t="s">
         <v>33</v>
       </c>
-      <c r="P27" s="69"/>
+      <c r="P27" s="82"/>
     </row>
     <row r="28" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
@@ -3322,24 +3285,24 @@
         <f>MOD(DEGREES(ATAN2(D28, E28)),360)</f>
         <v>140.37238856690334</v>
       </c>
-      <c r="L28" s="70">
+      <c r="L28" s="83">
         <f>C32/(2*L32)</f>
         <v>0.51896398158143286</v>
       </c>
-      <c r="M28" s="70">
+      <c r="M28" s="83">
         <f>H32/(1*M32)</f>
         <v>-1.4856708744546322E-2</v>
       </c>
-      <c r="N28" s="70">
+      <c r="N28" s="83">
         <f>I32/O32</f>
         <v>-1.3112410815593687</v>
       </c>
-      <c r="O28" s="71">
+      <c r="O28" s="84">
         <f>SQRT(L28^2+M28^2+N28^2)</f>
         <v>1.4102827765886377</v>
       </c>
-      <c r="P28" s="71"/>
-      <c r="Q28" s="72" t="str">
+      <c r="P28" s="84"/>
+      <c r="Q28" s="85" t="str">
         <f>+B27</f>
         <v>TL84</v>
       </c>
@@ -3365,12 +3328,12 @@
         <f>MOD(DEGREES(ATAN2(D29, E29)),360)</f>
         <v>133.2767213010336</v>
       </c>
-      <c r="L29" s="70"/>
-      <c r="M29" s="70"/>
-      <c r="N29" s="70"/>
-      <c r="O29" s="71"/>
-      <c r="P29" s="71"/>
-      <c r="Q29" s="72"/>
+      <c r="L29" s="83"/>
+      <c r="M29" s="83"/>
+      <c r="N29" s="83"/>
+      <c r="O29" s="84"/>
+      <c r="P29" s="84"/>
+      <c r="Q29" s="85"/>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="L30" s="35"/>
@@ -3378,7 +3341,7 @@
       <c r="N30" s="35"/>
     </row>
     <row r="31" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="73" t="s">
+      <c r="B31" s="72" t="s">
         <v>36</v>
       </c>
       <c r="C31" s="36" t="s">
@@ -3416,7 +3379,7 @@
       </c>
     </row>
     <row r="32" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="73"/>
+      <c r="B32" s="72"/>
       <c r="C32" s="38">
         <f>+C29-C28</f>
         <v>1.0900000000000034</v>
@@ -3463,7 +3426,7 @@
       </c>
     </row>
     <row r="33" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="73"/>
+      <c r="B33" s="72"/>
       <c r="C33" s="44" t="str">
         <f>+IF(C32&gt;0,C62,C63)</f>
         <v>Claro (Thin)</v>
@@ -3486,7 +3449,7 @@
       </c>
     </row>
     <row r="35" spans="2:17" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="74" t="s">
+      <c r="B35" s="73" t="s">
         <v>49</v>
       </c>
       <c r="C35" s="45" t="str">
@@ -3515,18 +3478,18 @@
         <f>+_xlfn.XLOOKUP(I33,C70:C78,D70:D78,"")</f>
         <v>Bluer (Greener)</v>
       </c>
-      <c r="L35" s="81">
+      <c r="L35" s="76">
         <f>+ABS(O16-O28)</f>
         <v>0.65900977750996648</v>
       </c>
-      <c r="M35" s="82"/>
-      <c r="N35" s="82"/>
-      <c r="O35" s="82"/>
-      <c r="P35" s="82"/>
-      <c r="Q35" s="83"/>
+      <c r="M35" s="77"/>
+      <c r="N35" s="77"/>
+      <c r="O35" s="77"/>
+      <c r="P35" s="77"/>
+      <c r="Q35" s="78"/>
     </row>
     <row r="36" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B36" s="75"/>
+      <c r="B36" s="74"/>
       <c r="C36" s="48">
         <f>+ABS(C32)/C28</f>
         <v>2.3290598290598364E-2</v>
@@ -3547,12 +3510,12 @@
         <f>+ABS(I32)*0.1</f>
         <v>0.12233494443495832</v>
       </c>
-      <c r="L36" s="84"/>
-      <c r="M36" s="85"/>
-      <c r="N36" s="85"/>
-      <c r="O36" s="85"/>
-      <c r="P36" s="85"/>
-      <c r="Q36" s="86"/>
+      <c r="L36" s="79"/>
+      <c r="M36" s="80"/>
+      <c r="N36" s="80"/>
+      <c r="O36" s="80"/>
+      <c r="P36" s="80"/>
+      <c r="Q36" s="81"/>
     </row>
     <row r="38" spans="2:17" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Q38" s="2"/>
@@ -3585,10 +3548,10 @@
       <c r="N39" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="O39" s="69" t="s">
+      <c r="O39" s="82" t="s">
         <v>33</v>
       </c>
-      <c r="P39" s="69"/>
+      <c r="P39" s="82"/>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B40" s="1" t="s">
@@ -3611,24 +3574,24 @@
         <f>MOD(DEGREES(ATAN2(D40, E40)),360)</f>
         <v>139.08561677997488</v>
       </c>
-      <c r="L40" s="70">
+      <c r="L40" s="83">
         <f>C44/(2*L44)</f>
         <v>0.62209112501074215</v>
       </c>
-      <c r="M40" s="70">
+      <c r="M40" s="83">
         <f>H44/(1*M44)</f>
         <v>0.28079926627754348</v>
       </c>
-      <c r="N40" s="70">
+      <c r="N40" s="83">
         <f>I44/O44</f>
         <v>-1.7815064743433757</v>
       </c>
-      <c r="O40" s="71">
+      <c r="O40" s="84">
         <f>SQRT(L40^2+M40^2+N40^2)</f>
         <v>1.9077764318406134</v>
       </c>
-      <c r="P40" s="71"/>
-      <c r="Q40" s="72" t="str">
+      <c r="P40" s="84"/>
+      <c r="Q40" s="85" t="str">
         <f>+B39</f>
         <v>CWF</v>
       </c>
@@ -3654,12 +3617,12 @@
         <f>MOD(DEGREES(ATAN2(D41, E41)),360)</f>
         <v>128.57893917650927</v>
       </c>
-      <c r="L41" s="70"/>
-      <c r="M41" s="70"/>
-      <c r="N41" s="70"/>
-      <c r="O41" s="71"/>
-      <c r="P41" s="71"/>
-      <c r="Q41" s="72"/>
+      <c r="L41" s="83"/>
+      <c r="M41" s="83"/>
+      <c r="N41" s="83"/>
+      <c r="O41" s="84"/>
+      <c r="P41" s="84"/>
+      <c r="Q41" s="85"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.25">
       <c r="L42" s="35"/>
@@ -3667,7 +3630,7 @@
       <c r="N42" s="35"/>
     </row>
     <row r="43" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="73" t="s">
+      <c r="B43" s="72" t="s">
         <v>36</v>
       </c>
       <c r="C43" s="36" t="s">
@@ -3705,7 +3668,7 @@
       </c>
     </row>
     <row r="44" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="73"/>
+      <c r="B44" s="72"/>
       <c r="C44" s="38">
         <f>+C41-C40</f>
         <v>1.3000000000000043</v>
@@ -3752,7 +3715,7 @@
       </c>
     </row>
     <row r="45" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="73"/>
+      <c r="B45" s="72"/>
       <c r="C45" s="44" t="str">
         <f>+IF(C44&gt;0,C62,C63)</f>
         <v>Claro (Thin)</v>
@@ -3775,7 +3738,7 @@
       </c>
     </row>
     <row r="47" spans="2:17" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="74" t="s">
+      <c r="B47" s="73" t="s">
         <v>49</v>
       </c>
       <c r="C47" s="45" t="str">
@@ -3806,7 +3769,7 @@
       </c>
     </row>
     <row r="48" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B48" s="75"/>
+      <c r="B48" s="74"/>
       <c r="C48" s="48">
         <f>+ABS(C44)/C40</f>
         <v>2.8035367694630241E-2</v>
@@ -4075,10 +4038,10 @@
       <c r="E62" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="F62" s="87" t="s">
+      <c r="F62" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="G62" s="87"/>
+      <c r="G62" s="75"/>
       <c r="H62" s="55">
         <v>100</v>
       </c>
@@ -4093,10 +4056,10 @@
       <c r="E63" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="F63" s="87" t="s">
+      <c r="F63" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="G63" s="87"/>
+      <c r="G63" s="75"/>
       <c r="H63" s="57">
         <v>0</v>
       </c>
@@ -4546,19 +4509,14 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="L35:Q36"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="L40:L41"/>
-    <mergeCell ref="M40:M41"/>
-    <mergeCell ref="N40:N41"/>
-    <mergeCell ref="O40:P41"/>
-    <mergeCell ref="Q40:Q41"/>
+    <mergeCell ref="O6:R6"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="O16:P17"/>
+    <mergeCell ref="Q16:Q17"/>
     <mergeCell ref="Q28:Q29"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="B23:B24"/>
@@ -4571,14 +4529,19 @@
     <mergeCell ref="M28:M29"/>
     <mergeCell ref="N28:N29"/>
     <mergeCell ref="O28:P29"/>
-    <mergeCell ref="O6:R6"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="L16:L17"/>
-    <mergeCell ref="M16:M17"/>
-    <mergeCell ref="N16:N17"/>
-    <mergeCell ref="O16:P17"/>
-    <mergeCell ref="Q16:Q17"/>
+    <mergeCell ref="L35:Q36"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="L40:L41"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="N40:N41"/>
+    <mergeCell ref="O40:P41"/>
+    <mergeCell ref="Q40:Q41"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="B35:B36"/>
   </mergeCells>
   <conditionalFormatting sqref="E7:E9">
     <cfRule type="dataBar" priority="19">
@@ -5117,123 +5080,123 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="89">
+      <c r="C2" s="67">
         <v>1.8</v>
       </c>
-      <c r="E2" s="88" t="s">
+      <c r="E2" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="F2" s="89">
+      <c r="F2" s="67">
         <v>1.2</v>
       </c>
-      <c r="G2" s="90"/>
-      <c r="H2" s="88" t="s">
+      <c r="G2" s="68"/>
+      <c r="H2" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="I2" s="89">
+      <c r="I2" s="67">
         <v>0.6</v>
       </c>
-      <c r="J2" s="90"/>
-      <c r="K2" s="88" t="s">
+      <c r="J2" s="68"/>
+      <c r="K2" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="L2" s="89"/>
+      <c r="L2" s="67"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="91" t="s">
+      <c r="B3" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="92">
+      <c r="C3" s="70">
         <f>SQRT(($L$2^2)/3)</f>
         <v>0</v>
       </c>
-      <c r="E3" s="91" t="s">
+      <c r="E3" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="F3" s="92">
+      <c r="F3" s="70">
         <f>SQRT(($F$2^2)/3)</f>
         <v>0.69282032302755092</v>
       </c>
-      <c r="H3" s="91" t="s">
+      <c r="H3" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="I3" s="92">
+      <c r="I3" s="70">
         <f>SQRT(($I$2^2)/3)</f>
         <v>0.34641016151377546</v>
       </c>
-      <c r="K3" s="91" t="s">
+      <c r="K3" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="L3" s="92">
+      <c r="L3" s="70">
         <f>SQRT(($L$2^2)/3)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="91" t="s">
+      <c r="B4" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="92">
+      <c r="C4" s="70">
         <f t="shared" ref="C4:C5" si="0">SQRT(($L$2^2)/3)</f>
         <v>0</v>
       </c>
-      <c r="E4" s="91" t="s">
+      <c r="E4" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="F4" s="92">
+      <c r="F4" s="70">
         <f t="shared" ref="F4:F5" si="1">SQRT(($F$2^2)/3)</f>
         <v>0.69282032302755092</v>
       </c>
-      <c r="H4" s="91" t="s">
+      <c r="H4" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="I4" s="92">
+      <c r="I4" s="70">
         <f t="shared" ref="I4:I5" si="2">SQRT(($I$2^2)/3)</f>
         <v>0.34641016151377546</v>
       </c>
-      <c r="K4" s="91" t="s">
+      <c r="K4" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="L4" s="92">
+      <c r="L4" s="70">
         <f t="shared" ref="L4:L5" si="3">SQRT(($L$2^2)/3)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" s="91" t="s">
+      <c r="B5" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="92">
+      <c r="C5" s="70">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E5" s="91" t="s">
+      <c r="E5" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="F5" s="92">
+      <c r="F5" s="70">
         <f t="shared" si="1"/>
         <v>0.69282032302755092</v>
       </c>
-      <c r="H5" s="91" t="s">
+      <c r="H5" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="I5" s="92">
+      <c r="I5" s="70">
         <f t="shared" si="2"/>
         <v>0.34641016151377546</v>
       </c>
-      <c r="K5" s="91" t="s">
+      <c r="K5" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="L5" s="92">
+      <c r="L5" s="70">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="H12" s="93"/>
+      <c r="H12" s="71"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Color/LogicDocs/formulas y funciones .xlsx
+++ b/Color/LogicDocs/formulas y funciones .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coatsplc-my.sharepoint.com/personal/elkinduvan_quebradaguapacha_coats_com/Documents/Escritorio/Colorimetria/Color/LogicDocs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1227" documentId="8_{9F78D261-5971-4E36-A791-098E2ABB119D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E7DC9B8-9282-4C94-B4FF-940AEA46B31A}"/>
+  <xr:revisionPtr revIDLastSave="1229" documentId="8_{9F78D261-5971-4E36-A791-098E2ABB119D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61CD409D-47B9-4A6F-B97C-96DB24835E62}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="840" windowWidth="12525" windowHeight="11940" activeTab="2" xr2:uid="{74F1A0B1-3ED8-4C59-B930-9B261CE40F5C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{74F1A0B1-3ED8-4C59-B930-9B261CE40F5C}"/>
   </bookViews>
   <sheets>
     <sheet name="CMC" sheetId="5" r:id="rId1"/>
@@ -19,6 +19,7 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <calcPr calcId="191028"/>
   <extLst>
@@ -1104,6 +1105,27 @@
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1113,61 +1135,40 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="28" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="30" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="30" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="30" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="30" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="30" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="30" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="28" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2351,6 +2352,40 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="CMC"/>
+      <sheetName val="CMC_Calculator"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="16">
+          <cell r="E16">
+            <v>-26.66</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="E17">
+            <v>-26.3</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2757,12 +2792,12 @@
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="13"/>
-      <c r="O6" s="91" t="s">
+      <c r="O6" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="P6" s="91"/>
-      <c r="Q6" s="91"/>
-      <c r="R6" s="91"/>
+      <c r="P6" s="72"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="72"/>
     </row>
     <row r="7" spans="2:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
@@ -2821,7 +2856,7 @@
       </c>
       <c r="L8" s="12"/>
       <c r="M8" s="13"/>
-      <c r="O8" s="92">
+      <c r="O8" s="73">
         <v>1.2</v>
       </c>
       <c r="P8" s="19">
@@ -2859,7 +2894,7 @@
       </c>
       <c r="L9" s="12"/>
       <c r="M9" s="13"/>
-      <c r="O9" s="93"/>
+      <c r="O9" s="74"/>
       <c r="P9" s="22">
         <f>+P8*-1</f>
         <v>-0.69282032302755092</v>
@@ -2956,10 +2991,10 @@
       <c r="N15" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="O15" s="82" t="s">
+      <c r="O15" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="P15" s="82"/>
+      <c r="P15" s="75"/>
     </row>
     <row r="16" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
@@ -2982,24 +3017,24 @@
         <f>MOD(DEGREES(ATAN2(D16, E16)),360)</f>
         <v>137.42529199615964</v>
       </c>
-      <c r="L16" s="83">
+      <c r="L16" s="76">
         <f>C20/(2*L20)</f>
         <v>0.35546916060255679</v>
       </c>
-      <c r="M16" s="83">
+      <c r="M16" s="76">
         <f>H20/(1*M20)</f>
         <v>1.9097043522295685E-4</v>
       </c>
-      <c r="N16" s="83">
+      <c r="N16" s="76">
         <f>I20/O20</f>
         <v>-0.66185554204483898</v>
       </c>
-      <c r="O16" s="84">
+      <c r="O16" s="77">
         <f>SQRT(L16^2+M16^2+N16^2)</f>
         <v>0.75127299907867118</v>
       </c>
-      <c r="P16" s="84"/>
-      <c r="Q16" s="85" t="str">
+      <c r="P16" s="77"/>
+      <c r="Q16" s="78" t="str">
         <f>+B15</f>
         <v>D65</v>
       </c>
@@ -3025,12 +3060,12 @@
         <f>MOD(DEGREES(ATAN2(D17, E17)),360)</f>
         <v>133.84930693757883</v>
       </c>
-      <c r="L17" s="83"/>
-      <c r="M17" s="83"/>
-      <c r="N17" s="83"/>
-      <c r="O17" s="84"/>
-      <c r="P17" s="84"/>
-      <c r="Q17" s="85"/>
+      <c r="L17" s="76"/>
+      <c r="M17" s="76"/>
+      <c r="N17" s="76"/>
+      <c r="O17" s="77"/>
+      <c r="P17" s="77"/>
+      <c r="Q17" s="78"/>
     </row>
     <row r="18" spans="2:17" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L18" s="35"/>
@@ -3038,7 +3073,7 @@
       <c r="N18" s="35"/>
     </row>
     <row r="19" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="72" t="s">
+      <c r="B19" s="79" t="s">
         <v>36</v>
       </c>
       <c r="C19" s="36" t="s">
@@ -3076,7 +3111,7 @@
       </c>
     </row>
     <row r="20" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="72"/>
+      <c r="B20" s="79"/>
       <c r="C20" s="38">
         <f>+C17-C16</f>
         <v>0.75</v>
@@ -3123,7 +3158,7 @@
       </c>
     </row>
     <row r="21" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="72"/>
+      <c r="B21" s="79"/>
       <c r="C21" s="41" t="str">
         <f>+IF(C20&gt;0,C62,C63)</f>
         <v>Claro (Thin)</v>
@@ -3146,7 +3181,7 @@
     </row>
     <row r="22" spans="2:17" ht="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="2:17" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="73" t="s">
+      <c r="B23" s="80" t="s">
         <v>49</v>
       </c>
       <c r="C23" s="45" t="str">
@@ -3175,18 +3210,18 @@
         <f>+_xlfn.XLOOKUP(I21,C70:C78,D70:D78,"")</f>
         <v>Bluer (Greener)</v>
       </c>
-      <c r="L23" s="86" t="str">
+      <c r="L23" s="82" t="str">
         <f>+IF(L35&gt;O25,"FALLA",IF(L35&gt;L25,"alerta","ok"))</f>
         <v>ok</v>
       </c>
-      <c r="M23" s="87"/>
-      <c r="N23" s="87"/>
-      <c r="O23" s="87"/>
-      <c r="P23" s="87"/>
-      <c r="Q23" s="88"/>
+      <c r="M23" s="83"/>
+      <c r="N23" s="83"/>
+      <c r="O23" s="83"/>
+      <c r="P23" s="83"/>
+      <c r="Q23" s="84"/>
     </row>
     <row r="24" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="74"/>
+      <c r="B24" s="81"/>
       <c r="C24" s="48">
         <f>+ABS(C20)/C16</f>
         <v>1.5893197711379529E-2</v>
@@ -3207,26 +3242,26 @@
         <f>+ABS(I20)*0.1</f>
         <v>6.1522349428154724E-2</v>
       </c>
-      <c r="L24" s="89" t="s">
+      <c r="L24" s="85" t="s">
         <v>50</v>
       </c>
-      <c r="M24" s="89"/>
-      <c r="N24" s="89"/>
-      <c r="O24" s="89"/>
-      <c r="P24" s="89"/>
-      <c r="Q24" s="89"/>
+      <c r="M24" s="85"/>
+      <c r="N24" s="85"/>
+      <c r="O24" s="85"/>
+      <c r="P24" s="85"/>
+      <c r="Q24" s="85"/>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="L25" s="90">
+      <c r="L25" s="86">
         <v>0.8</v>
       </c>
-      <c r="M25" s="90"/>
-      <c r="N25" s="90"/>
-      <c r="O25" s="90">
+      <c r="M25" s="86"/>
+      <c r="N25" s="86"/>
+      <c r="O25" s="86">
         <v>1.2</v>
       </c>
-      <c r="P25" s="90"/>
-      <c r="Q25" s="90"/>
+      <c r="P25" s="86"/>
+      <c r="Q25" s="86"/>
     </row>
     <row r="26" spans="2:17" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Q26" s="2"/>
@@ -3259,10 +3294,10 @@
       <c r="N27" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="O27" s="82" t="s">
+      <c r="O27" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="P27" s="82"/>
+      <c r="P27" s="75"/>
     </row>
     <row r="28" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
@@ -3285,24 +3320,24 @@
         <f>MOD(DEGREES(ATAN2(D28, E28)),360)</f>
         <v>140.37238856690334</v>
       </c>
-      <c r="L28" s="83">
+      <c r="L28" s="76">
         <f>C32/(2*L32)</f>
         <v>0.51896398158143286</v>
       </c>
-      <c r="M28" s="83">
+      <c r="M28" s="76">
         <f>H32/(1*M32)</f>
         <v>-1.4856708744546322E-2</v>
       </c>
-      <c r="N28" s="83">
+      <c r="N28" s="76">
         <f>I32/O32</f>
         <v>-1.3112410815593687</v>
       </c>
-      <c r="O28" s="84">
+      <c r="O28" s="77">
         <f>SQRT(L28^2+M28^2+N28^2)</f>
         <v>1.4102827765886377</v>
       </c>
-      <c r="P28" s="84"/>
-      <c r="Q28" s="85" t="str">
+      <c r="P28" s="77"/>
+      <c r="Q28" s="78" t="str">
         <f>+B27</f>
         <v>TL84</v>
       </c>
@@ -3328,12 +3363,12 @@
         <f>MOD(DEGREES(ATAN2(D29, E29)),360)</f>
         <v>133.2767213010336</v>
       </c>
-      <c r="L29" s="83"/>
-      <c r="M29" s="83"/>
-      <c r="N29" s="83"/>
-      <c r="O29" s="84"/>
-      <c r="P29" s="84"/>
-      <c r="Q29" s="85"/>
+      <c r="L29" s="76"/>
+      <c r="M29" s="76"/>
+      <c r="N29" s="76"/>
+      <c r="O29" s="77"/>
+      <c r="P29" s="77"/>
+      <c r="Q29" s="78"/>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="L30" s="35"/>
@@ -3341,7 +3376,7 @@
       <c r="N30" s="35"/>
     </row>
     <row r="31" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="72" t="s">
+      <c r="B31" s="79" t="s">
         <v>36</v>
       </c>
       <c r="C31" s="36" t="s">
@@ -3379,7 +3414,7 @@
       </c>
     </row>
     <row r="32" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="72"/>
+      <c r="B32" s="79"/>
       <c r="C32" s="38">
         <f>+C29-C28</f>
         <v>1.0900000000000034</v>
@@ -3426,7 +3461,7 @@
       </c>
     </row>
     <row r="33" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="72"/>
+      <c r="B33" s="79"/>
       <c r="C33" s="44" t="str">
         <f>+IF(C32&gt;0,C62,C63)</f>
         <v>Claro (Thin)</v>
@@ -3449,7 +3484,7 @@
       </c>
     </row>
     <row r="35" spans="2:17" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="73" t="s">
+      <c r="B35" s="80" t="s">
         <v>49</v>
       </c>
       <c r="C35" s="45" t="str">
@@ -3478,18 +3513,18 @@
         <f>+_xlfn.XLOOKUP(I33,C70:C78,D70:D78,"")</f>
         <v>Bluer (Greener)</v>
       </c>
-      <c r="L35" s="76">
+      <c r="L35" s="87">
         <f>+ABS(O16-O28)</f>
         <v>0.65900977750996648</v>
       </c>
-      <c r="M35" s="77"/>
-      <c r="N35" s="77"/>
-      <c r="O35" s="77"/>
-      <c r="P35" s="77"/>
-      <c r="Q35" s="78"/>
+      <c r="M35" s="88"/>
+      <c r="N35" s="88"/>
+      <c r="O35" s="88"/>
+      <c r="P35" s="88"/>
+      <c r="Q35" s="89"/>
     </row>
     <row r="36" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B36" s="74"/>
+      <c r="B36" s="81"/>
       <c r="C36" s="48">
         <f>+ABS(C32)/C28</f>
         <v>2.3290598290598364E-2</v>
@@ -3510,12 +3545,12 @@
         <f>+ABS(I32)*0.1</f>
         <v>0.12233494443495832</v>
       </c>
-      <c r="L36" s="79"/>
-      <c r="M36" s="80"/>
-      <c r="N36" s="80"/>
-      <c r="O36" s="80"/>
-      <c r="P36" s="80"/>
-      <c r="Q36" s="81"/>
+      <c r="L36" s="90"/>
+      <c r="M36" s="91"/>
+      <c r="N36" s="91"/>
+      <c r="O36" s="91"/>
+      <c r="P36" s="91"/>
+      <c r="Q36" s="92"/>
     </row>
     <row r="38" spans="2:17" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Q38" s="2"/>
@@ -3548,10 +3583,10 @@
       <c r="N39" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="O39" s="82" t="s">
+      <c r="O39" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="P39" s="82"/>
+      <c r="P39" s="75"/>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B40" s="1" t="s">
@@ -3574,24 +3609,24 @@
         <f>MOD(DEGREES(ATAN2(D40, E40)),360)</f>
         <v>139.08561677997488</v>
       </c>
-      <c r="L40" s="83">
+      <c r="L40" s="76">
         <f>C44/(2*L44)</f>
         <v>0.62209112501074215</v>
       </c>
-      <c r="M40" s="83">
+      <c r="M40" s="76">
         <f>H44/(1*M44)</f>
         <v>0.28079926627754348</v>
       </c>
-      <c r="N40" s="83">
+      <c r="N40" s="76">
         <f>I44/O44</f>
         <v>-1.7815064743433757</v>
       </c>
-      <c r="O40" s="84">
+      <c r="O40" s="77">
         <f>SQRT(L40^2+M40^2+N40^2)</f>
         <v>1.9077764318406134</v>
       </c>
-      <c r="P40" s="84"/>
-      <c r="Q40" s="85" t="str">
+      <c r="P40" s="77"/>
+      <c r="Q40" s="78" t="str">
         <f>+B39</f>
         <v>CWF</v>
       </c>
@@ -3617,12 +3652,12 @@
         <f>MOD(DEGREES(ATAN2(D41, E41)),360)</f>
         <v>128.57893917650927</v>
       </c>
-      <c r="L41" s="83"/>
-      <c r="M41" s="83"/>
-      <c r="N41" s="83"/>
-      <c r="O41" s="84"/>
-      <c r="P41" s="84"/>
-      <c r="Q41" s="85"/>
+      <c r="L41" s="76"/>
+      <c r="M41" s="76"/>
+      <c r="N41" s="76"/>
+      <c r="O41" s="77"/>
+      <c r="P41" s="77"/>
+      <c r="Q41" s="78"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.25">
       <c r="L42" s="35"/>
@@ -3630,7 +3665,7 @@
       <c r="N42" s="35"/>
     </row>
     <row r="43" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="72" t="s">
+      <c r="B43" s="79" t="s">
         <v>36</v>
       </c>
       <c r="C43" s="36" t="s">
@@ -3668,7 +3703,7 @@
       </c>
     </row>
     <row r="44" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="72"/>
+      <c r="B44" s="79"/>
       <c r="C44" s="38">
         <f>+C41-C40</f>
         <v>1.3000000000000043</v>
@@ -3715,7 +3750,7 @@
       </c>
     </row>
     <row r="45" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="72"/>
+      <c r="B45" s="79"/>
       <c r="C45" s="44" t="str">
         <f>+IF(C44&gt;0,C62,C63)</f>
         <v>Claro (Thin)</v>
@@ -3738,7 +3773,7 @@
       </c>
     </row>
     <row r="47" spans="2:17" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="73" t="s">
+      <c r="B47" s="80" t="s">
         <v>49</v>
       </c>
       <c r="C47" s="45" t="str">
@@ -3769,7 +3804,7 @@
       </c>
     </row>
     <row r="48" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B48" s="74"/>
+      <c r="B48" s="81"/>
       <c r="C48" s="48">
         <f>+ABS(C44)/C40</f>
         <v>2.8035367694630241E-2</v>
@@ -4038,10 +4073,10 @@
       <c r="E62" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="F62" s="75" t="s">
+      <c r="F62" s="93" t="s">
         <v>61</v>
       </c>
-      <c r="G62" s="75"/>
+      <c r="G62" s="93"/>
       <c r="H62" s="55">
         <v>100</v>
       </c>
@@ -4056,10 +4091,10 @@
       <c r="E63" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="F63" s="75" t="s">
+      <c r="F63" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="G63" s="75"/>
+      <c r="G63" s="93"/>
       <c r="H63" s="57">
         <v>0</v>
       </c>
@@ -4509,14 +4544,19 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="O6:R6"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="L16:L17"/>
-    <mergeCell ref="M16:M17"/>
-    <mergeCell ref="N16:N17"/>
-    <mergeCell ref="O16:P17"/>
-    <mergeCell ref="Q16:Q17"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="L35:Q36"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="L40:L41"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="N40:N41"/>
+    <mergeCell ref="O40:P41"/>
+    <mergeCell ref="Q40:Q41"/>
     <mergeCell ref="Q28:Q29"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="B23:B24"/>
@@ -4529,19 +4569,14 @@
     <mergeCell ref="M28:M29"/>
     <mergeCell ref="N28:N29"/>
     <mergeCell ref="O28:P29"/>
-    <mergeCell ref="L35:Q36"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="L40:L41"/>
-    <mergeCell ref="M40:M41"/>
-    <mergeCell ref="N40:N41"/>
-    <mergeCell ref="O40:P41"/>
-    <mergeCell ref="Q40:Q41"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="O6:R6"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="O16:P17"/>
+    <mergeCell ref="Q16:Q17"/>
   </mergeCells>
   <conditionalFormatting sqref="E7:E9">
     <cfRule type="dataBar" priority="19">
